--- a/data/drafts/新增门店_严格排柜结果.xlsx
+++ b/data/drafts/新增门店_严格排柜结果.xlsx
@@ -14,9 +14,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">'10%触发_门店汇总'!A1:Q2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'10%触发_SKU明细'!A1:AK72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'10%触发_外储明细'!A1:M55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'10%触发_柜段余量'!A1:N35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'10%触发_未排入SKU清单'!A1:K25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'10%触发_外储明细'!A1:M53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'10%触发_柜段余量'!A1:N37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'10%触发_未排入SKU清单'!A1:K23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">'71SKU有效池明细'!A1:Q72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">'测算规则说明'!A1:B3</definedName>
   </definedNames>
@@ -473,7 +473,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>小于等于10%触发</v>
@@ -485,28 +485,28 @@
         <v>71</v>
       </c>
       <c r="E2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H2">
         <v>30</v>
       </c>
       <c r="I2">
-        <v>989.6</v>
+        <v>973.7</v>
       </c>
       <c r="J2">
-        <v>494.8</v>
+        <v>486.9</v>
       </c>
       <c r="K2">
-        <v>614.4</v>
+        <v>604.6</v>
       </c>
       <c r="L2">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="M2" t="str">
         <v>未超754L</v>
@@ -651,7 +651,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>酥皮牛肉馅饼500g</v>
@@ -678,7 +678,7 @@
         <v>卧柜</v>
       </c>
       <c r="L2" t="str">
-        <v>卧柜2500mm-柜1</v>
+        <v>卧柜2505mm-柜1</v>
       </c>
       <c r="M2" t="str">
         <v>分区2</v>
@@ -752,7 +752,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g</v>
@@ -779,7 +779,7 @@
         <v>卧柜</v>
       </c>
       <c r="L3" t="str">
-        <v>卧柜2500mm-柜2</v>
+        <v>卧柜2505mm-柜2</v>
       </c>
       <c r="M3" t="str">
         <v>分区2</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>【真值】甄选黄油鸡蛋灌饼皮640g</v>
@@ -880,7 +880,7 @@
         <v>卧柜</v>
       </c>
       <c r="L4" t="str">
-        <v>卧柜2500mm-柜3</v>
+        <v>卧柜2505mm-柜3</v>
       </c>
       <c r="M4" t="str">
         <v>分区2</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>酥皮香菇猪肉馅饼500g</v>
@@ -981,7 +981,7 @@
         <v>卧柜</v>
       </c>
       <c r="L5" t="str">
-        <v>卧柜2000mm-柜4</v>
+        <v>卧柜2505mm-柜4</v>
       </c>
       <c r="M5" t="str">
         <v>分区2</v>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>纸皮韭菜盒子280g</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>老上海葱油饼900g</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>毛肚/200g</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>火锅三宝/450g（毛肚+千层肚+鸭肠）</v>
@@ -1385,10 +1385,10 @@
         <v>立柜</v>
       </c>
       <c r="L9" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="M9" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="N9" t="str">
         <v>主陈列</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
         <v>冰鲜鸭肠/200g</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
         <v>【真值】大个爆汁鲜肉包800g</v>
@@ -1587,7 +1587,7 @@
         <v>立柜</v>
       </c>
       <c r="L11" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="M11" t="str">
         <v>第3层</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
         <v>【真值】大个三鲜青菜包800g</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
         <v>麻辣小龙虾1000g</v>
@@ -1789,7 +1789,7 @@
         <v>立柜</v>
       </c>
       <c r="L13" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="M13" t="str">
         <v>第4层</v>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>番茄肉酱意大利面280g</v>
@@ -1890,10 +1890,10 @@
         <v>立柜</v>
       </c>
       <c r="L14" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="M14" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="N14" t="str">
         <v>主陈列</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>【真值】纸皮烧麦蛋黄味240g</v>
@@ -1991,10 +1991,10 @@
         <v>立柜</v>
       </c>
       <c r="L15" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="M15" t="str">
-        <v>第2层</v>
+        <v>第1层</v>
       </c>
       <c r="N15" t="str">
         <v>主陈列</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>【真值】纸皮烧麦鲜肉味240g</v>
@@ -2092,10 +2092,10 @@
         <v>立柜</v>
       </c>
       <c r="L16" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="M16" t="str">
-        <v>第3层</v>
+        <v>第4层</v>
       </c>
       <c r="N16" t="str">
         <v>主陈列</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>【真值】纸皮烧麦香菇味240g</v>
@@ -2193,7 +2193,7 @@
         <v>立柜</v>
       </c>
       <c r="L17" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="M17" t="str">
         <v>第1层</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>【真好】乌米三丁纸皮烧麦240g</v>
@@ -2294,10 +2294,10 @@
         <v>立柜</v>
       </c>
       <c r="L18" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="M18" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="N18" t="str">
         <v>主陈列</v>
@@ -2368,7 +2368,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>【真好】黑猪肉梅干菜纸皮烧麦240g</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>【真好】黑松露纸皮烧麦240g</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>鸡胸肉/400g</v>
@@ -2597,10 +2597,10 @@
         <v>立柜</v>
       </c>
       <c r="L21" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="M21" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="N21" t="str">
         <v>主陈列</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>安格斯牛排150g</v>
@@ -2695,34 +2695,34 @@
         <v>冷冻食材</v>
       </c>
       <c r="K22" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>卧柜1886mm-柜5</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="N22" t="str">
         <v>主陈列</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="U22">
         <v>40</v>
@@ -2752,19 +2752,19 @@
         <v>40</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF22">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="AG22">
-        <v>31.824</v>
+        <v>3.1824</v>
       </c>
       <c r="AH22">
-        <v>15.912</v>
+        <v>1.5912</v>
       </c>
       <c r="AK22" t="str">
         <v>是</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>潮香村眼肉牛排3片装</v>
@@ -2799,10 +2799,10 @@
         <v>立柜</v>
       </c>
       <c r="L23" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="M23" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="N23" t="str">
         <v>主陈列</v>
@@ -2873,7 +2873,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B24" t="str">
         <v>冷冻鸡翅根/400g</v>
@@ -2974,7 +2974,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B25" t="str">
         <v>鸡爪/400g</v>
@@ -3075,7 +3075,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B26" t="str">
         <v>抽肠青虾仁150g</v>
@@ -3102,16 +3102,16 @@
         <v>立柜</v>
       </c>
       <c r="L26" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="M26" t="str">
-        <v>第4层</v>
+        <v>第5层</v>
       </c>
       <c r="N26" t="str">
         <v>主陈列</v>
       </c>
       <c r="O26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P26">
         <v>2</v>
@@ -3120,13 +3120,13 @@
         <v>275</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T26">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U26">
         <v>30</v>
@@ -3159,16 +3159,16 @@
         <v>1</v>
       </c>
       <c r="AE26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF26">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG26">
-        <v>38.0538</v>
+        <v>40.8726</v>
       </c>
       <c r="AH26">
-        <v>19.0269</v>
+        <v>20.4363</v>
       </c>
       <c r="AK26" t="str">
         <v>是</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B27" t="str">
         <v>黑鱼片250g</v>
@@ -3203,7 +3203,7 @@
         <v>立柜</v>
       </c>
       <c r="L27" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="M27" t="str">
         <v>第5层</v>
@@ -3212,7 +3212,7 @@
         <v>主陈列</v>
       </c>
       <c r="O27">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P27">
         <v>4</v>
@@ -3221,13 +3221,13 @@
         <v>190</v>
       </c>
       <c r="R27">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="S27">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T27">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="U27">
         <v>25</v>
@@ -3257,19 +3257,19 @@
         <v>104.9</v>
       </c>
       <c r="AD27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AF27">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AG27">
-        <v>11.115</v>
+        <v>16.302</v>
       </c>
       <c r="AH27">
-        <v>5.5575</v>
+        <v>8.151</v>
       </c>
       <c r="AK27" t="str">
         <v>是</v>
@@ -3277,7 +3277,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B28" t="str">
         <v>整虾/冷冻南美白虾250g</v>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
         <v>带鱼段400g</v>
@@ -3479,7 +3479,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
         <v>冻榴莲500g</v>
@@ -3506,7 +3506,7 @@
         <v>卧柜</v>
       </c>
       <c r="L30" t="str">
-        <v>卧柜2500mm-柜3</v>
+        <v>卧柜2505mm-柜4</v>
       </c>
       <c r="M30" t="str">
         <v>分区1</v>
@@ -3518,19 +3518,19 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q30">
         <v>270</v>
       </c>
       <c r="R30">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="S30">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="T30">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="U30">
         <v>30</v>
@@ -3560,7 +3560,7 @@
         <v>43.3</v>
       </c>
       <c r="AD30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AE30">
         <v>30</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
         <v>双色开花馒头（紫薯味+南瓜味）360g</v>
@@ -3607,10 +3607,10 @@
         <v>立柜</v>
       </c>
       <c r="L31" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="M31" t="str">
-        <v>第1层</v>
+        <v>第2层</v>
       </c>
       <c r="N31" t="str">
         <v>主陈列</v>
@@ -3681,7 +3681,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
         <v>手作奶香黄油开花馒头360g</v>
@@ -3708,10 +3708,10 @@
         <v>立柜</v>
       </c>
       <c r="L32" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="M32" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="N32" t="str">
         <v>主陈列</v>
@@ -3782,7 +3782,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
         <v>生活馆_料多多薯香乳酪包/400g</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
         <v>鲜奶馒头300g</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
         <v>皓月新西兰羔羊卷WMT/450g</v>
@@ -4011,31 +4011,31 @@
         <v>立柜</v>
       </c>
       <c r="L35" t="str">
-        <v/>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>第2层</v>
       </c>
       <c r="N35" t="str">
         <v>主陈列</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>15</v>
@@ -4065,19 +4065,19 @@
         <v>44</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF35">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AG35">
-        <v>27.945</v>
+        <v>18.63</v>
       </c>
       <c r="AH35">
-        <v>13.9725</v>
+        <v>9.315</v>
       </c>
       <c r="AK35" t="str">
         <v>是</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B36" t="str">
         <v>原切肥羊卷300g</v>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B37" t="str">
         <v>【真好】黑猪肉爆汁烤肠原味400g</v>
@@ -4213,10 +4213,10 @@
         <v>立柜</v>
       </c>
       <c r="L37" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="M37" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="N37" t="str">
         <v>主陈列</v>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B38" t="str">
         <v>肉馅芹菜饺480g（两袋仅15.8元）</v>
@@ -4314,16 +4314,16 @@
         <v>立柜</v>
       </c>
       <c r="L38" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="M38" t="str">
-        <v>第1层</v>
+        <v>第4层</v>
       </c>
       <c r="N38" t="str">
         <v>主陈列</v>
       </c>
       <c r="O38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38">
         <v>2</v>
@@ -4332,13 +4332,13 @@
         <v>315</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U38">
         <v>20</v>
@@ -4371,16 +4371,16 @@
         <v>1</v>
       </c>
       <c r="AE38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF38">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG38">
-        <v>51.471</v>
+        <v>46.053</v>
       </c>
       <c r="AH38">
-        <v>25.7355</v>
+        <v>23.0265</v>
       </c>
       <c r="AK38" t="str">
         <v>是</v>
@@ -4388,7 +4388,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B39" t="str">
         <v>荠菜笋丁鸡胸肉水饺480g</v>
@@ -4415,16 +4415,16 @@
         <v>立柜</v>
       </c>
       <c r="L39" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="M39" t="str">
-        <v>第1层</v>
+        <v>第2层</v>
       </c>
       <c r="N39" t="str">
         <v>主陈列</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P39">
         <v>2</v>
@@ -4433,13 +4433,13 @@
         <v>310</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U39">
         <v>20</v>
@@ -4472,16 +4472,16 @@
         <v>1</v>
       </c>
       <c r="AE39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF39">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG39">
-        <v>58.311</v>
+        <v>52.173</v>
       </c>
       <c r="AH39">
-        <v>29.1555</v>
+        <v>26.0865</v>
       </c>
       <c r="AK39" t="str">
         <v>是</v>
@@ -4489,7 +4489,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B40" t="str">
         <v>肉馅玉米饺480g（两袋仅15.8元）</v>
@@ -4516,10 +4516,10 @@
         <v>立柜</v>
       </c>
       <c r="L40" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="M40" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="N40" t="str">
         <v>主陈列</v>
@@ -4590,7 +4590,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B41" t="str">
         <v>生活馆_鲜肉小馄饨/++/512g</v>
@@ -4617,10 +4617,10 @@
         <v>立柜</v>
       </c>
       <c r="L41" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="M41" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="N41" t="str">
         <v>主陈列</v>
@@ -4691,7 +4691,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B42" t="str">
         <v>生活馆_菌菇三鲜水饺/480g</v>
@@ -4792,7 +4792,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B43" t="str">
         <v>魔芋羽衣甘蓝水饺480g</v>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B44" t="str">
         <v>思念放心饺猪肉荠菜水饺</v>
@@ -4920,10 +4920,10 @@
         <v>立柜</v>
       </c>
       <c r="L44" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="M44" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="N44" t="str">
         <v>主陈列</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B45" t="str">
         <v>【真值】披萨奥尔良风味鸡肉味200克</v>
@@ -5024,7 +5024,7 @@
         <v>立柜3m-柜9</v>
       </c>
       <c r="M45" t="str">
-        <v>第3层</v>
+        <v>第4层</v>
       </c>
       <c r="N45" t="str">
         <v>主陈列</v>
@@ -5095,7 +5095,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B46" t="str">
         <v>【真值】披萨精品榴莲芝士180g</v>
@@ -5122,10 +5122,10 @@
         <v>立柜</v>
       </c>
       <c r="L46" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="M46" t="str">
-        <v>第4层</v>
+        <v>第5层</v>
       </c>
       <c r="N46" t="str">
         <v>主陈列</v>
@@ -5196,7 +5196,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B47" t="str">
         <v>【真值】披萨黑椒牛肉风味200g</v>
@@ -5223,10 +5223,10 @@
         <v>立柜</v>
       </c>
       <c r="L47" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="M47" t="str">
-        <v>第4层</v>
+        <v>第5层</v>
       </c>
       <c r="N47" t="str">
         <v>主陈列</v>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B48" t="str">
         <v>【真值】披萨芝士培根风味200g</v>
@@ -5321,34 +5321,34 @@
         <v>速食披萨</v>
       </c>
       <c r="K48" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L48" t="str">
-        <v>立柜3m-柜9</v>
+        <v>卧柜1886mm-柜5</v>
       </c>
       <c r="M48" t="str">
-        <v>第5层</v>
+        <v>分区1</v>
       </c>
       <c r="N48" t="str">
         <v>主陈列</v>
       </c>
       <c r="O48">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P48">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="Q48">
         <v>180</v>
       </c>
       <c r="R48">
-        <v>6</v>
+        <v>294</v>
       </c>
       <c r="S48">
-        <v>6</v>
+        <v>294</v>
       </c>
       <c r="T48">
-        <v>6</v>
+        <v>294</v>
       </c>
       <c r="U48">
         <v>30</v>
@@ -5378,19 +5378,19 @@
         <v>101.3</v>
       </c>
       <c r="AD48">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AE48">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AF48">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>28.35</v>
+        <v>0</v>
       </c>
       <c r="AH48">
-        <v>14.175</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="str">
         <v>是</v>
@@ -5398,7 +5398,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B49" t="str">
         <v>思念-黑芝麻汤圆455g</v>
@@ -5425,7 +5425,7 @@
         <v>卧柜</v>
       </c>
       <c r="L49" t="str">
-        <v>卧柜2000mm-柜4</v>
+        <v>卧柜2505mm-柜1</v>
       </c>
       <c r="M49" t="str">
         <v>分区1</v>
@@ -5437,19 +5437,19 @@
         <v>1</v>
       </c>
       <c r="P49">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="Q49">
         <v>220</v>
       </c>
       <c r="R49">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="S49">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="T49">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="U49">
         <v>20</v>
@@ -5479,7 +5479,7 @@
         <v>4.4</v>
       </c>
       <c r="AD49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE49">
         <v>20</v>
@@ -5499,7 +5499,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B50" t="str">
         <v>思念大黄米黑芝麻汤圆454g</v>
@@ -5526,7 +5526,7 @@
         <v>卧柜</v>
       </c>
       <c r="L50" t="str">
-        <v>卧柜2000mm-柜4</v>
+        <v>卧柜2505mm-柜1</v>
       </c>
       <c r="M50" t="str">
         <v>分区1</v>
@@ -5538,19 +5538,19 @@
         <v>1</v>
       </c>
       <c r="P50">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q50">
         <v>265</v>
       </c>
       <c r="R50">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="S50">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="T50">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="U50">
         <v>20</v>
@@ -5580,7 +5580,7 @@
         <v>9.3</v>
       </c>
       <c r="AD50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE50">
         <v>20</v>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B51" t="str">
         <v>冷冻食材_潮汕风味牛肉丸/160g</v>
@@ -5627,10 +5627,10 @@
         <v>立柜</v>
       </c>
       <c r="L51" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="M51" t="str">
-        <v>第4层</v>
+        <v>第5层</v>
       </c>
       <c r="N51" t="str">
         <v>主陈列</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B52" t="str">
         <v>冷冻食材_包心鱼丸/160g(shg)</v>
@@ -5728,7 +5728,7 @@
         <v>卧柜</v>
       </c>
       <c r="L52" t="str">
-        <v>卧柜2500mm-柜1</v>
+        <v>卧柜2505mm-柜2</v>
       </c>
       <c r="M52" t="str">
         <v>分区1</v>
@@ -5740,19 +5740,19 @@
         <v>9</v>
       </c>
       <c r="P52">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q52">
         <v>185</v>
       </c>
       <c r="R52">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="S52">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="T52">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="U52">
         <v>40</v>
@@ -5782,7 +5782,7 @@
         <v>137.4</v>
       </c>
       <c r="AD52">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AE52">
         <v>40</v>
@@ -5802,7 +5802,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B53" t="str">
         <v>青虾滑95% 150g</v>
@@ -5829,7 +5829,7 @@
         <v>卧柜</v>
       </c>
       <c r="L53" t="str">
-        <v>卧柜2500mm-柜1</v>
+        <v>卧柜2505mm-柜2</v>
       </c>
       <c r="M53" t="str">
         <v>分区1</v>
@@ -5841,19 +5841,19 @@
         <v>1</v>
       </c>
       <c r="P53">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="Q53">
         <v>240</v>
       </c>
       <c r="R53">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="S53">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="T53">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="U53">
         <v>30</v>
@@ -5883,7 +5883,7 @@
         <v>45.5</v>
       </c>
       <c r="AD53">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE53">
         <v>30</v>
@@ -5903,7 +5903,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B54" t="str">
         <v>宏宝来俄式大脆筒牛奶味100g</v>
@@ -5930,7 +5930,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L54" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="M54" t="str">
         <v>分区2</v>
@@ -5942,19 +5942,19 @@
         <v>1</v>
       </c>
       <c r="P54">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="Q54">
         <v>320</v>
       </c>
       <c r="R54">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="S54">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="T54">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="U54">
         <v>20</v>
@@ -5984,19 +5984,19 @@
         <v>2.1</v>
       </c>
       <c r="AD54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE54">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AF54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="AH54">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="str">
         <v>是</v>
@@ -6004,7 +6004,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B55" t="str">
         <v>宏宝莱老冰棍80g</v>
@@ -6031,7 +6031,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L55" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="M55" t="str">
         <v>分区1</v>
@@ -6043,19 +6043,19 @@
         <v>1</v>
       </c>
       <c r="P55">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="Q55">
         <v>200</v>
       </c>
       <c r="R55">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="S55">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="T55">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="U55">
         <v>50</v>
@@ -6085,7 +6085,7 @@
         <v>3.8</v>
       </c>
       <c r="AD55">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AE55">
         <v>50</v>
@@ -6105,7 +6105,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B56" t="str">
         <v>蒙牛随变转巧克力雪糕65g</v>
@@ -6132,7 +6132,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L56" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="M56" t="str">
         <v>分区1</v>
@@ -6144,19 +6144,19 @@
         <v>1</v>
       </c>
       <c r="P56">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="Q56">
         <v>210</v>
       </c>
       <c r="R56">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="S56">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="T56">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="U56">
         <v>40</v>
@@ -6186,7 +6186,7 @@
         <v>4.3</v>
       </c>
       <c r="AD56">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE56">
         <v>40</v>
@@ -6206,7 +6206,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B57" t="str">
         <v>伊利巧脆棒雪糕75g</v>
@@ -6233,7 +6233,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L57" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="M57" t="str">
         <v>分区1</v>
@@ -6245,19 +6245,19 @@
         <v>1</v>
       </c>
       <c r="P57">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="Q57">
         <v>190</v>
       </c>
       <c r="R57">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="S57">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="T57">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="U57">
         <v>40</v>
@@ -6287,7 +6287,7 @@
         <v>4.4</v>
       </c>
       <c r="AD57">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE57">
         <v>40</v>
@@ -6307,7 +6307,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B58" t="str">
         <v>伊利大布丁60g</v>
@@ -6334,7 +6334,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L58" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="M58" t="str">
         <v>分区1</v>
@@ -6346,19 +6346,19 @@
         <v>1</v>
       </c>
       <c r="P58">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="Q58">
         <v>200</v>
       </c>
       <c r="R58">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="S58">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="T58">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="U58">
         <v>40</v>
@@ -6388,7 +6388,7 @@
         <v>5</v>
       </c>
       <c r="AD58">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AE58">
         <v>40</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B59" t="str">
         <v>酷企鹅食用冰杯160g</v>
@@ -6435,7 +6435,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L59" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="M59" t="str">
         <v>分区1</v>
@@ -6509,7 +6509,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B60" t="str">
         <v>上上鲜 绿色心情绿莎莎雪糕70g</v>
@@ -6536,7 +6536,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L60" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="M60" t="str">
         <v>分区1</v>
@@ -6548,19 +6548,19 @@
         <v>1</v>
       </c>
       <c r="P60">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="Q60">
         <v>200</v>
       </c>
       <c r="R60">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="S60">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="T60">
-        <v>192</v>
+        <v>260</v>
       </c>
       <c r="U60">
         <v>40</v>
@@ -6590,7 +6590,7 @@
         <v>6.5</v>
       </c>
       <c r="AD60">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AE60">
         <v>40</v>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B61" t="str">
         <v>伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g</v>
@@ -6637,7 +6637,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L61" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="M61" t="str">
         <v>分区1</v>
@@ -6649,19 +6649,19 @@
         <v>1</v>
       </c>
       <c r="P61">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="Q61">
         <v>190</v>
       </c>
       <c r="R61">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="S61">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="T61">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="U61">
         <v>16</v>
@@ -6691,7 +6691,7 @@
         <v>6.7</v>
       </c>
       <c r="AD61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE61">
         <v>16</v>
@@ -6711,7 +6711,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B62" t="str">
         <v>和路雪绿舌头54g</v>
@@ -6806,7 +6806,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B63" t="str">
         <v>雀巢8次方巧克力香草味84g</v>
@@ -6901,7 +6901,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B64" t="str">
         <v>和路雪可爱多香草67g</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B65" t="str">
         <v>小金条无核榴莲肉100g</v>
@@ -7091,7 +7091,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B66" t="str">
         <v>伊利6重巧巧70g</v>
@@ -7186,7 +7186,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B67" t="str">
         <v>【真值】芝士鸡肉卷奥尔良味120g</v>
@@ -7213,7 +7213,7 @@
         <v>卧柜</v>
       </c>
       <c r="L67" t="str">
-        <v>卧柜2000mm-柜4</v>
+        <v>卧柜2505mm-柜1</v>
       </c>
       <c r="M67" t="str">
         <v>分区1</v>
@@ -7222,22 +7222,22 @@
         <v>主陈列</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P67">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="Q67">
         <v>200</v>
       </c>
       <c r="R67">
-        <v>400</v>
+        <v>726</v>
       </c>
       <c r="S67">
-        <v>400</v>
+        <v>726</v>
       </c>
       <c r="T67">
-        <v>400</v>
+        <v>726</v>
       </c>
       <c r="U67">
         <v>40</v>
@@ -7267,7 +7267,7 @@
         <v>25.8</v>
       </c>
       <c r="AD67">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="AE67">
         <v>40</v>
@@ -7287,7 +7287,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B68" t="str">
         <v>【真值】芝士牛肉卷黑胡椒味120g</v>
@@ -7314,7 +7314,7 @@
         <v>卧柜</v>
       </c>
       <c r="L68" t="str">
-        <v>卧柜2000mm-柜4</v>
+        <v>卧柜2505mm-柜1</v>
       </c>
       <c r="M68" t="str">
         <v>分区1</v>
@@ -7326,19 +7326,19 @@
         <v>1</v>
       </c>
       <c r="P68">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="Q68">
         <v>200</v>
       </c>
       <c r="R68">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="S68">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="T68">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="U68">
         <v>40</v>
@@ -7368,7 +7368,7 @@
         <v>49.2</v>
       </c>
       <c r="AD68">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AE68">
         <v>40</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B69" t="str">
         <v>【真值】香脆小酥肉原味800g</v>
@@ -7415,7 +7415,7 @@
         <v>卧柜</v>
       </c>
       <c r="L69" t="str">
-        <v>卧柜2500mm-柜2</v>
+        <v>卧柜2505mm-柜3</v>
       </c>
       <c r="M69" t="str">
         <v>分区1</v>
@@ -7424,22 +7424,22 @@
         <v>主陈列</v>
       </c>
       <c r="O69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P69">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q69">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="R69">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="S69">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="T69">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="U69">
         <v>10</v>
@@ -7469,7 +7469,7 @@
         <v>16.5</v>
       </c>
       <c r="AD69">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE69">
         <v>10</v>
@@ -7489,7 +7489,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B70" t="str">
         <v>台式鸡排400g</v>
@@ -7516,7 +7516,7 @@
         <v>卧柜</v>
       </c>
       <c r="L70" t="str">
-        <v>卧柜2500mm-柜2</v>
+        <v>卧柜2505mm-柜3</v>
       </c>
       <c r="M70" t="str">
         <v>分区1</v>
@@ -7528,19 +7528,19 @@
         <v>1</v>
       </c>
       <c r="P70">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="Q70">
         <v>220</v>
       </c>
       <c r="R70">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="S70">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="T70">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="U70">
         <v>15</v>
@@ -7570,7 +7570,7 @@
         <v>32.6</v>
       </c>
       <c r="AD70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE70">
         <v>15</v>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B71" t="str">
         <v>玉米布丁酥400g</v>
@@ -7617,7 +7617,7 @@
         <v>卧柜</v>
       </c>
       <c r="L71" t="str">
-        <v>卧柜2500mm-柜2</v>
+        <v>卧柜2505mm-柜3</v>
       </c>
       <c r="M71" t="str">
         <v>分区1</v>
@@ -7629,19 +7629,19 @@
         <v>1</v>
       </c>
       <c r="P71">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q71">
         <v>240</v>
       </c>
       <c r="R71">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="S71">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="T71">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U71">
         <v>15</v>
@@ -7691,7 +7691,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B72" t="str">
         <v>美好小酥肉800g</v>
@@ -7800,7 +7800,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M53"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7845,7 +7845,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>酥皮牛肉馅饼500g</v>
@@ -7857,7 +7857,7 @@
         <v>B</v>
       </c>
       <c r="E2" t="str">
-        <v>卧柜2500mm-柜1</v>
+        <v>卧柜2505mm-柜1</v>
       </c>
       <c r="F2" t="str">
         <v>分区2</v>
@@ -7880,7 +7880,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g</v>
@@ -7892,7 +7892,7 @@
         <v>C</v>
       </c>
       <c r="E3" t="str">
-        <v>卧柜2500mm-柜2</v>
+        <v>卧柜2505mm-柜2</v>
       </c>
       <c r="F3" t="str">
         <v>分区2</v>
@@ -7915,7 +7915,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>酥皮香菇猪肉馅饼500g</v>
@@ -7927,7 +7927,7 @@
         <v>C</v>
       </c>
       <c r="E4" t="str">
-        <v>卧柜2000mm-柜4</v>
+        <v>卧柜2505mm-柜4</v>
       </c>
       <c r="F4" t="str">
         <v>分区2</v>
@@ -7950,7 +7950,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>纸皮韭菜盒子280g</v>
@@ -7985,7 +7985,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>老上海葱油饼900g</v>
@@ -8020,7 +8020,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>毛肚/200g</v>
@@ -8055,7 +8055,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>火锅三宝/450g（毛肚+千层肚+鸭肠）</v>
@@ -8067,10 +8067,10 @@
         <v>D</v>
       </c>
       <c r="E8" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="F8" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="G8">
         <v>12</v>
@@ -8090,7 +8090,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>冰鲜鸭肠/200g</v>
@@ -8125,7 +8125,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
         <v>【真值】大个爆汁鲜肉包800g</v>
@@ -8137,7 +8137,7 @@
         <v>B</v>
       </c>
       <c r="E10" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="F10" t="str">
         <v>第3层</v>
@@ -8160,7 +8160,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
         <v>【真值】大个三鲜青菜包800g</v>
@@ -8195,7 +8195,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
         <v>麻辣小龙虾1000g</v>
@@ -8207,7 +8207,7 @@
         <v>C</v>
       </c>
       <c r="E12" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="F12" t="str">
         <v>第4层</v>
@@ -8230,7 +8230,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
         <v>番茄肉酱意大利面280g</v>
@@ -8242,10 +8242,10 @@
         <v>A</v>
       </c>
       <c r="E13" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="F13" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="G13">
         <v>36</v>
@@ -8265,7 +8265,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>【真值】纸皮烧麦蛋黄味240g</v>
@@ -8277,10 +8277,10 @@
         <v>A</v>
       </c>
       <c r="E14" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="F14" t="str">
-        <v>第2层</v>
+        <v>第1层</v>
       </c>
       <c r="G14">
         <v>48</v>
@@ -8300,7 +8300,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>【真值】纸皮烧麦鲜肉味240g</v>
@@ -8312,10 +8312,10 @@
         <v>A</v>
       </c>
       <c r="E15" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="F15" t="str">
-        <v>第3层</v>
+        <v>第4层</v>
       </c>
       <c r="G15">
         <v>48</v>
@@ -8335,7 +8335,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>【真值】纸皮烧麦香菇味240g</v>
@@ -8347,7 +8347,7 @@
         <v>A</v>
       </c>
       <c r="E16" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="F16" t="str">
         <v>第1层</v>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>【真好】乌米三丁纸皮烧麦240g</v>
@@ -8382,10 +8382,10 @@
         <v>B</v>
       </c>
       <c r="E17" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="F17" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="G17">
         <v>48</v>
@@ -8405,7 +8405,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>【真好】黑猪肉梅干菜纸皮烧麦240g</v>
@@ -8440,7 +8440,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>【真好】黑松露纸皮烧麦240g</v>
@@ -8475,7 +8475,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>鸡胸肉/400g</v>
@@ -8487,10 +8487,10 @@
         <v>C</v>
       </c>
       <c r="E20" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="F20" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="G20">
         <v>25</v>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>安格斯牛排150g</v>
@@ -8522,30 +8522,30 @@
         <v>D</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>卧柜1886mm-柜5</v>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="G21">
         <v>40</v>
       </c>
       <c r="H21">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="I21">
         <v>0.7956</v>
       </c>
       <c r="J21">
-        <v>31.824</v>
+        <v>3.1824</v>
       </c>
       <c r="K21">
-        <v>15.912</v>
+        <v>1.5912</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>潮香村眼肉牛排3片装</v>
@@ -8557,10 +8557,10 @@
         <v>D</v>
       </c>
       <c r="E22" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="F22" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="G22">
         <v>12</v>
@@ -8580,7 +8580,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>冷冻鸡翅根/400g</v>
@@ -8615,7 +8615,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B24" t="str">
         <v>鸡爪/400g</v>
@@ -8650,7 +8650,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B25" t="str">
         <v>抽肠青虾仁150g</v>
@@ -8662,30 +8662,30 @@
         <v>C</v>
       </c>
       <c r="E25" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="F25" t="str">
-        <v>第4层</v>
+        <v>第5层</v>
       </c>
       <c r="G25">
         <v>30</v>
       </c>
       <c r="H25">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I25">
         <v>1.4094</v>
       </c>
       <c r="J25">
-        <v>38.0538</v>
+        <v>40.8726</v>
       </c>
       <c r="K25">
-        <v>19.0269</v>
+        <v>20.4363</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B26" t="str">
         <v>黑鱼片250g</v>
@@ -8697,7 +8697,7 @@
         <v>D</v>
       </c>
       <c r="E26" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="F26" t="str">
         <v>第5层</v>
@@ -8706,21 +8706,21 @@
         <v>25</v>
       </c>
       <c r="H26">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I26">
         <v>0.741</v>
       </c>
       <c r="J26">
-        <v>11.115</v>
+        <v>16.302</v>
       </c>
       <c r="K26">
-        <v>5.5575</v>
+        <v>8.151</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B27" t="str">
         <v>整虾/冷冻南美白虾250g</v>
@@ -8755,7 +8755,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B28" t="str">
         <v>带鱼段400g</v>
@@ -8790,7 +8790,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
         <v>双色开花馒头（紫薯味+南瓜味）360g</v>
@@ -8802,10 +8802,10 @@
         <v>B</v>
       </c>
       <c r="E29" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="F29" t="str">
-        <v>第1层</v>
+        <v>第2层</v>
       </c>
       <c r="G29">
         <v>24</v>
@@ -8825,7 +8825,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
         <v>手作奶香黄油开花馒头360g</v>
@@ -8837,10 +8837,10 @@
         <v>B</v>
       </c>
       <c r="E30" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="F30" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="G30">
         <v>24</v>
@@ -8860,7 +8860,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
         <v>生活馆_料多多薯香乳酪包/400g</v>
@@ -8895,7 +8895,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
         <v>鲜奶馒头300g</v>
@@ -8930,7 +8930,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
         <v>皓月新西兰羔羊卷WMT/450g</v>
@@ -8942,30 +8942,30 @@
         <v>D</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>第2层</v>
       </c>
       <c r="G33">
         <v>15</v>
       </c>
       <c r="H33">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>1.863</v>
       </c>
       <c r="J33">
-        <v>27.945</v>
+        <v>18.63</v>
       </c>
       <c r="K33">
-        <v>13.9725</v>
+        <v>9.315</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
         <v>原切肥羊卷300g</v>
@@ -9000,7 +9000,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
         <v>【真好】黑猪肉爆汁烤肠原味400g</v>
@@ -9012,10 +9012,10 @@
         <v>C</v>
       </c>
       <c r="E35" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="F35" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="G35">
         <v>20</v>
@@ -9035,7 +9035,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B36" t="str">
         <v>肉馅芹菜饺480g（两袋仅15.8元）</v>
@@ -9047,30 +9047,30 @@
         <v>B</v>
       </c>
       <c r="E36" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="F36" t="str">
-        <v>第1层</v>
+        <v>第4层</v>
       </c>
       <c r="G36">
         <v>20</v>
       </c>
       <c r="H36">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I36">
         <v>2.709</v>
       </c>
       <c r="J36">
-        <v>51.471</v>
+        <v>46.053</v>
       </c>
       <c r="K36">
-        <v>25.7355</v>
+        <v>23.0265</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B37" t="str">
         <v>荠菜笋丁鸡胸肉水饺480g</v>
@@ -9082,30 +9082,30 @@
         <v>B</v>
       </c>
       <c r="E37" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="F37" t="str">
-        <v>第1层</v>
+        <v>第2层</v>
       </c>
       <c r="G37">
         <v>20</v>
       </c>
       <c r="H37">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I37">
         <v>3.069</v>
       </c>
       <c r="J37">
-        <v>58.311</v>
+        <v>52.173</v>
       </c>
       <c r="K37">
-        <v>29.1555</v>
+        <v>26.0865</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B38" t="str">
         <v>肉馅玉米饺480g（两袋仅15.8元）</v>
@@ -9117,10 +9117,10 @@
         <v>B</v>
       </c>
       <c r="E38" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="F38" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="G38">
         <v>20</v>
@@ -9140,7 +9140,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B39" t="str">
         <v>生活馆_鲜肉小馄饨/++/512g</v>
@@ -9152,10 +9152,10 @@
         <v>B</v>
       </c>
       <c r="E39" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="F39" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="G39">
         <v>18</v>
@@ -9175,7 +9175,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B40" t="str">
         <v>生活馆_菌菇三鲜水饺/480g</v>
@@ -9210,7 +9210,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B41" t="str">
         <v>魔芋羽衣甘蓝水饺480g</v>
@@ -9245,7 +9245,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B42" t="str">
         <v>思念放心饺猪肉荠菜水饺</v>
@@ -9257,10 +9257,10 @@
         <v>C</v>
       </c>
       <c r="E42" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="F42" t="str">
-        <v>第2层</v>
+        <v>第3层</v>
       </c>
       <c r="G42">
         <v>12</v>
@@ -9280,7 +9280,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B43" t="str">
         <v>【真值】披萨奥尔良风味鸡肉味200克</v>
@@ -9295,7 +9295,7 @@
         <v>立柜3m-柜9</v>
       </c>
       <c r="F43" t="str">
-        <v>第3层</v>
+        <v>第4层</v>
       </c>
       <c r="G43">
         <v>30</v>
@@ -9315,7 +9315,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B44" t="str">
         <v>【真值】披萨精品榴莲芝士180g</v>
@@ -9327,10 +9327,10 @@
         <v>B</v>
       </c>
       <c r="E44" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="F44" t="str">
-        <v>第4层</v>
+        <v>第5层</v>
       </c>
       <c r="G44">
         <v>30</v>
@@ -9350,7 +9350,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B45" t="str">
         <v>【真值】披萨黑椒牛肉风味200g</v>
@@ -9362,10 +9362,10 @@
         <v>B</v>
       </c>
       <c r="E45" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="F45" t="str">
-        <v>第4层</v>
+        <v>第5层</v>
       </c>
       <c r="G45">
         <v>30</v>
@@ -9385,16 +9385,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B46" t="str">
-        <v>【真值】披萨芝士培根风味200g</v>
+        <v>冷冻食材_潮汕风味牛肉丸/160g</v>
       </c>
       <c r="C46" t="str">
-        <v>6978425420014</v>
+        <v>6923365101516</v>
       </c>
       <c r="D46" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E46" t="str">
         <v>立柜3m-柜9</v>
@@ -9403,135 +9403,135 @@
         <v>第5层</v>
       </c>
       <c r="G46">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H46">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I46">
-        <v>1.134</v>
+        <v>1.0036</v>
       </c>
       <c r="J46">
-        <v>28.35</v>
+        <v>32.1152</v>
       </c>
       <c r="K46">
-        <v>14.175</v>
+        <v>16.0576</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B47" t="str">
-        <v>冷冻食材_潮汕风味牛肉丸/160g</v>
+        <v>酷企鹅食用冰杯160g</v>
       </c>
       <c r="C47" t="str">
-        <v>6923365101516</v>
+        <v>6977602190221</v>
       </c>
       <c r="D47" t="str">
         <v>A</v>
       </c>
       <c r="E47" t="str">
-        <v>立柜3m-柜8</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="F47" t="str">
-        <v>第4层</v>
+        <v>分区1</v>
       </c>
       <c r="G47">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H47">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>1.0036</v>
+        <v>1.04</v>
       </c>
       <c r="J47">
-        <v>32.1152</v>
+        <v>3.12</v>
       </c>
       <c r="K47">
-        <v>16.0576</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B48" t="str">
-        <v>宏宝来俄式大脆筒牛奶味100g</v>
+        <v>和路雪绿舌头54g</v>
       </c>
       <c r="C48" t="str">
-        <v>6920858270995</v>
+        <v>6909493800453</v>
       </c>
       <c r="D48" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E48" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v/>
       </c>
       <c r="F48" t="str">
-        <v>分区2</v>
+        <v/>
       </c>
       <c r="G48">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="I48">
-        <v>1.44</v>
+        <v>0.2888</v>
       </c>
       <c r="J48">
-        <v>5.76</v>
+        <v>10.3968</v>
       </c>
       <c r="K48">
-        <v>2.88</v>
+        <v>5.1984</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B49" t="str">
-        <v>酷企鹅食用冰杯160g</v>
+        <v>雀巢8次方巧克力香草味84g</v>
       </c>
       <c r="C49" t="str">
-        <v>6977602190221</v>
+        <v>6918551807884</v>
       </c>
       <c r="D49" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="E49" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v/>
       </c>
       <c r="F49" t="str">
-        <v>分区1</v>
+        <v/>
       </c>
       <c r="G49">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I49">
-        <v>1.04</v>
+        <v>0.2721</v>
       </c>
       <c r="J49">
-        <v>3.12</v>
+        <v>4.8978</v>
       </c>
       <c r="K49">
-        <v>1.56</v>
+        <v>2.4489</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B50" t="str">
-        <v>和路雪绿舌头54g</v>
+        <v>和路雪可爱多香草67g</v>
       </c>
       <c r="C50" t="str">
-        <v>6909493800453</v>
+        <v>6909493401032</v>
       </c>
       <c r="D50" t="str">
         <v>B</v>
@@ -9543,33 +9543,33 @@
         <v/>
       </c>
       <c r="G50">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H50">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I50">
-        <v>0.2888</v>
+        <v>0.558</v>
       </c>
       <c r="J50">
-        <v>10.3968</v>
+        <v>13.392</v>
       </c>
       <c r="K50">
-        <v>5.1984</v>
+        <v>6.696</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B51" t="str">
-        <v>雀巢8次方巧克力香草味84g</v>
+        <v>小金条无核榴莲肉100g</v>
       </c>
       <c r="C51" t="str">
-        <v>6918551807884</v>
+        <v>6977480896154</v>
       </c>
       <c r="D51" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -9578,33 +9578,33 @@
         <v/>
       </c>
       <c r="G51">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H51">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="I51">
-        <v>0.2721</v>
+        <v>0.3776</v>
       </c>
       <c r="J51">
-        <v>4.8978</v>
+        <v>22.656</v>
       </c>
       <c r="K51">
-        <v>2.4489</v>
+        <v>11.328</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B52" t="str">
-        <v>和路雪可爱多香草67g</v>
+        <v>伊利6重巧巧70g</v>
       </c>
       <c r="C52" t="str">
-        <v>6909493401032</v>
+        <v>6907992827353</v>
       </c>
       <c r="D52" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -9613,30 +9613,30 @@
         <v/>
       </c>
       <c r="G52">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H52">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I52">
-        <v>0.558</v>
+        <v>0.275</v>
       </c>
       <c r="J52">
-        <v>13.392</v>
+        <v>9.625</v>
       </c>
       <c r="K52">
-        <v>6.696</v>
+        <v>4.8125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B53" t="str">
-        <v>小金条无核榴莲肉100g</v>
+        <v>美好小酥肉800g</v>
       </c>
       <c r="C53" t="str">
-        <v>6977480896154</v>
+        <v>6971938880948</v>
       </c>
       <c r="D53" t="str">
         <v>未评级</v>
@@ -9648,102 +9648,32 @@
         <v/>
       </c>
       <c r="G53">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H53">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I53">
-        <v>0.3776</v>
+        <v>4.725</v>
       </c>
       <c r="J53">
-        <v>22.656</v>
+        <v>47.25</v>
       </c>
       <c r="K53">
-        <v>11.328</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B54" t="str">
-        <v>伊利6重巧巧70g</v>
-      </c>
-      <c r="C54" t="str">
-        <v>6907992827353</v>
-      </c>
-      <c r="D54" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-      <c r="F54" t="str">
-        <v/>
-      </c>
-      <c r="G54">
-        <v>35</v>
-      </c>
-      <c r="H54">
-        <v>35</v>
-      </c>
-      <c r="I54">
-        <v>0.275</v>
-      </c>
-      <c r="J54">
-        <v>9.625</v>
-      </c>
-      <c r="K54">
-        <v>4.8125</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B55" t="str">
-        <v>美好小酥肉800g</v>
-      </c>
-      <c r="C55" t="str">
-        <v>6971938880948</v>
-      </c>
-      <c r="D55" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="E55" t="str">
-        <v/>
-      </c>
-      <c r="F55" t="str">
-        <v/>
-      </c>
-      <c r="G55">
-        <v>10</v>
-      </c>
-      <c r="H55">
-        <v>10</v>
-      </c>
-      <c r="I55">
-        <v>4.725</v>
-      </c>
-      <c r="J55">
-        <v>47.25</v>
-      </c>
-      <c r="K55">
         <v>23.625</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M55"/>
+  <autoFilter ref="A1:M53"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M53"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9791,7 +9721,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>卧柜</v>
@@ -9800,28 +9730,28 @@
         <v>卧柜</v>
       </c>
       <c r="D2" t="str">
-        <v>卧柜2500mm-柜1</v>
+        <v>卧柜2505mm-柜1</v>
       </c>
       <c r="E2" t="str">
         <v>分区1</v>
       </c>
       <c r="H2">
-        <v>1988</v>
+        <v>1942</v>
       </c>
       <c r="I2">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="K2">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="L2">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="M2" t="str">
-        <v>冷冻食材_包心鱼丸/160g(shg) 9列；青虾滑95% 150g 1列</v>
+        <v>思念-黑芝麻汤圆455g 1列；思念大黄米黑芝麻汤圆454g 1列；【真值】芝士鸡肉卷奥尔良味120g 6列；【真值】芝士牛肉卷黑胡椒味120g 1列</v>
       </c>
       <c r="N2" t="str">
         <v>正常使用</v>
@@ -9829,7 +9759,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>卧柜</v>
@@ -9838,25 +9768,25 @@
         <v>卧柜</v>
       </c>
       <c r="D3" t="str">
-        <v>卧柜2500mm-柜1</v>
+        <v>卧柜2505mm-柜1</v>
       </c>
       <c r="E3" t="str">
         <v>分区2</v>
       </c>
       <c r="H3">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="I3">
         <v>230</v>
       </c>
       <c r="J3">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="K3">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="L3">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M3" t="str">
         <v>酥皮牛肉馅饼500g 1列</v>
@@ -9867,7 +9797,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>卧柜</v>
@@ -9876,28 +9806,28 @@
         <v>卧柜</v>
       </c>
       <c r="D4" t="str">
-        <v>卧柜2500mm-柜2</v>
+        <v>卧柜2505mm-柜2</v>
       </c>
       <c r="E4" t="str">
         <v>分区1</v>
       </c>
       <c r="H4">
-        <v>1988</v>
+        <v>1942</v>
       </c>
       <c r="I4">
-        <v>1860</v>
+        <v>1905</v>
       </c>
       <c r="J4">
-        <v>128</v>
+        <v>37</v>
       </c>
       <c r="K4">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="L4">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="M4" t="str">
-        <v>【真值】香脆小酥肉原味800g 4列；台式鸡排400g 1列；玉米布丁酥400g 1列</v>
+        <v>冷冻食材_包心鱼丸/160g(shg) 9列；青虾滑95% 150g 1列</v>
       </c>
       <c r="N4" t="str">
         <v>正常使用</v>
@@ -9905,7 +9835,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>卧柜</v>
@@ -9914,25 +9844,25 @@
         <v>卧柜</v>
       </c>
       <c r="D5" t="str">
-        <v>卧柜2500mm-柜2</v>
+        <v>卧柜2505mm-柜2</v>
       </c>
       <c r="E5" t="str">
         <v>分区2</v>
       </c>
       <c r="H5">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="I5">
         <v>277.5</v>
       </c>
       <c r="J5">
-        <v>82.5</v>
+        <v>122.5</v>
       </c>
       <c r="K5">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="L5">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M5" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g 1列</v>
@@ -9943,7 +9873,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>卧柜</v>
@@ -9952,28 +9882,28 @@
         <v>卧柜</v>
       </c>
       <c r="D6" t="str">
-        <v>卧柜2500mm-柜3</v>
+        <v>卧柜2505mm-柜3</v>
       </c>
       <c r="E6" t="str">
         <v>分区1</v>
       </c>
       <c r="H6">
-        <v>1988</v>
+        <v>1942</v>
       </c>
       <c r="I6">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="J6">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="K6">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="L6">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="M6" t="str">
-        <v>冻榴莲500g 7列</v>
+        <v>【真值】香脆小酥肉原味800g 6列；台式鸡排400g 1列；玉米布丁酥400g 1列</v>
       </c>
       <c r="N6" t="str">
         <v>正常使用</v>
@@ -9981,7 +9911,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>卧柜</v>
@@ -9990,25 +9920,25 @@
         <v>卧柜</v>
       </c>
       <c r="D7" t="str">
-        <v>卧柜2500mm-柜3</v>
+        <v>卧柜2505mm-柜3</v>
       </c>
       <c r="E7" t="str">
         <v>分区2</v>
       </c>
       <c r="H7">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="I7">
         <v>250</v>
       </c>
       <c r="J7">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="K7">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="L7">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M7" t="str">
         <v>【真值】甄选黄油鸡蛋灌饼皮640g 1列</v>
@@ -10019,7 +9949,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>卧柜</v>
@@ -10028,28 +9958,28 @@
         <v>卧柜</v>
       </c>
       <c r="D8" t="str">
-        <v>卧柜2000mm-柜4</v>
+        <v>卧柜2505mm-柜4</v>
       </c>
       <c r="E8" t="str">
         <v>分区1</v>
       </c>
       <c r="H8">
-        <v>1488</v>
+        <v>1942</v>
       </c>
       <c r="I8">
-        <v>1485</v>
+        <v>1890</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="K8">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="L8">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="M8" t="str">
-        <v>思念-黑芝麻汤圆455g 1列；思念大黄米黑芝麻汤圆454g 1列；【真值】芝士鸡肉卷奥尔良味120g 4列；【真值】芝士牛肉卷黑胡椒味120g 1列</v>
+        <v>冻榴莲500g 7列</v>
       </c>
       <c r="N8" t="str">
         <v>正常使用</v>
@@ -10057,7 +9987,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>卧柜</v>
@@ -10066,25 +9996,25 @@
         <v>卧柜</v>
       </c>
       <c r="D9" t="str">
-        <v>卧柜2000mm-柜4</v>
+        <v>卧柜2505mm-柜4</v>
       </c>
       <c r="E9" t="str">
         <v>分区2</v>
       </c>
       <c r="H9">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="I9">
         <v>230</v>
       </c>
       <c r="J9">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="K9">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="L9">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M9" t="str">
         <v>酥皮香菇猪肉馅饼500g 1列</v>
@@ -10095,37 +10025,37 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C10" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D10" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>卧柜1886mm-柜5</v>
       </c>
       <c r="E10" t="str">
         <v>分区1</v>
       </c>
       <c r="H10">
-        <v>1386</v>
+        <v>1295</v>
       </c>
       <c r="I10">
-        <v>1290</v>
+        <v>1260</v>
       </c>
       <c r="J10">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="K10">
-        <v>697.5</v>
+        <v>719</v>
       </c>
       <c r="L10">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="M10" t="str">
-        <v>宏宝莱老冰棍80g 1列；蒙牛随变转巧克力雪糕65g 1列；伊利巧脆棒雪糕75g 1列；伊利大布丁60g 1列；酷企鹅食用冰杯160g 1列；上上鲜 绿色心情绿莎莎雪糕70g 1列；伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g 1列</v>
+        <v>【真值】披萨芝士培根风味200g 7列</v>
       </c>
       <c r="N10" t="str">
         <v>正常使用</v>
@@ -10133,37 +10063,37 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C11" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D11" t="str">
-        <v>冰淇淋柜1900mm-柜5</v>
+        <v>卧柜1886mm-柜5</v>
       </c>
       <c r="E11" t="str">
         <v>分区2</v>
       </c>
       <c r="H11">
-        <v>325</v>
+        <v>400</v>
       </c>
       <c r="I11">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="K11">
-        <v>697.5</v>
+        <v>719</v>
       </c>
       <c r="L11">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="M11" t="str">
-        <v>宏宝来俄式大脆筒牛奶味100g 1列</v>
+        <v>安格斯牛排150g 1列</v>
       </c>
       <c r="N11" t="str">
         <v>正常使用</v>
@@ -10171,37 +10101,37 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="C12" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="D12" t="str">
-        <v>立柜3m-柜6</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="E12" t="str">
-        <v>第1层</v>
+        <v>分区1</v>
       </c>
       <c r="H12">
-        <v>710</v>
+        <v>1295</v>
       </c>
       <c r="I12">
-        <v>660</v>
+        <v>1290</v>
       </c>
       <c r="J12">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>534</v>
+        <v>719</v>
       </c>
       <c r="L12">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="M12" t="str">
-        <v>番茄肉酱意大利面280g 3列</v>
+        <v>宏宝莱老冰棍80g 1列；蒙牛随变转巧克力雪糕65g 1列；伊利巧脆棒雪糕75g 1列；伊利大布丁60g 1列；酷企鹅食用冰杯160g 1列；上上鲜 绿色心情绿莎莎雪糕70g 1列；伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g 1列</v>
       </c>
       <c r="N12" t="str">
         <v>正常使用</v>
@@ -10209,37 +10139,37 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="C13" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="D13" t="str">
-        <v>立柜3m-柜6</v>
+        <v>冰淇淋柜1886mm-柜6</v>
       </c>
       <c r="E13" t="str">
-        <v>第2层</v>
+        <v>分区2</v>
       </c>
       <c r="H13">
-        <v>710</v>
+        <v>400</v>
       </c>
       <c r="I13">
-        <v>660</v>
+        <v>320</v>
       </c>
       <c r="J13">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K13">
-        <v>534</v>
+        <v>719</v>
       </c>
       <c r="L13">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="M13" t="str">
-        <v>【真值】纸皮烧麦蛋黄味240g 4列</v>
+        <v>宏宝来俄式大脆筒牛奶味100g 1列</v>
       </c>
       <c r="N13" t="str">
         <v>正常使用</v>
@@ -10247,7 +10177,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>立柜</v>
@@ -10256,19 +10186,19 @@
         <v>立柜</v>
       </c>
       <c r="D14" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="E14" t="str">
-        <v>第3层</v>
+        <v>第1层</v>
       </c>
       <c r="H14">
         <v>710</v>
       </c>
       <c r="I14">
-        <v>580</v>
+        <v>660</v>
       </c>
       <c r="J14">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="K14">
         <v>534</v>
@@ -10277,7 +10207,7 @@
         <v>250</v>
       </c>
       <c r="M14" t="str">
-        <v>【真值】大个爆汁鲜肉包800g 2列</v>
+        <v>【真值】纸皮烧麦蛋黄味240g 4列</v>
       </c>
       <c r="N14" t="str">
         <v>正常使用</v>
@@ -10285,7 +10215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>立柜</v>
@@ -10294,19 +10224,19 @@
         <v>立柜</v>
       </c>
       <c r="D15" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="E15" t="str">
-        <v>第4层</v>
+        <v>第2层</v>
       </c>
       <c r="H15">
         <v>710</v>
       </c>
       <c r="I15">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="J15">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="K15">
         <v>534</v>
@@ -10315,7 +10245,7 @@
         <v>250</v>
       </c>
       <c r="M15" t="str">
-        <v>麻辣小龙虾1000g 2列</v>
+        <v>皓月新西兰羔羊卷WMT/450g 3列</v>
       </c>
       <c r="N15" t="str">
         <v>正常使用</v>
@@ -10323,7 +10253,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>立柜</v>
@@ -10332,19 +10262,19 @@
         <v>立柜</v>
       </c>
       <c r="D16" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="E16" t="str">
-        <v>第5层</v>
+        <v>第3层</v>
       </c>
       <c r="H16">
         <v>710</v>
       </c>
       <c r="I16">
-        <v>630</v>
+        <v>580</v>
       </c>
       <c r="J16">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="K16">
         <v>534</v>
@@ -10353,7 +10283,7 @@
         <v>250</v>
       </c>
       <c r="M16" t="str">
-        <v>【真好】乌米三丁纸皮烧麦240g 3列</v>
+        <v>【真值】大个爆汁鲜肉包800g 2列</v>
       </c>
       <c r="N16" t="str">
         <v>正常使用</v>
@@ -10361,7 +10291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>立柜</v>
@@ -10370,19 +10300,19 @@
         <v>立柜</v>
       </c>
       <c r="D17" t="str">
-        <v>立柜3m-柜6</v>
+        <v>立柜3m-柜7</v>
       </c>
       <c r="E17" t="str">
-        <v>第6层</v>
+        <v>第4层</v>
       </c>
       <c r="H17">
         <v>710</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J17">
-        <v>710</v>
+        <v>210</v>
       </c>
       <c r="K17">
         <v>534</v>
@@ -10391,15 +10321,15 @@
         <v>250</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>麻辣小龙虾1000g 2列</v>
       </c>
       <c r="N17" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>立柜</v>
@@ -10411,16 +10341,16 @@
         <v>立柜3m-柜7</v>
       </c>
       <c r="E18" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="H18">
         <v>710</v>
       </c>
       <c r="I18">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="J18">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="K18">
         <v>534</v>
@@ -10429,7 +10359,7 @@
         <v>250</v>
       </c>
       <c r="M18" t="str">
-        <v>双色开花馒头（紫薯味+南瓜味）360g 3列</v>
+        <v>番茄肉酱意大利面280g 3列</v>
       </c>
       <c r="N18" t="str">
         <v>正常使用</v>
@@ -10437,7 +10367,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>立柜</v>
@@ -10449,16 +10379,16 @@
         <v>立柜3m-柜7</v>
       </c>
       <c r="E19" t="str">
-        <v>第2层</v>
+        <v>第6层</v>
       </c>
       <c r="H19">
         <v>710</v>
       </c>
       <c r="I19">
-        <v>595</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>115</v>
+        <v>710</v>
       </c>
       <c r="K19">
         <v>534</v>
@@ -10467,15 +10397,15 @@
         <v>250</v>
       </c>
       <c r="M19" t="str">
-        <v>鸡胸肉/400g 2列；潮香村眼肉牛排3片装 1列</v>
+        <v/>
       </c>
       <c r="N19" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>立柜</v>
@@ -10484,19 +10414,19 @@
         <v>立柜</v>
       </c>
       <c r="D20" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="E20" t="str">
-        <v>第3层</v>
+        <v>第1层</v>
       </c>
       <c r="H20">
         <v>710</v>
       </c>
       <c r="I20">
-        <v>660</v>
+        <v>630</v>
       </c>
       <c r="J20">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="K20">
         <v>534</v>
@@ -10505,7 +10435,7 @@
         <v>250</v>
       </c>
       <c r="M20" t="str">
-        <v>【真值】纸皮烧麦鲜肉味240g 4列</v>
+        <v>【真好】乌米三丁纸皮烧麦240g 3列</v>
       </c>
       <c r="N20" t="str">
         <v>正常使用</v>
@@ -10513,7 +10443,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>立柜</v>
@@ -10522,19 +10452,19 @@
         <v>立柜</v>
       </c>
       <c r="D21" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="E21" t="str">
-        <v>第4层</v>
+        <v>第2层</v>
       </c>
       <c r="H21">
         <v>710</v>
       </c>
       <c r="I21">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="J21">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="K21">
         <v>534</v>
@@ -10543,7 +10473,7 @@
         <v>250</v>
       </c>
       <c r="M21" t="str">
-        <v>抽肠青虾仁150g 2列</v>
+        <v>双色开花馒头（紫薯味+南瓜味）360g 3列</v>
       </c>
       <c r="N21" t="str">
         <v>正常使用</v>
@@ -10551,7 +10481,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>立柜</v>
@@ -10560,19 +10490,19 @@
         <v>立柜</v>
       </c>
       <c r="D22" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="E22" t="str">
-        <v>第5层</v>
+        <v>第3层</v>
       </c>
       <c r="H22">
         <v>710</v>
       </c>
       <c r="I22">
-        <v>570</v>
+        <v>595</v>
       </c>
       <c r="J22">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="K22">
         <v>534</v>
@@ -10581,7 +10511,7 @@
         <v>250</v>
       </c>
       <c r="M22" t="str">
-        <v>黑鱼片250g 3列</v>
+        <v>鸡胸肉/400g 2列；潮香村眼肉牛排3片装 1列</v>
       </c>
       <c r="N22" t="str">
         <v>正常使用</v>
@@ -10589,7 +10519,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>立柜</v>
@@ -10598,19 +10528,19 @@
         <v>立柜</v>
       </c>
       <c r="D23" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜8</v>
       </c>
       <c r="E23" t="str">
-        <v>第6层</v>
+        <v>第4层</v>
       </c>
       <c r="H23">
         <v>710</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="J23">
-        <v>710</v>
+        <v>50</v>
       </c>
       <c r="K23">
         <v>534</v>
@@ -10619,15 +10549,15 @@
         <v>250</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>【真值】纸皮烧麦鲜肉味240g 4列</v>
       </c>
       <c r="N23" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B24" t="str">
         <v>立柜</v>
@@ -10639,16 +10569,16 @@
         <v>立柜3m-柜8</v>
       </c>
       <c r="E24" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="H24">
         <v>710</v>
       </c>
       <c r="I24">
-        <v>660</v>
+        <v>465</v>
       </c>
       <c r="J24">
-        <v>50</v>
+        <v>245</v>
       </c>
       <c r="K24">
         <v>534</v>
@@ -10657,7 +10587,7 @@
         <v>250</v>
       </c>
       <c r="M24" t="str">
-        <v>【真值】纸皮烧麦香菇味240g 4列</v>
+        <v>抽肠青虾仁150g 1列；黑鱼片250g 1列</v>
       </c>
       <c r="N24" t="str">
         <v>正常使用</v>
@@ -10665,7 +10595,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B25" t="str">
         <v>立柜</v>
@@ -10677,16 +10607,16 @@
         <v>立柜3m-柜8</v>
       </c>
       <c r="E25" t="str">
-        <v>第2层</v>
+        <v>第6层</v>
       </c>
       <c r="H25">
         <v>710</v>
       </c>
       <c r="I25">
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>45</v>
+        <v>710</v>
       </c>
       <c r="K25">
         <v>534</v>
@@ -10695,15 +10625,15 @@
         <v>250</v>
       </c>
       <c r="M25" t="str">
-        <v>手作奶香黄油开花馒头360g 2列；思念放心饺猪肉荠菜水饺 1列</v>
+        <v/>
       </c>
       <c r="N25" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B26" t="str">
         <v>立柜</v>
@@ -10712,19 +10642,19 @@
         <v>立柜</v>
       </c>
       <c r="D26" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="E26" t="str">
-        <v>第3层</v>
+        <v>第1层</v>
       </c>
       <c r="H26">
         <v>710</v>
       </c>
       <c r="I26">
-        <v>540</v>
+        <v>660</v>
       </c>
       <c r="J26">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="K26">
         <v>534</v>
@@ -10733,7 +10663,7 @@
         <v>250</v>
       </c>
       <c r="M26" t="str">
-        <v>火锅三宝/450g（毛肚+千层肚+鸭肠） 3列</v>
+        <v>【真值】纸皮烧麦香菇味240g 4列</v>
       </c>
       <c r="N26" t="str">
         <v>正常使用</v>
@@ -10741,7 +10671,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B27" t="str">
         <v>立柜</v>
@@ -10750,19 +10680,19 @@
         <v>立柜</v>
       </c>
       <c r="D27" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="E27" t="str">
-        <v>第4层</v>
+        <v>第2层</v>
       </c>
       <c r="H27">
         <v>710</v>
       </c>
       <c r="I27">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="J27">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K27">
         <v>534</v>
@@ -10771,7 +10701,7 @@
         <v>250</v>
       </c>
       <c r="M27" t="str">
-        <v>冷冻食材_潮汕风味牛肉丸/160g 3列</v>
+        <v>火锅三宝/450g（毛肚+千层肚+鸭肠） 3列</v>
       </c>
       <c r="N27" t="str">
         <v>正常使用</v>
@@ -10779,7 +10709,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B28" t="str">
         <v>立柜</v>
@@ -10788,19 +10718,19 @@
         <v>立柜</v>
       </c>
       <c r="D28" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="E28" t="str">
-        <v>第5层</v>
+        <v>第3层</v>
       </c>
       <c r="H28">
         <v>710</v>
       </c>
       <c r="I28">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="J28">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K28">
         <v>534</v>
@@ -10809,7 +10739,7 @@
         <v>250</v>
       </c>
       <c r="M28" t="str">
-        <v>【真好】黑猪肉爆汁烤肠原味400g 3列</v>
+        <v>手作奶香黄油开花馒头360g 2列；思念放心饺猪肉荠菜水饺 1列</v>
       </c>
       <c r="N28" t="str">
         <v>正常使用</v>
@@ -10817,7 +10747,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
         <v>立柜</v>
@@ -10826,19 +10756,19 @@
         <v>立柜</v>
       </c>
       <c r="D29" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜9</v>
       </c>
       <c r="E29" t="str">
-        <v>第6层</v>
+        <v>第4层</v>
       </c>
       <c r="H29">
         <v>710</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="J29">
-        <v>710</v>
+        <v>170</v>
       </c>
       <c r="K29">
         <v>534</v>
@@ -10847,15 +10777,15 @@
         <v>250</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>【真值】披萨奥尔良风味鸡肉味200克 3列</v>
       </c>
       <c r="N29" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
         <v>立柜</v>
@@ -10867,16 +10797,16 @@
         <v>立柜3m-柜9</v>
       </c>
       <c r="E30" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="H30">
         <v>710</v>
       </c>
       <c r="I30">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="J30">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="K30">
         <v>534</v>
@@ -10885,7 +10815,7 @@
         <v>250</v>
       </c>
       <c r="M30" t="str">
-        <v>肉馅芹菜饺480g（两袋仅15.8元） 1列；荠菜笋丁鸡胸肉水饺480g 1列</v>
+        <v>冷冻食材_潮汕风味牛肉丸/160g 3列</v>
       </c>
       <c r="N30" t="str">
         <v>正常使用</v>
@@ -10893,7 +10823,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
         <v>立柜</v>
@@ -10905,16 +10835,16 @@
         <v>立柜3m-柜9</v>
       </c>
       <c r="E31" t="str">
-        <v>第2层</v>
+        <v>第6层</v>
       </c>
       <c r="H31">
         <v>710</v>
       </c>
       <c r="I31">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>85</v>
+        <v>710</v>
       </c>
       <c r="K31">
         <v>534</v>
@@ -10923,15 +10853,15 @@
         <v>250</v>
       </c>
       <c r="M31" t="str">
-        <v>肉馅玉米饺480g（两袋仅15.8元） 1列；生活馆_鲜肉小馄饨/++/512g 1列</v>
+        <v/>
       </c>
       <c r="N31" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
         <v>立柜</v>
@@ -10940,19 +10870,19 @@
         <v>立柜</v>
       </c>
       <c r="D32" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="E32" t="str">
-        <v>第3层</v>
+        <v>第1层</v>
       </c>
       <c r="H32">
         <v>710</v>
       </c>
       <c r="I32">
-        <v>540</v>
+        <v>675</v>
       </c>
       <c r="J32">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="K32">
         <v>534</v>
@@ -10961,7 +10891,7 @@
         <v>250</v>
       </c>
       <c r="M32" t="str">
-        <v>【真值】披萨奥尔良风味鸡肉味200克 3列</v>
+        <v>【真好】黑猪肉爆汁烤肠原味400g 3列</v>
       </c>
       <c r="N32" t="str">
         <v>正常使用</v>
@@ -10969,7 +10899,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
         <v>立柜</v>
@@ -10978,19 +10908,19 @@
         <v>立柜</v>
       </c>
       <c r="D33" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="E33" t="str">
-        <v>第4层</v>
+        <v>第2层</v>
       </c>
       <c r="H33">
         <v>710</v>
       </c>
       <c r="I33">
-        <v>540</v>
+        <v>620</v>
       </c>
       <c r="J33">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="K33">
         <v>534</v>
@@ -10999,7 +10929,7 @@
         <v>250</v>
       </c>
       <c r="M33" t="str">
-        <v>【真值】披萨精品榴莲芝士180g 2列；【真值】披萨黑椒牛肉风味200g 1列</v>
+        <v>荠菜笋丁鸡胸肉水饺480g 2列</v>
       </c>
       <c r="N33" t="str">
         <v>正常使用</v>
@@ -11007,7 +10937,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
         <v>立柜</v>
@@ -11016,19 +10946,19 @@
         <v>立柜</v>
       </c>
       <c r="D34" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="E34" t="str">
-        <v>第5层</v>
+        <v>第3层</v>
       </c>
       <c r="H34">
         <v>710</v>
       </c>
       <c r="I34">
-        <v>540</v>
+        <v>625</v>
       </c>
       <c r="J34">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="K34">
         <v>534</v>
@@ -11037,7 +10967,7 @@
         <v>250</v>
       </c>
       <c r="M34" t="str">
-        <v>【真值】披萨芝士培根风味200g 3列</v>
+        <v>肉馅玉米饺480g（两袋仅15.8元） 1列；生活馆_鲜肉小馄饨/++/512g 1列</v>
       </c>
       <c r="N34" t="str">
         <v>正常使用</v>
@@ -11045,7 +10975,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
         <v>立柜</v>
@@ -11054,19 +10984,19 @@
         <v>立柜</v>
       </c>
       <c r="D35" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜10</v>
       </c>
       <c r="E35" t="str">
-        <v>第6层</v>
+        <v>第4层</v>
       </c>
       <c r="H35">
         <v>710</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="J35">
-        <v>710</v>
+        <v>80</v>
       </c>
       <c r="K35">
         <v>534</v>
@@ -11075,23 +11005,99 @@
         <v>250</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>肉馅芹菜饺480g（两袋仅15.8元） 2列</v>
       </c>
       <c r="N35" t="str">
+        <v>正常使用</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B36" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C36" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D36" t="str">
+        <v>立柜3m-柜10</v>
+      </c>
+      <c r="E36" t="str">
+        <v>第5层</v>
+      </c>
+      <c r="H36">
+        <v>710</v>
+      </c>
+      <c r="I36">
+        <v>540</v>
+      </c>
+      <c r="J36">
+        <v>170</v>
+      </c>
+      <c r="K36">
+        <v>534</v>
+      </c>
+      <c r="L36">
+        <v>250</v>
+      </c>
+      <c r="M36" t="str">
+        <v>【真值】披萨精品榴莲芝士180g 2列；【真值】披萨黑椒牛肉风味200g 1列</v>
+      </c>
+      <c r="N36" t="str">
+        <v>正常使用</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B37" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C37" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D37" t="str">
+        <v>立柜3m-柜10</v>
+      </c>
+      <c r="E37" t="str">
+        <v>第6层</v>
+      </c>
+      <c r="H37">
+        <v>710</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>710</v>
+      </c>
+      <c r="K37">
+        <v>534</v>
+      </c>
+      <c r="L37">
+        <v>250</v>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
         <v>存储位</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N35"/>
+  <autoFilter ref="A1:N37"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N37"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11130,7 +11136,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>小于等于10%触发</v>
@@ -11165,7 +11171,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>小于等于10%触发</v>
@@ -11200,7 +11206,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>小于等于10%触发</v>
@@ -11235,7 +11241,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>小于等于10%触发</v>
@@ -11270,7 +11276,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>小于等于10%触发</v>
@@ -11305,7 +11311,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>小于等于10%触发</v>
@@ -11340,7 +11346,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>小于等于10%触发</v>
@@ -11375,7 +11381,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>小于等于10%触发</v>
@@ -11390,7 +11396,7 @@
         <v>D</v>
       </c>
       <c r="F9">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -11402,15 +11408,15 @@
         <v>冷冻食材</v>
       </c>
       <c r="J9" t="str">
-        <v>安格斯牛排150g</v>
+        <v>冷冻鸡翅根/400g</v>
       </c>
       <c r="K9" t="str">
-        <v>6926557320191</v>
+        <v>6970005561735</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
         <v>小于等于10%触发</v>
@@ -11425,7 +11431,7 @@
         <v>D</v>
       </c>
       <c r="F10">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -11437,15 +11443,15 @@
         <v>冷冻食材</v>
       </c>
       <c r="J10" t="str">
-        <v>冷冻鸡翅根/400g</v>
+        <v>鸡爪/400g</v>
       </c>
       <c r="K10" t="str">
-        <v>6970005561735</v>
+        <v>6970005561711</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
         <v>小于等于10%触发</v>
@@ -11460,7 +11466,7 @@
         <v>D</v>
       </c>
       <c r="F11">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -11469,18 +11475,18 @@
         <v>冷冻食材</v>
       </c>
       <c r="I11" t="str">
-        <v>冷冻食材</v>
+        <v>冷冻水产</v>
       </c>
       <c r="J11" t="str">
-        <v>鸡爪/400g</v>
+        <v>整虾/冷冻南美白虾250g</v>
       </c>
       <c r="K11" t="str">
-        <v>6970005561711</v>
+        <v>6971806122033</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
         <v>小于等于10%触发</v>
@@ -11495,7 +11501,7 @@
         <v>D</v>
       </c>
       <c r="F12">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -11507,15 +11513,15 @@
         <v>冷冻水产</v>
       </c>
       <c r="J12" t="str">
-        <v>整虾/冷冻南美白虾250g</v>
+        <v>带鱼段400g</v>
       </c>
       <c r="K12" t="str">
-        <v>6971806122033</v>
+        <v>6971806121982</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
         <v>小于等于10%触发</v>
@@ -11527,30 +11533,30 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E13" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="F13">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>冷冻食材</v>
+        <v>预制主食</v>
       </c>
       <c r="I13" t="str">
-        <v>冷冻水产</v>
+        <v>馒头发糕</v>
       </c>
       <c r="J13" t="str">
-        <v>带鱼段400g</v>
+        <v>生活馆_料多多薯香乳酪包/400g</v>
       </c>
       <c r="K13" t="str">
-        <v>6971806121982</v>
+        <v>6971997913342</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>小于等于10%触发</v>
@@ -11562,10 +11568,10 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E14" t="str">
-        <v>C</v>
+        <v>未评级</v>
       </c>
       <c r="F14">
-        <v>39</v>
+        <v>9999</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -11577,15 +11583,15 @@
         <v>馒头发糕</v>
       </c>
       <c r="J14" t="str">
-        <v>生活馆_料多多薯香乳酪包/400g</v>
+        <v>鲜奶馒头300g</v>
       </c>
       <c r="K14" t="str">
-        <v>6971997913342</v>
+        <v>6973560306940</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>小于等于10%触发</v>
@@ -11597,30 +11603,30 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E15" t="str">
-        <v>未评级</v>
+        <v>D</v>
       </c>
       <c r="F15">
-        <v>9999</v>
+        <v>61</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>预制主食</v>
+        <v>火锅食材</v>
       </c>
       <c r="I15" t="str">
-        <v>馒头发糕</v>
+        <v>牛羊肉卷</v>
       </c>
       <c r="J15" t="str">
-        <v>鲜奶馒头300g</v>
+        <v>原切肥羊卷300g</v>
       </c>
       <c r="K15" t="str">
-        <v>6973560306940</v>
+        <v>6926557321051</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>小于等于10%触发</v>
@@ -11632,30 +11638,30 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E16" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="F16">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>火锅食材</v>
+        <v>预制主食</v>
       </c>
       <c r="I16" t="str">
-        <v>牛羊肉卷</v>
+        <v>水饺馄饨</v>
       </c>
       <c r="J16" t="str">
-        <v>皓月新西兰羔羊卷WMT/450g</v>
+        <v>生活馆_菌菇三鲜水饺/480g</v>
       </c>
       <c r="K16" t="str">
-        <v>6926557316743</v>
+        <v>6970185773607</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>小于等于10%触发</v>
@@ -11667,30 +11673,30 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E17" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="F17">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>火锅食材</v>
+        <v>预制主食</v>
       </c>
       <c r="I17" t="str">
-        <v>牛羊肉卷</v>
+        <v>水饺馄饨</v>
       </c>
       <c r="J17" t="str">
-        <v>原切肥羊卷300g</v>
+        <v>魔芋羽衣甘蓝水饺480g</v>
       </c>
       <c r="K17" t="str">
-        <v>6926557321051</v>
+        <v>6970185773799</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>小于等于10%触发</v>
@@ -11699,33 +11705,33 @@
         <v>暂不纳入</v>
       </c>
       <c r="D18" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
+        <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E18" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="F18">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>预制主食</v>
+        <v>雪糕冰品</v>
       </c>
       <c r="I18" t="str">
-        <v>水饺馄饨</v>
+        <v>雪糕冰淇淋</v>
       </c>
       <c r="J18" t="str">
-        <v>生活馆_菌菇三鲜水饺/480g</v>
+        <v>和路雪绿舌头54g</v>
       </c>
       <c r="K18" t="str">
-        <v>6970185773607</v>
+        <v>6909493800453</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>小于等于10%触发</v>
@@ -11734,33 +11740,33 @@
         <v>暂不纳入</v>
       </c>
       <c r="D19" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
+        <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E19" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="F19">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>预制主食</v>
+        <v>雪糕冰品</v>
       </c>
       <c r="I19" t="str">
-        <v>水饺馄饨</v>
+        <v>雪糕冰淇淋</v>
       </c>
       <c r="J19" t="str">
-        <v>魔芋羽衣甘蓝水饺480g</v>
+        <v>雀巢8次方巧克力香草味84g</v>
       </c>
       <c r="K19" t="str">
-        <v>6970185773799</v>
+        <v>6918551807884</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>小于等于10%触发</v>
@@ -11775,7 +11781,7 @@
         <v>B</v>
       </c>
       <c r="F20">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -11787,15 +11793,15 @@
         <v>雪糕冰淇淋</v>
       </c>
       <c r="J20" t="str">
-        <v>和路雪绿舌头54g</v>
+        <v>和路雪可爱多香草67g</v>
       </c>
       <c r="K20" t="str">
-        <v>6909493800453</v>
+        <v>6909493401032</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>小于等于10%触发</v>
@@ -11807,10 +11813,10 @@
         <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E21" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="F21">
-        <v>23</v>
+        <v>9999</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -11822,15 +11828,15 @@
         <v>雪糕冰淇淋</v>
       </c>
       <c r="J21" t="str">
-        <v>雀巢8次方巧克力香草味84g</v>
+        <v>小金条无核榴莲肉100g</v>
       </c>
       <c r="K21" t="str">
-        <v>6918551807884</v>
+        <v>6977480896154</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>小于等于10%触发</v>
@@ -11842,10 +11848,10 @@
         <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E22" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="F22">
-        <v>33</v>
+        <v>9999</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -11857,15 +11863,15 @@
         <v>雪糕冰淇淋</v>
       </c>
       <c r="J22" t="str">
-        <v>和路雪可爱多香草67g</v>
+        <v>伊利6重巧巧70g</v>
       </c>
       <c r="K22" t="str">
-        <v>6909493401032</v>
+        <v>6907992827353</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>小于等于10%触发</v>
@@ -11874,7 +11880,7 @@
         <v>暂不纳入</v>
       </c>
       <c r="D23" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
+        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E23" t="str">
         <v>未评级</v>
@@ -11886,92 +11892,22 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>雪糕冰品</v>
+        <v>预制菜类</v>
       </c>
       <c r="I23" t="str">
-        <v>雪糕冰淇淋</v>
+        <v>炸物小吃</v>
       </c>
       <c r="J23" t="str">
-        <v>小金条无核榴莲肉100g</v>
+        <v>美好小酥肉800g</v>
       </c>
       <c r="K23" t="str">
-        <v>6977480896154</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B24" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C24" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D24" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E24" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F24">
-        <v>9999</v>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
-      <c r="H24" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I24" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J24" t="str">
-        <v>伊利6重巧巧70g</v>
-      </c>
-      <c r="K24" t="str">
-        <v>6907992827353</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B25" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C25" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D25" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
-      </c>
-      <c r="E25" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F25">
-        <v>9999</v>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
-      <c r="H25" t="str">
-        <v>预制菜类</v>
-      </c>
-      <c r="I25" t="str">
-        <v>炸物小吃</v>
-      </c>
-      <c r="J25" t="str">
-        <v>美好小酥肉800g</v>
-      </c>
-      <c r="K25" t="str">
         <v>6971938880948</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K25"/>
+  <autoFilter ref="A1:K23"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K23"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/drafts/新增门店_严格排柜结果.xlsx
+++ b/data/drafts/新增门店_严格排柜结果.xlsx
@@ -14,9 +14,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">'10%触发_门店汇总'!A1:Q2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'10%触发_SKU明细'!A1:AK72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'10%触发_外储明细'!A1:M53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'10%触发_柜段余量'!A1:N37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'10%触发_未排入SKU清单'!A1:K23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'10%触发_外储明细'!A1:M46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'10%触发_柜段余量'!A1:N39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'10%触发_未排入SKU清单'!A1:K15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">'71SKU有效池明细'!A1:Q72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">'测算规则说明'!A1:B3</definedName>
   </definedNames>
@@ -485,28 +485,28 @@
         <v>71</v>
       </c>
       <c r="E2">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2">
-        <v>973.7</v>
+        <v>971.7</v>
       </c>
       <c r="J2">
-        <v>486.9</v>
+        <v>485.8</v>
       </c>
       <c r="K2">
-        <v>604.6</v>
+        <v>603.3</v>
       </c>
       <c r="L2">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="M2" t="str">
         <v>未超754L</v>
@@ -678,7 +678,7 @@
         <v>卧柜</v>
       </c>
       <c r="L2" t="str">
-        <v>卧柜2505mm-柜1</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="M2" t="str">
         <v>分区2</v>
@@ -690,19 +690,19 @@
         <v>1</v>
       </c>
       <c r="P2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q2">
         <v>230</v>
       </c>
       <c r="R2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U2">
         <v>24</v>
@@ -735,16 +735,16 @@
         <v>2</v>
       </c>
       <c r="AE2">
+        <v>14</v>
+      </c>
+      <c r="AF2">
         <v>10</v>
       </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
       <c r="AG2">
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="AH2">
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
       <c r="AK2" t="str">
         <v>是</v>
@@ -779,7 +779,7 @@
         <v>卧柜</v>
       </c>
       <c r="L3" t="str">
-        <v>卧柜2505mm-柜2</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M3" t="str">
         <v>分区2</v>
@@ -791,19 +791,19 @@
         <v>1</v>
       </c>
       <c r="P3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q3">
         <v>277.5</v>
       </c>
       <c r="R3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U3">
         <v>20</v>
@@ -836,16 +836,16 @@
         <v>2</v>
       </c>
       <c r="AE3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG3">
-        <v>16.9272</v>
+        <v>12.6954</v>
       </c>
       <c r="AH3">
-        <v>8.4636</v>
+        <v>6.3477</v>
       </c>
       <c r="AK3" t="str">
         <v>是</v>
@@ -880,7 +880,7 @@
         <v>卧柜</v>
       </c>
       <c r="L4" t="str">
-        <v>卧柜2505mm-柜3</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="M4" t="str">
         <v>分区2</v>
@@ -981,7 +981,7 @@
         <v>卧柜</v>
       </c>
       <c r="L5" t="str">
-        <v>卧柜2505mm-柜4</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M5" t="str">
         <v>分区2</v>
@@ -993,19 +993,19 @@
         <v>1</v>
       </c>
       <c r="P5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q5">
         <v>230</v>
       </c>
       <c r="R5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U5">
         <v>24</v>
@@ -1038,16 +1038,16 @@
         <v>2</v>
       </c>
       <c r="AE5">
+        <v>14</v>
+      </c>
+      <c r="AF5">
         <v>10</v>
       </c>
-      <c r="AF5">
-        <v>14</v>
-      </c>
       <c r="AG5">
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="AH5">
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
       <c r="AK5" t="str">
         <v>是</v>
@@ -1281,34 +1281,34 @@
         <v>火锅肉类</v>
       </c>
       <c r="K8" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L8" t="str">
-        <v/>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="N8" t="str">
         <v>主陈列</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U8">
         <v>32</v>
@@ -1338,19 +1338,19 @@
         <v>12.9</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF8">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="AG8">
-        <v>38.1344</v>
+        <v>11.917</v>
       </c>
       <c r="AH8">
-        <v>19.0672</v>
+        <v>5.9585</v>
       </c>
       <c r="AK8" t="str">
         <v>是</v>
@@ -1385,10 +1385,10 @@
         <v>立柜</v>
       </c>
       <c r="L9" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="M9" t="str">
-        <v>第2层</v>
+        <v>第1层</v>
       </c>
       <c r="N9" t="str">
         <v>主陈列</v>
@@ -1587,16 +1587,16 @@
         <v>立柜</v>
       </c>
       <c r="L11" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="M11" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="N11" t="str">
         <v>主陈列</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11">
         <v>2</v>
@@ -1605,13 +1605,13 @@
         <v>290</v>
       </c>
       <c r="R11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1644,16 +1644,16 @@
         <v>1</v>
       </c>
       <c r="AE11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG11">
-        <v>40.3466</v>
+        <v>51.8742</v>
       </c>
       <c r="AH11">
-        <v>20.1733</v>
+        <v>25.9371</v>
       </c>
       <c r="AK11" t="str">
         <v>是</v>
@@ -1688,31 +1688,31 @@
         <v>立柜</v>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>第2层</v>
       </c>
       <c r="N12" t="str">
         <v>主陈列</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -1742,19 +1742,19 @@
         <v>29.2</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG12">
-        <v>57.638</v>
+        <v>51.8742</v>
       </c>
       <c r="AH12">
-        <v>28.819</v>
+        <v>25.9371</v>
       </c>
       <c r="AK12" t="str">
         <v>是</v>
@@ -1789,10 +1789,10 @@
         <v>立柜</v>
       </c>
       <c r="L13" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="M13" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="N13" t="str">
         <v>主陈列</v>
@@ -1890,10 +1890,10 @@
         <v>立柜</v>
       </c>
       <c r="L14" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="M14" t="str">
-        <v>第5层</v>
+        <v>第4层</v>
       </c>
       <c r="N14" t="str">
         <v>主陈列</v>
@@ -1991,10 +1991,10 @@
         <v>立柜</v>
       </c>
       <c r="L15" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="M15" t="str">
-        <v>第1层</v>
+        <v>第3层</v>
       </c>
       <c r="N15" t="str">
         <v>主陈列</v>
@@ -2092,10 +2092,10 @@
         <v>立柜</v>
       </c>
       <c r="L16" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="M16" t="str">
-        <v>第4层</v>
+        <v>第1层</v>
       </c>
       <c r="N16" t="str">
         <v>主陈列</v>
@@ -2193,16 +2193,16 @@
         <v>立柜</v>
       </c>
       <c r="L17" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="M17" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="N17" t="str">
         <v>主陈列</v>
       </c>
       <c r="O17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P17">
         <v>3</v>
@@ -2211,13 +2211,13 @@
         <v>165</v>
       </c>
       <c r="R17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>48</v>
@@ -2247,19 +2247,19 @@
         <v>50.9</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG17">
-        <v>43.89</v>
+        <v>46.2</v>
       </c>
       <c r="AH17">
-        <v>21.945</v>
+        <v>23.1</v>
       </c>
       <c r="AK17" t="str">
         <v>是</v>
@@ -2294,16 +2294,16 @@
         <v>立柜</v>
       </c>
       <c r="L18" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="M18" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="N18" t="str">
         <v>主陈列</v>
       </c>
       <c r="O18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P18">
         <v>3</v>
@@ -2312,13 +2312,13 @@
         <v>210</v>
       </c>
       <c r="R18">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S18">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U18">
         <v>48</v>
@@ -2351,16 +2351,16 @@
         <v>1</v>
       </c>
       <c r="AE18">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AF18">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AG18">
-        <v>59.724</v>
+        <v>68.6826</v>
       </c>
       <c r="AH18">
-        <v>29.862</v>
+        <v>34.3413</v>
       </c>
       <c r="AK18" t="str">
         <v>是</v>
@@ -2597,16 +2597,16 @@
         <v>立柜</v>
       </c>
       <c r="L21" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="M21" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="N21" t="str">
         <v>主陈列</v>
       </c>
       <c r="O21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21">
         <v>2</v>
@@ -2615,13 +2615,13 @@
         <v>180</v>
       </c>
       <c r="R21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U21">
         <v>25</v>
@@ -2654,16 +2654,16 @@
         <v>1</v>
       </c>
       <c r="AE21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF21">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG21">
-        <v>33.957</v>
+        <v>37.044</v>
       </c>
       <c r="AH21">
-        <v>16.9785</v>
+        <v>18.522</v>
       </c>
       <c r="AK21" t="str">
         <v>是</v>
@@ -2695,13 +2695,13 @@
         <v>冷冻食材</v>
       </c>
       <c r="K22" t="str">
-        <v>卧柜</v>
+        <v>立柜</v>
       </c>
       <c r="L22" t="str">
-        <v>卧柜1886mm-柜5</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="M22" t="str">
-        <v>分区2</v>
+        <v>第2层</v>
       </c>
       <c r="N22" t="str">
         <v>主陈列</v>
@@ -2710,19 +2710,19 @@
         <v>1</v>
       </c>
       <c r="P22">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="Q22">
         <v>260</v>
       </c>
       <c r="R22">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="T22">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="U22">
         <v>40</v>
@@ -2752,19 +2752,19 @@
         <v>40</v>
       </c>
       <c r="AD22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE22">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="AF22">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="AG22">
-        <v>3.1824</v>
+        <v>30.2328</v>
       </c>
       <c r="AH22">
-        <v>1.5912</v>
+        <v>15.1164</v>
       </c>
       <c r="AK22" t="str">
         <v>是</v>
@@ -2799,10 +2799,10 @@
         <v>立柜</v>
       </c>
       <c r="L23" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="M23" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="N23" t="str">
         <v>主陈列</v>
@@ -3102,10 +3102,10 @@
         <v>立柜</v>
       </c>
       <c r="L26" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="M26" t="str">
-        <v>第5层</v>
+        <v>第4层</v>
       </c>
       <c r="N26" t="str">
         <v>主陈列</v>
@@ -3203,10 +3203,10 @@
         <v>立柜</v>
       </c>
       <c r="L27" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="M27" t="str">
-        <v>第5层</v>
+        <v>第4层</v>
       </c>
       <c r="N27" t="str">
         <v>主陈列</v>
@@ -3304,31 +3304,31 @@
         <v>立柜</v>
       </c>
       <c r="L28" t="str">
-        <v/>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>第5层</v>
       </c>
       <c r="N28" t="str">
         <v>主陈列</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U28">
         <v>20</v>
@@ -3358,19 +3358,19 @@
         <v>142</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF28">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG28">
-        <v>33.824</v>
+        <v>28.7504</v>
       </c>
       <c r="AH28">
-        <v>16.912</v>
+        <v>14.3752</v>
       </c>
       <c r="AK28" t="str">
         <v>是</v>
@@ -3402,34 +3402,34 @@
         <v>冷冻水产</v>
       </c>
       <c r="K29" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="N29" t="str">
         <v>主陈列</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U29">
         <v>20</v>
@@ -3459,19 +3459,19 @@
         <v>147</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AF29">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AG29">
-        <v>45.1</v>
+        <v>15.785</v>
       </c>
       <c r="AH29">
-        <v>22.55</v>
+        <v>7.8925</v>
       </c>
       <c r="AK29" t="str">
         <v>是</v>
@@ -3503,34 +3503,34 @@
         <v>冷冻水果</v>
       </c>
       <c r="K30" t="str">
-        <v>卧柜</v>
+        <v>立柜</v>
       </c>
       <c r="L30" t="str">
-        <v>卧柜2505mm-柜4</v>
+        <v/>
       </c>
       <c r="M30" t="str">
-        <v>分区1</v>
+        <v/>
       </c>
       <c r="N30" t="str">
         <v>主陈列</v>
       </c>
       <c r="O30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="U30">
         <v>30</v>
@@ -3560,19 +3560,19 @@
         <v>43.3</v>
       </c>
       <c r="AD30">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
         <v>30</v>
       </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
       <c r="AG30">
-        <v>0</v>
+        <v>124.74</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>62.37</v>
       </c>
       <c r="AK30" t="str">
         <v>是</v>
@@ -3607,10 +3607,10 @@
         <v>立柜</v>
       </c>
       <c r="L31" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="M31" t="str">
-        <v>第2层</v>
+        <v>第1层</v>
       </c>
       <c r="N31" t="str">
         <v>主陈列</v>
@@ -3708,10 +3708,10 @@
         <v>立柜</v>
       </c>
       <c r="L32" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="M32" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="N32" t="str">
         <v>主陈列</v>
@@ -4011,16 +4011,16 @@
         <v>立柜</v>
       </c>
       <c r="L35" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="M35" t="str">
-        <v>第2层</v>
+        <v>第4层</v>
       </c>
       <c r="N35" t="str">
         <v>主陈列</v>
       </c>
       <c r="O35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P35">
         <v>2</v>
@@ -4029,13 +4029,13 @@
         <v>180</v>
       </c>
       <c r="R35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U35">
         <v>15</v>
@@ -4068,16 +4068,16 @@
         <v>1</v>
       </c>
       <c r="AE35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF35">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AG35">
-        <v>18.63</v>
+        <v>26.082</v>
       </c>
       <c r="AH35">
-        <v>9.315</v>
+        <v>13.041</v>
       </c>
       <c r="AK35" t="str">
         <v>是</v>
@@ -4112,31 +4112,31 @@
         <v>立柜</v>
       </c>
       <c r="L36" t="str">
-        <v/>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>第4层</v>
       </c>
       <c r="N36" t="str">
         <v>主陈列</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36">
         <v>18</v>
@@ -4166,19 +4166,19 @@
         <v>44.1</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG36">
-        <v>29.16</v>
+        <v>27.54</v>
       </c>
       <c r="AH36">
-        <v>14.58</v>
+        <v>13.77</v>
       </c>
       <c r="AK36" t="str">
         <v>是</v>
@@ -4213,10 +4213,10 @@
         <v>立柜</v>
       </c>
       <c r="L37" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="M37" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="N37" t="str">
         <v>主陈列</v>
@@ -4314,16 +4314,16 @@
         <v>立柜</v>
       </c>
       <c r="L38" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜4</v>
       </c>
       <c r="M38" t="str">
-        <v>第4层</v>
+        <v>第5层</v>
       </c>
       <c r="N38" t="str">
         <v>主陈列</v>
       </c>
       <c r="O38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38">
         <v>2</v>
@@ -4332,13 +4332,13 @@
         <v>315</v>
       </c>
       <c r="R38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U38">
         <v>20</v>
@@ -4371,16 +4371,16 @@
         <v>1</v>
       </c>
       <c r="AE38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF38">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG38">
-        <v>46.053</v>
+        <v>51.471</v>
       </c>
       <c r="AH38">
-        <v>23.0265</v>
+        <v>25.7355</v>
       </c>
       <c r="AK38" t="str">
         <v>是</v>
@@ -4415,16 +4415,16 @@
         <v>立柜</v>
       </c>
       <c r="L39" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜4</v>
       </c>
       <c r="M39" t="str">
-        <v>第2层</v>
+        <v>第5层</v>
       </c>
       <c r="N39" t="str">
         <v>主陈列</v>
       </c>
       <c r="O39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P39">
         <v>2</v>
@@ -4433,13 +4433,13 @@
         <v>310</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U39">
         <v>20</v>
@@ -4472,16 +4472,16 @@
         <v>1</v>
       </c>
       <c r="AE39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF39">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG39">
-        <v>52.173</v>
+        <v>58.311</v>
       </c>
       <c r="AH39">
-        <v>26.0865</v>
+        <v>29.1555</v>
       </c>
       <c r="AK39" t="str">
         <v>是</v>
@@ -4513,13 +4513,13 @@
         <v>水饺馄饨</v>
       </c>
       <c r="K40" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L40" t="str">
-        <v>立柜3m-柜10</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M40" t="str">
-        <v>第3层</v>
+        <v>分区1</v>
       </c>
       <c r="N40" t="str">
         <v>主陈列</v>
@@ -4528,19 +4528,19 @@
         <v>1</v>
       </c>
       <c r="P40">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="Q40">
         <v>315</v>
       </c>
       <c r="R40">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="S40">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="T40">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="U40">
         <v>20</v>
@@ -4570,19 +4570,19 @@
         <v>43</v>
       </c>
       <c r="AD40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE40">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AF40">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>51.471</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>25.7355</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="str">
         <v>是</v>
@@ -4614,13 +4614,13 @@
         <v>水饺馄饨</v>
       </c>
       <c r="K41" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L41" t="str">
-        <v>立柜3m-柜10</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M41" t="str">
-        <v>第3层</v>
+        <v>分区1</v>
       </c>
       <c r="N41" t="str">
         <v>主陈列</v>
@@ -4629,19 +4629,19 @@
         <v>1</v>
       </c>
       <c r="P41">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="Q41">
         <v>310</v>
       </c>
       <c r="R41">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="S41">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="T41">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="U41">
         <v>18</v>
@@ -4671,19 +4671,19 @@
         <v>44.3</v>
       </c>
       <c r="AD41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE41">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AF41">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>56.5216</v>
+        <v>0</v>
       </c>
       <c r="AH41">
-        <v>28.2608</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="str">
         <v>是</v>
@@ -4715,34 +4715,34 @@
         <v>水饺馄饨</v>
       </c>
       <c r="K42" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L42" t="str">
-        <v/>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M42" t="str">
-        <v/>
+        <v>分区1</v>
       </c>
       <c r="N42" t="str">
         <v>主陈列</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="U42">
         <v>20</v>
@@ -4772,19 +4772,19 @@
         <v>88.2</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AF42">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>61.38</v>
+        <v>0</v>
       </c>
       <c r="AH42">
-        <v>30.69</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="str">
         <v>是</v>
@@ -4816,34 +4816,34 @@
         <v>水饺馄饨</v>
       </c>
       <c r="K43" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L43" t="str">
-        <v/>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>分区1</v>
       </c>
       <c r="N43" t="str">
         <v>主陈列</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="U43">
         <v>20</v>
@@ -4873,19 +4873,19 @@
         <v>173.6</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AF43">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>61.38</v>
+        <v>0</v>
       </c>
       <c r="AH43">
-        <v>30.69</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="str">
         <v>是</v>
@@ -4917,13 +4917,13 @@
         <v>水饺馄饨</v>
       </c>
       <c r="K44" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L44" t="str">
-        <v>立柜3m-柜9</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M44" t="str">
-        <v>第3层</v>
+        <v>分区1</v>
       </c>
       <c r="N44" t="str">
         <v>主陈列</v>
@@ -4932,19 +4932,19 @@
         <v>1</v>
       </c>
       <c r="P44">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q44">
         <v>235</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="S44">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="T44">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="U44">
         <v>12</v>
@@ -4974,19 +4974,19 @@
         <v>7.5</v>
       </c>
       <c r="AD44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE44">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AF44">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>28.788</v>
+        <v>0</v>
       </c>
       <c r="AH44">
-        <v>14.394</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="str">
         <v>是</v>
@@ -5021,16 +5021,16 @@
         <v>立柜</v>
       </c>
       <c r="L45" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="M45" t="str">
-        <v>第4层</v>
+        <v>第2层</v>
       </c>
       <c r="N45" t="str">
         <v>主陈列</v>
       </c>
       <c r="O45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P45">
         <v>2</v>
@@ -5039,13 +5039,13 @@
         <v>180</v>
       </c>
       <c r="R45">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T45">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U45">
         <v>30</v>
@@ -5078,16 +5078,16 @@
         <v>1</v>
       </c>
       <c r="AE45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF45">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AG45">
-        <v>28.35</v>
+        <v>32.886</v>
       </c>
       <c r="AH45">
-        <v>14.175</v>
+        <v>16.443</v>
       </c>
       <c r="AK45" t="str">
         <v>是</v>
@@ -5119,34 +5119,34 @@
         <v>速食披萨</v>
       </c>
       <c r="K46" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L46" t="str">
-        <v>立柜3m-柜10</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M46" t="str">
-        <v>第5层</v>
+        <v>分区1</v>
       </c>
       <c r="N46" t="str">
         <v>主陈列</v>
       </c>
       <c r="O46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P46">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="Q46">
         <v>180</v>
       </c>
       <c r="R46">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="S46">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="U46">
         <v>30</v>
@@ -5176,19 +5176,19 @@
         <v>90.3</v>
       </c>
       <c r="AD46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE46">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="AF46">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>30.618</v>
+        <v>0</v>
       </c>
       <c r="AH46">
-        <v>15.309</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="str">
         <v>是</v>
@@ -5220,13 +5220,13 @@
         <v>速食披萨</v>
       </c>
       <c r="K47" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L47" t="str">
-        <v>立柜3m-柜10</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M47" t="str">
-        <v>第5层</v>
+        <v>分区1</v>
       </c>
       <c r="N47" t="str">
         <v>主陈列</v>
@@ -5235,19 +5235,19 @@
         <v>1</v>
       </c>
       <c r="P47">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="Q47">
         <v>180</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="S47">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="T47">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U47">
         <v>30</v>
@@ -5277,19 +5277,19 @@
         <v>97.5</v>
       </c>
       <c r="AD47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE47">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="AF47">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>32.886</v>
+        <v>0</v>
       </c>
       <c r="AH47">
-        <v>16.443</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="str">
         <v>是</v>
@@ -5324,7 +5324,7 @@
         <v>卧柜</v>
       </c>
       <c r="L48" t="str">
-        <v>卧柜1886mm-柜5</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="M48" t="str">
         <v>分区1</v>
@@ -5333,22 +5333,22 @@
         <v>主陈列</v>
       </c>
       <c r="O48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P48">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q48">
         <v>180</v>
       </c>
       <c r="R48">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="S48">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="T48">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="U48">
         <v>30</v>
@@ -5378,7 +5378,7 @@
         <v>101.3</v>
       </c>
       <c r="AD48">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE48">
         <v>30</v>
@@ -5425,7 +5425,7 @@
         <v>卧柜</v>
       </c>
       <c r="L49" t="str">
-        <v>卧柜2505mm-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M49" t="str">
         <v>分区1</v>
@@ -5437,19 +5437,19 @@
         <v>1</v>
       </c>
       <c r="P49">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q49">
         <v>220</v>
       </c>
       <c r="R49">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="S49">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="T49">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U49">
         <v>20</v>
@@ -5526,7 +5526,7 @@
         <v>卧柜</v>
       </c>
       <c r="L50" t="str">
-        <v>卧柜2505mm-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M50" t="str">
         <v>分区1</v>
@@ -5538,19 +5538,19 @@
         <v>1</v>
       </c>
       <c r="P50">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q50">
         <v>265</v>
       </c>
       <c r="R50">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="S50">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="T50">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="U50">
         <v>20</v>
@@ -5580,7 +5580,7 @@
         <v>9.3</v>
       </c>
       <c r="AD50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE50">
         <v>20</v>
@@ -5627,10 +5627,10 @@
         <v>立柜</v>
       </c>
       <c r="L51" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="M51" t="str">
-        <v>第5层</v>
+        <v>第3层</v>
       </c>
       <c r="N51" t="str">
         <v>主陈列</v>
@@ -5728,7 +5728,7 @@
         <v>卧柜</v>
       </c>
       <c r="L52" t="str">
-        <v>卧柜2505mm-柜2</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="M52" t="str">
         <v>分区1</v>
@@ -5740,19 +5740,19 @@
         <v>9</v>
       </c>
       <c r="P52">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="Q52">
         <v>185</v>
       </c>
       <c r="R52">
-        <v>504</v>
+        <v>468</v>
       </c>
       <c r="S52">
-        <v>504</v>
+        <v>468</v>
       </c>
       <c r="T52">
-        <v>504</v>
+        <v>468</v>
       </c>
       <c r="U52">
         <v>40</v>
@@ -5782,7 +5782,7 @@
         <v>137.4</v>
       </c>
       <c r="AD52">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AE52">
         <v>40</v>
@@ -5829,7 +5829,7 @@
         <v>卧柜</v>
       </c>
       <c r="L53" t="str">
-        <v>卧柜2505mm-柜2</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="M53" t="str">
         <v>分区1</v>
@@ -5841,19 +5841,19 @@
         <v>1</v>
       </c>
       <c r="P53">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q53">
         <v>240</v>
       </c>
       <c r="R53">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="S53">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="T53">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U53">
         <v>30</v>
@@ -5930,7 +5930,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L54" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M54" t="str">
         <v>分区2</v>
@@ -5942,19 +5942,19 @@
         <v>1</v>
       </c>
       <c r="P54">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Q54">
         <v>320</v>
       </c>
       <c r="R54">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="S54">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="T54">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="U54">
         <v>20</v>
@@ -5984,19 +5984,19 @@
         <v>2.1</v>
       </c>
       <c r="AD54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE54">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AH54">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AK54" t="str">
         <v>是</v>
@@ -6031,7 +6031,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L55" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M55" t="str">
         <v>分区1</v>
@@ -6043,19 +6043,19 @@
         <v>1</v>
       </c>
       <c r="P55">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="Q55">
         <v>200</v>
       </c>
       <c r="R55">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="S55">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="T55">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="U55">
         <v>50</v>
@@ -6085,7 +6085,7 @@
         <v>3.8</v>
       </c>
       <c r="AD55">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AE55">
         <v>50</v>
@@ -6132,7 +6132,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L56" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M56" t="str">
         <v>分区1</v>
@@ -6144,19 +6144,19 @@
         <v>1</v>
       </c>
       <c r="P56">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="Q56">
         <v>210</v>
       </c>
       <c r="R56">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="S56">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="T56">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="U56">
         <v>40</v>
@@ -6186,7 +6186,7 @@
         <v>4.3</v>
       </c>
       <c r="AD56">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AE56">
         <v>40</v>
@@ -6233,7 +6233,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L57" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M57" t="str">
         <v>分区1</v>
@@ -6245,19 +6245,19 @@
         <v>1</v>
       </c>
       <c r="P57">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="Q57">
         <v>190</v>
       </c>
       <c r="R57">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="S57">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="T57">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="U57">
         <v>40</v>
@@ -6287,7 +6287,7 @@
         <v>4.4</v>
       </c>
       <c r="AD57">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE57">
         <v>40</v>
@@ -6334,7 +6334,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L58" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M58" t="str">
         <v>分区1</v>
@@ -6346,19 +6346,19 @@
         <v>1</v>
       </c>
       <c r="P58">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="Q58">
         <v>200</v>
       </c>
       <c r="R58">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="S58">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="T58">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="U58">
         <v>40</v>
@@ -6388,7 +6388,7 @@
         <v>5</v>
       </c>
       <c r="AD58">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AE58">
         <v>40</v>
@@ -6435,7 +6435,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L59" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M59" t="str">
         <v>分区1</v>
@@ -6536,7 +6536,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L60" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M60" t="str">
         <v>分区1</v>
@@ -6548,19 +6548,19 @@
         <v>1</v>
       </c>
       <c r="P60">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="Q60">
         <v>200</v>
       </c>
       <c r="R60">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="S60">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="T60">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="U60">
         <v>40</v>
@@ -6590,7 +6590,7 @@
         <v>6.5</v>
       </c>
       <c r="AD60">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AE60">
         <v>40</v>
@@ -6637,7 +6637,7 @@
         <v>冰淇淋柜</v>
       </c>
       <c r="L61" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M61" t="str">
         <v>分区1</v>
@@ -6649,19 +6649,19 @@
         <v>1</v>
       </c>
       <c r="P61">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="Q61">
         <v>190</v>
       </c>
       <c r="R61">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="S61">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="T61">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="U61">
         <v>16</v>
@@ -6691,7 +6691,7 @@
         <v>6.7</v>
       </c>
       <c r="AD61">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE61">
         <v>16</v>
@@ -6734,29 +6734,35 @@
       <c r="H62" t="str">
         <v>雪糕冰淇淋</v>
       </c>
+      <c r="K62" t="str">
+        <v>冰淇淋柜</v>
+      </c>
       <c r="L62" t="str">
-        <v/>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>分区1</v>
+      </c>
+      <c r="N62" t="str">
+        <v>主陈列</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="U62">
         <v>36</v>
@@ -6786,19 +6792,19 @@
         <v>7.4</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF62">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>10.3968</v>
+        <v>0</v>
       </c>
       <c r="AH62">
-        <v>5.1984</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="str">
         <v>是</v>
@@ -6924,29 +6930,35 @@
       <c r="H64" t="str">
         <v>雪糕冰淇淋</v>
       </c>
+      <c r="K64" t="str">
+        <v>冰淇淋柜</v>
+      </c>
       <c r="L64" t="str">
-        <v/>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>分区1</v>
+      </c>
+      <c r="N64" t="str">
+        <v>主陈列</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="U64">
         <v>24</v>
@@ -6976,19 +6988,19 @@
         <v>10.3</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF64">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AG64">
-        <v>13.392</v>
+        <v>0</v>
       </c>
       <c r="AH64">
-        <v>6.696</v>
+        <v>0</v>
       </c>
       <c r="AK64" t="str">
         <v>是</v>
@@ -7213,7 +7225,7 @@
         <v>卧柜</v>
       </c>
       <c r="L67" t="str">
-        <v>卧柜2505mm-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M67" t="str">
         <v>分区1</v>
@@ -7222,22 +7234,22 @@
         <v>主陈列</v>
       </c>
       <c r="O67">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P67">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="Q67">
         <v>200</v>
       </c>
       <c r="R67">
-        <v>726</v>
+        <v>400</v>
       </c>
       <c r="S67">
-        <v>726</v>
+        <v>400</v>
       </c>
       <c r="T67">
-        <v>726</v>
+        <v>400</v>
       </c>
       <c r="U67">
         <v>40</v>
@@ -7267,7 +7279,7 @@
         <v>25.8</v>
       </c>
       <c r="AD67">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="AE67">
         <v>40</v>
@@ -7314,7 +7326,7 @@
         <v>卧柜</v>
       </c>
       <c r="L68" t="str">
-        <v>卧柜2505mm-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M68" t="str">
         <v>分区1</v>
@@ -7326,19 +7338,19 @@
         <v>1</v>
       </c>
       <c r="P68">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="Q68">
         <v>200</v>
       </c>
       <c r="R68">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="S68">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="T68">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="U68">
         <v>40</v>
@@ -7368,7 +7380,7 @@
         <v>49.2</v>
       </c>
       <c r="AD68">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE68">
         <v>40</v>
@@ -7415,7 +7427,7 @@
         <v>卧柜</v>
       </c>
       <c r="L69" t="str">
-        <v>卧柜2505mm-柜3</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M69" t="str">
         <v>分区1</v>
@@ -7424,22 +7436,22 @@
         <v>主陈列</v>
       </c>
       <c r="O69">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P69">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q69">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="R69">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="S69">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="T69">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="U69">
         <v>10</v>
@@ -7469,7 +7481,7 @@
         <v>16.5</v>
       </c>
       <c r="AD69">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE69">
         <v>10</v>
@@ -7516,7 +7528,7 @@
         <v>卧柜</v>
       </c>
       <c r="L70" t="str">
-        <v>卧柜2505mm-柜3</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M70" t="str">
         <v>分区1</v>
@@ -7528,19 +7540,19 @@
         <v>1</v>
       </c>
       <c r="P70">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="Q70">
         <v>220</v>
       </c>
       <c r="R70">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="S70">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="T70">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="U70">
         <v>15</v>
@@ -7570,7 +7582,7 @@
         <v>32.6</v>
       </c>
       <c r="AD70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE70">
         <v>15</v>
@@ -7617,7 +7629,7 @@
         <v>卧柜</v>
       </c>
       <c r="L71" t="str">
-        <v>卧柜2505mm-柜3</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M71" t="str">
         <v>分区1</v>
@@ -7629,19 +7641,19 @@
         <v>1</v>
       </c>
       <c r="P71">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="Q71">
         <v>240</v>
       </c>
       <c r="R71">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S71">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="T71">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="U71">
         <v>15</v>
@@ -7800,7 +7812,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7857,7 +7869,7 @@
         <v>B</v>
       </c>
       <c r="E2" t="str">
-        <v>卧柜2505mm-柜1</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="F2" t="str">
         <v>分区2</v>
@@ -7866,16 +7878,16 @@
         <v>24</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>1.955</v>
       </c>
       <c r="J2">
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="K2">
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
     </row>
     <row r="3">
@@ -7892,7 +7904,7 @@
         <v>C</v>
       </c>
       <c r="E3" t="str">
-        <v>卧柜2505mm-柜2</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="F3" t="str">
         <v>分区2</v>
@@ -7901,16 +7913,16 @@
         <v>20</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>2.1159</v>
       </c>
       <c r="J3">
-        <v>16.9272</v>
+        <v>12.6954</v>
       </c>
       <c r="K3">
-        <v>8.4636</v>
+        <v>6.3477</v>
       </c>
     </row>
     <row r="4">
@@ -7927,7 +7939,7 @@
         <v>C</v>
       </c>
       <c r="E4" t="str">
-        <v>卧柜2505mm-柜4</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="F4" t="str">
         <v>分区2</v>
@@ -7936,16 +7948,16 @@
         <v>24</v>
       </c>
       <c r="H4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>1.955</v>
       </c>
       <c r="J4">
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="K4">
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
     </row>
     <row r="5">
@@ -8032,25 +8044,25 @@
         <v>D</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="G7">
         <v>32</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>1.1917</v>
       </c>
       <c r="J7">
-        <v>38.1344</v>
+        <v>11.917</v>
       </c>
       <c r="K7">
-        <v>19.0672</v>
+        <v>5.9585</v>
       </c>
     </row>
     <row r="8">
@@ -8067,10 +8079,10 @@
         <v>D</v>
       </c>
       <c r="E8" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="F8" t="str">
-        <v>第2层</v>
+        <v>第1层</v>
       </c>
       <c r="G8">
         <v>12</v>
@@ -8137,25 +8149,25 @@
         <v>B</v>
       </c>
       <c r="E10" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="F10" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="G10">
         <v>10</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>5.7638</v>
       </c>
       <c r="J10">
-        <v>40.3466</v>
+        <v>51.8742</v>
       </c>
       <c r="K10">
-        <v>20.1733</v>
+        <v>25.9371</v>
       </c>
     </row>
     <row r="11">
@@ -8172,25 +8184,25 @@
         <v>C</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>第2层</v>
       </c>
       <c r="G11">
         <v>10</v>
       </c>
       <c r="H11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>5.7638</v>
       </c>
       <c r="J11">
-        <v>57.638</v>
+        <v>51.8742</v>
       </c>
       <c r="K11">
-        <v>28.819</v>
+        <v>25.9371</v>
       </c>
     </row>
     <row r="12">
@@ -8207,10 +8219,10 @@
         <v>C</v>
       </c>
       <c r="E12" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="F12" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="G12">
         <v>9</v>
@@ -8242,10 +8254,10 @@
         <v>A</v>
       </c>
       <c r="E13" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="F13" t="str">
-        <v>第5层</v>
+        <v>第4层</v>
       </c>
       <c r="G13">
         <v>36</v>
@@ -8277,10 +8289,10 @@
         <v>A</v>
       </c>
       <c r="E14" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="F14" t="str">
-        <v>第1层</v>
+        <v>第3层</v>
       </c>
       <c r="G14">
         <v>48</v>
@@ -8312,10 +8324,10 @@
         <v>A</v>
       </c>
       <c r="E15" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="F15" t="str">
-        <v>第4层</v>
+        <v>第1层</v>
       </c>
       <c r="G15">
         <v>48</v>
@@ -8347,25 +8359,25 @@
         <v>A</v>
       </c>
       <c r="E16" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="F16" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="G16">
         <v>48</v>
       </c>
       <c r="H16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I16">
         <v>1.155</v>
       </c>
       <c r="J16">
-        <v>43.89</v>
+        <v>46.2</v>
       </c>
       <c r="K16">
-        <v>21.945</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="17">
@@ -8382,25 +8394,25 @@
         <v>B</v>
       </c>
       <c r="E17" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="F17" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="G17">
         <v>48</v>
       </c>
       <c r="H17">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I17">
         <v>1.4931</v>
       </c>
       <c r="J17">
-        <v>59.724</v>
+        <v>68.6826</v>
       </c>
       <c r="K17">
-        <v>29.862</v>
+        <v>34.3413</v>
       </c>
     </row>
     <row r="18">
@@ -8487,25 +8499,25 @@
         <v>C</v>
       </c>
       <c r="E20" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="F20" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="G20">
         <v>25</v>
       </c>
       <c r="H20">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I20">
         <v>1.5435</v>
       </c>
       <c r="J20">
-        <v>33.957</v>
+        <v>37.044</v>
       </c>
       <c r="K20">
-        <v>16.9785</v>
+        <v>18.522</v>
       </c>
     </row>
     <row r="21">
@@ -8522,25 +8534,25 @@
         <v>D</v>
       </c>
       <c r="E21" t="str">
-        <v>卧柜1886mm-柜5</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="F21" t="str">
-        <v>分区2</v>
+        <v>第2层</v>
       </c>
       <c r="G21">
         <v>40</v>
       </c>
       <c r="H21">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="I21">
         <v>0.7956</v>
       </c>
       <c r="J21">
-        <v>3.1824</v>
+        <v>30.2328</v>
       </c>
       <c r="K21">
-        <v>1.5912</v>
+        <v>15.1164</v>
       </c>
     </row>
     <row r="22">
@@ -8557,10 +8569,10 @@
         <v>D</v>
       </c>
       <c r="E22" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="F22" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="G22">
         <v>12</v>
@@ -8662,10 +8674,10 @@
         <v>C</v>
       </c>
       <c r="E25" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="F25" t="str">
-        <v>第5层</v>
+        <v>第4层</v>
       </c>
       <c r="G25">
         <v>30</v>
@@ -8697,10 +8709,10 @@
         <v>D</v>
       </c>
       <c r="E26" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="F26" t="str">
-        <v>第5层</v>
+        <v>第4层</v>
       </c>
       <c r="G26">
         <v>25</v>
@@ -8732,25 +8744,25 @@
         <v>D</v>
       </c>
       <c r="E27" t="str">
-        <v/>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>第5层</v>
       </c>
       <c r="G27">
         <v>20</v>
       </c>
       <c r="H27">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I27">
         <v>1.6912</v>
       </c>
       <c r="J27">
-        <v>33.824</v>
+        <v>28.7504</v>
       </c>
       <c r="K27">
-        <v>16.912</v>
+        <v>14.3752</v>
       </c>
     </row>
     <row r="28">
@@ -8767,25 +8779,25 @@
         <v>D</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="G28">
         <v>20</v>
       </c>
       <c r="H28">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>2.255</v>
       </c>
       <c r="J28">
-        <v>45.1</v>
+        <v>15.785</v>
       </c>
       <c r="K28">
-        <v>22.55</v>
+        <v>7.8925</v>
       </c>
     </row>
     <row r="29">
@@ -8793,34 +8805,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
-        <v>双色开花馒头（紫薯味+南瓜味）360g</v>
+        <v>冻榴莲500g</v>
       </c>
       <c r="C29" t="str">
-        <v>6934756102302</v>
+        <v>6977480891210</v>
       </c>
       <c r="D29" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="E29" t="str">
-        <v>立柜3m-柜8</v>
+        <v/>
       </c>
       <c r="F29" t="str">
-        <v>第2层</v>
+        <v/>
       </c>
       <c r="G29">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H29">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I29">
-        <v>2.585</v>
+        <v>4.158</v>
       </c>
       <c r="J29">
-        <v>49.115</v>
+        <v>124.74</v>
       </c>
       <c r="K29">
-        <v>24.5575</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="30">
@@ -8828,34 +8840,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
-        <v>手作奶香黄油开花馒头360g</v>
+        <v>双色开花馒头（紫薯味+南瓜味）360g</v>
       </c>
       <c r="C30" t="str">
-        <v>6934756102241</v>
+        <v>6934756102302</v>
       </c>
       <c r="D30" t="str">
         <v>B</v>
       </c>
       <c r="E30" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="F30" t="str">
-        <v>第3层</v>
+        <v>第1层</v>
       </c>
       <c r="G30">
         <v>24</v>
       </c>
       <c r="H30">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I30">
-        <v>2.58</v>
+        <v>2.585</v>
       </c>
       <c r="J30">
-        <v>54.18</v>
+        <v>49.115</v>
       </c>
       <c r="K30">
-        <v>27.09</v>
+        <v>24.5575</v>
       </c>
     </row>
     <row r="31">
@@ -8863,34 +8875,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
-        <v>生活馆_料多多薯香乳酪包/400g</v>
+        <v>手作奶香黄油开花馒头360g</v>
       </c>
       <c r="C31" t="str">
-        <v>6971997913342</v>
+        <v>6934756102241</v>
       </c>
       <c r="D31" t="str">
-        <v>C</v>
+        <v>B</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>第2层</v>
       </c>
       <c r="G31">
         <v>24</v>
       </c>
       <c r="H31">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I31">
-        <v>2.8875</v>
+        <v>2.58</v>
       </c>
       <c r="J31">
-        <v>69.3</v>
+        <v>54.18</v>
       </c>
       <c r="K31">
-        <v>34.65</v>
+        <v>27.09</v>
       </c>
     </row>
     <row r="32">
@@ -8898,13 +8910,13 @@
         <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
-        <v>鲜奶馒头300g</v>
+        <v>生活馆_料多多薯香乳酪包/400g</v>
       </c>
       <c r="C32" t="str">
-        <v>6973560306940</v>
+        <v>6971997913342</v>
       </c>
       <c r="D32" t="str">
-        <v>未评级</v>
+        <v>C</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -8919,13 +8931,13 @@
         <v>24</v>
       </c>
       <c r="I32">
-        <v>3.9</v>
+        <v>2.8875</v>
       </c>
       <c r="J32">
-        <v>93.6</v>
+        <v>69.3</v>
       </c>
       <c r="K32">
-        <v>46.8</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="33">
@@ -8933,34 +8945,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
-        <v>皓月新西兰羔羊卷WMT/450g</v>
+        <v>鲜奶馒头300g</v>
       </c>
       <c r="C33" t="str">
-        <v>6926557316743</v>
+        <v>6973560306940</v>
       </c>
       <c r="D33" t="str">
-        <v>D</v>
+        <v>未评级</v>
       </c>
       <c r="E33" t="str">
-        <v>立柜3m-柜7</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v>第2层</v>
+        <v/>
       </c>
       <c r="G33">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H33">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I33">
-        <v>1.863</v>
+        <v>3.9</v>
       </c>
       <c r="J33">
-        <v>18.63</v>
+        <v>93.6</v>
       </c>
       <c r="K33">
-        <v>9.315</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="34">
@@ -8968,34 +8980,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
-        <v>原切肥羊卷300g</v>
+        <v>皓月新西兰羔羊卷WMT/450g</v>
       </c>
       <c r="C34" t="str">
-        <v>6926557321051</v>
+        <v>6926557316743</v>
       </c>
       <c r="D34" t="str">
         <v>D</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>第4层</v>
       </c>
       <c r="G34">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H34">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I34">
-        <v>1.62</v>
+        <v>1.863</v>
       </c>
       <c r="J34">
-        <v>29.16</v>
+        <v>26.082</v>
       </c>
       <c r="K34">
-        <v>14.58</v>
+        <v>13.041</v>
       </c>
     </row>
     <row r="35">
@@ -9003,34 +9015,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
-        <v>【真好】黑猪肉爆汁烤肠原味400g</v>
+        <v>原切肥羊卷300g</v>
       </c>
       <c r="C35" t="str">
-        <v>6942209639503</v>
+        <v>6926557321051</v>
       </c>
       <c r="D35" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="E35" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="F35" t="str">
-        <v>第1层</v>
+        <v>第4层</v>
       </c>
       <c r="G35">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H35">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I35">
-        <v>1.0462</v>
+        <v>1.62</v>
       </c>
       <c r="J35">
-        <v>12.5544</v>
+        <v>27.54</v>
       </c>
       <c r="K35">
-        <v>6.2772</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="36">
@@ -9038,34 +9050,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B36" t="str">
-        <v>肉馅芹菜饺480g（两袋仅15.8元）</v>
+        <v>【真好】黑猪肉爆汁烤肠原味400g</v>
       </c>
       <c r="C36" t="str">
-        <v>6970185773461</v>
+        <v>6942209639503</v>
       </c>
       <c r="D36" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="E36" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="F36" t="str">
-        <v>第4层</v>
+        <v>第5层</v>
       </c>
       <c r="G36">
         <v>20</v>
       </c>
       <c r="H36">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I36">
-        <v>2.709</v>
+        <v>1.0462</v>
       </c>
       <c r="J36">
-        <v>46.053</v>
+        <v>12.5544</v>
       </c>
       <c r="K36">
-        <v>23.0265</v>
+        <v>6.2772</v>
       </c>
     </row>
     <row r="37">
@@ -9073,34 +9085,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B37" t="str">
-        <v>荠菜笋丁鸡胸肉水饺480g</v>
+        <v>肉馅芹菜饺480g（两袋仅15.8元）</v>
       </c>
       <c r="C37" t="str">
-        <v>6970185773782</v>
+        <v>6970185773461</v>
       </c>
       <c r="D37" t="str">
         <v>B</v>
       </c>
       <c r="E37" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜4</v>
       </c>
       <c r="F37" t="str">
-        <v>第2层</v>
+        <v>第5层</v>
       </c>
       <c r="G37">
         <v>20</v>
       </c>
       <c r="H37">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I37">
-        <v>3.069</v>
+        <v>2.709</v>
       </c>
       <c r="J37">
-        <v>52.173</v>
+        <v>51.471</v>
       </c>
       <c r="K37">
-        <v>26.0865</v>
+        <v>25.7355</v>
       </c>
     </row>
     <row r="38">
@@ -9108,19 +9120,19 @@
         <v>和县生活馆</v>
       </c>
       <c r="B38" t="str">
-        <v>肉馅玉米饺480g（两袋仅15.8元）</v>
+        <v>荠菜笋丁鸡胸肉水饺480g</v>
       </c>
       <c r="C38" t="str">
-        <v>6970185773454</v>
+        <v>6970185773782</v>
       </c>
       <c r="D38" t="str">
         <v>B</v>
       </c>
       <c r="E38" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜4</v>
       </c>
       <c r="F38" t="str">
-        <v>第3层</v>
+        <v>第5层</v>
       </c>
       <c r="G38">
         <v>20</v>
@@ -9129,13 +9141,13 @@
         <v>19</v>
       </c>
       <c r="I38">
-        <v>2.709</v>
+        <v>3.069</v>
       </c>
       <c r="J38">
-        <v>51.471</v>
+        <v>58.311</v>
       </c>
       <c r="K38">
-        <v>25.7355</v>
+        <v>29.1555</v>
       </c>
     </row>
     <row r="39">
@@ -9143,34 +9155,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B39" t="str">
-        <v>生活馆_鲜肉小馄饨/++/512g</v>
+        <v>【真值】披萨奥尔良风味鸡肉味200克</v>
       </c>
       <c r="C39" t="str">
-        <v>6970185773478</v>
+        <v>6978425420038</v>
       </c>
       <c r="D39" t="str">
         <v>B</v>
       </c>
       <c r="E39" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="F39" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="G39">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H39">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I39">
-        <v>3.3248</v>
+        <v>1.134</v>
       </c>
       <c r="J39">
-        <v>56.5216</v>
+        <v>32.886</v>
       </c>
       <c r="K39">
-        <v>28.2608</v>
+        <v>16.443</v>
       </c>
     </row>
     <row r="40">
@@ -9178,34 +9190,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B40" t="str">
-        <v>生活馆_菌菇三鲜水饺/480g</v>
+        <v>冷冻食材_潮汕风味牛肉丸/160g</v>
       </c>
       <c r="C40" t="str">
-        <v>6970185773607</v>
+        <v>6923365101516</v>
       </c>
       <c r="D40" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="F40" t="str">
-        <v/>
+        <v>第3层</v>
       </c>
       <c r="G40">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H40">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I40">
-        <v>3.069</v>
+        <v>1.0036</v>
       </c>
       <c r="J40">
-        <v>61.38</v>
+        <v>32.1152</v>
       </c>
       <c r="K40">
-        <v>30.69</v>
+        <v>16.0576</v>
       </c>
     </row>
     <row r="41">
@@ -9213,34 +9225,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B41" t="str">
-        <v>魔芋羽衣甘蓝水饺480g</v>
+        <v>宏宝来俄式大脆筒牛奶味100g</v>
       </c>
       <c r="C41" t="str">
-        <v>6970185773799</v>
+        <v>6920858270995</v>
       </c>
       <c r="D41" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="F41" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="G41">
         <v>20</v>
       </c>
       <c r="H41">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I41">
-        <v>3.069</v>
+        <v>1.44</v>
       </c>
       <c r="J41">
-        <v>61.38</v>
+        <v>5.76</v>
       </c>
       <c r="K41">
-        <v>30.69</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="42">
@@ -9248,34 +9260,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B42" t="str">
-        <v>思念放心饺猪肉荠菜水饺</v>
+        <v>酷企鹅食用冰杯160g</v>
       </c>
       <c r="C42" t="str">
-        <v>6921665753398</v>
+        <v>6977602190221</v>
       </c>
       <c r="D42" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="E42" t="str">
-        <v>立柜3m-柜9</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="F42" t="str">
-        <v>第3层</v>
+        <v>分区1</v>
       </c>
       <c r="G42">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H42">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I42">
-        <v>2.8788</v>
+        <v>1.04</v>
       </c>
       <c r="J42">
-        <v>28.788</v>
+        <v>3.12</v>
       </c>
       <c r="K42">
-        <v>14.394</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="43">
@@ -9283,34 +9295,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B43" t="str">
-        <v>【真值】披萨奥尔良风味鸡肉味200克</v>
+        <v>雀巢8次方巧克力香草味84g</v>
       </c>
       <c r="C43" t="str">
-        <v>6978425420038</v>
+        <v>6918551807884</v>
       </c>
       <c r="D43" t="str">
         <v>B</v>
       </c>
       <c r="E43" t="str">
-        <v>立柜3m-柜9</v>
+        <v/>
       </c>
       <c r="F43" t="str">
-        <v>第4层</v>
+        <v/>
       </c>
       <c r="G43">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H43">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I43">
-        <v>1.134</v>
+        <v>0.2721</v>
       </c>
       <c r="J43">
-        <v>28.35</v>
+        <v>4.8978</v>
       </c>
       <c r="K43">
-        <v>14.175</v>
+        <v>2.4489</v>
       </c>
     </row>
     <row r="44">
@@ -9318,34 +9330,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B44" t="str">
-        <v>【真值】披萨精品榴莲芝士180g</v>
+        <v>小金条无核榴莲肉100g</v>
       </c>
       <c r="C44" t="str">
-        <v>6978425420045</v>
+        <v>6977480896154</v>
       </c>
       <c r="D44" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="E44" t="str">
-        <v>立柜3m-柜10</v>
+        <v/>
       </c>
       <c r="F44" t="str">
-        <v>第5层</v>
+        <v/>
       </c>
       <c r="G44">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H44">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I44">
-        <v>1.134</v>
+        <v>0.3776</v>
       </c>
       <c r="J44">
-        <v>30.618</v>
+        <v>22.656</v>
       </c>
       <c r="K44">
-        <v>15.309</v>
+        <v>11.328</v>
       </c>
     </row>
     <row r="45">
@@ -9353,34 +9365,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B45" t="str">
-        <v>【真值】披萨黑椒牛肉风味200g</v>
+        <v>伊利6重巧巧70g</v>
       </c>
       <c r="C45" t="str">
-        <v>6978425420021</v>
+        <v>6907992827353</v>
       </c>
       <c r="D45" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="E45" t="str">
-        <v>立柜3m-柜10</v>
+        <v/>
       </c>
       <c r="F45" t="str">
-        <v>第5层</v>
+        <v/>
       </c>
       <c r="G45">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H45">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I45">
-        <v>1.134</v>
+        <v>0.275</v>
       </c>
       <c r="J45">
-        <v>32.886</v>
+        <v>9.625</v>
       </c>
       <c r="K45">
-        <v>16.443</v>
+        <v>4.8125</v>
       </c>
     </row>
     <row r="46">
@@ -9388,292 +9400,47 @@
         <v>和县生活馆</v>
       </c>
       <c r="B46" t="str">
-        <v>冷冻食材_潮汕风味牛肉丸/160g</v>
+        <v>美好小酥肉800g</v>
       </c>
       <c r="C46" t="str">
-        <v>6923365101516</v>
+        <v>6971938880948</v>
       </c>
       <c r="D46" t="str">
-        <v>A</v>
+        <v>未评级</v>
       </c>
       <c r="E46" t="str">
-        <v>立柜3m-柜9</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v>第5层</v>
+        <v/>
       </c>
       <c r="G46">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H46">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I46">
-        <v>1.0036</v>
+        <v>4.725</v>
       </c>
       <c r="J46">
-        <v>32.1152</v>
+        <v>47.25</v>
       </c>
       <c r="K46">
-        <v>16.0576</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B47" t="str">
-        <v>酷企鹅食用冰杯160g</v>
-      </c>
-      <c r="C47" t="str">
-        <v>6977602190221</v>
-      </c>
-      <c r="D47" t="str">
-        <v>A</v>
-      </c>
-      <c r="E47" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
-      </c>
-      <c r="F47" t="str">
-        <v>分区1</v>
-      </c>
-      <c r="G47">
-        <v>24</v>
-      </c>
-      <c r="H47">
-        <v>3</v>
-      </c>
-      <c r="I47">
-        <v>1.04</v>
-      </c>
-      <c r="J47">
-        <v>3.12</v>
-      </c>
-      <c r="K47">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B48" t="str">
-        <v>和路雪绿舌头54g</v>
-      </c>
-      <c r="C48" t="str">
-        <v>6909493800453</v>
-      </c>
-      <c r="D48" t="str">
-        <v>B</v>
-      </c>
-      <c r="E48" t="str">
-        <v/>
-      </c>
-      <c r="F48" t="str">
-        <v/>
-      </c>
-      <c r="G48">
-        <v>36</v>
-      </c>
-      <c r="H48">
-        <v>36</v>
-      </c>
-      <c r="I48">
-        <v>0.2888</v>
-      </c>
-      <c r="J48">
-        <v>10.3968</v>
-      </c>
-      <c r="K48">
-        <v>5.1984</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B49" t="str">
-        <v>雀巢8次方巧克力香草味84g</v>
-      </c>
-      <c r="C49" t="str">
-        <v>6918551807884</v>
-      </c>
-      <c r="D49" t="str">
-        <v>B</v>
-      </c>
-      <c r="E49" t="str">
-        <v/>
-      </c>
-      <c r="F49" t="str">
-        <v/>
-      </c>
-      <c r="G49">
-        <v>18</v>
-      </c>
-      <c r="H49">
-        <v>18</v>
-      </c>
-      <c r="I49">
-        <v>0.2721</v>
-      </c>
-      <c r="J49">
-        <v>4.8978</v>
-      </c>
-      <c r="K49">
-        <v>2.4489</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B50" t="str">
-        <v>和路雪可爱多香草67g</v>
-      </c>
-      <c r="C50" t="str">
-        <v>6909493401032</v>
-      </c>
-      <c r="D50" t="str">
-        <v>B</v>
-      </c>
-      <c r="E50" t="str">
-        <v/>
-      </c>
-      <c r="F50" t="str">
-        <v/>
-      </c>
-      <c r="G50">
-        <v>24</v>
-      </c>
-      <c r="H50">
-        <v>24</v>
-      </c>
-      <c r="I50">
-        <v>0.558</v>
-      </c>
-      <c r="J50">
-        <v>13.392</v>
-      </c>
-      <c r="K50">
-        <v>6.696</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B51" t="str">
-        <v>小金条无核榴莲肉100g</v>
-      </c>
-      <c r="C51" t="str">
-        <v>6977480896154</v>
-      </c>
-      <c r="D51" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="E51" t="str">
-        <v/>
-      </c>
-      <c r="F51" t="str">
-        <v/>
-      </c>
-      <c r="G51">
-        <v>60</v>
-      </c>
-      <c r="H51">
-        <v>60</v>
-      </c>
-      <c r="I51">
-        <v>0.3776</v>
-      </c>
-      <c r="J51">
-        <v>22.656</v>
-      </c>
-      <c r="K51">
-        <v>11.328</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B52" t="str">
-        <v>伊利6重巧巧70g</v>
-      </c>
-      <c r="C52" t="str">
-        <v>6907992827353</v>
-      </c>
-      <c r="D52" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-      <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52">
-        <v>35</v>
-      </c>
-      <c r="H52">
-        <v>35</v>
-      </c>
-      <c r="I52">
-        <v>0.275</v>
-      </c>
-      <c r="J52">
-        <v>9.625</v>
-      </c>
-      <c r="K52">
-        <v>4.8125</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B53" t="str">
-        <v>美好小酥肉800g</v>
-      </c>
-      <c r="C53" t="str">
-        <v>6971938880948</v>
-      </c>
-      <c r="D53" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-      <c r="F53" t="str">
-        <v/>
-      </c>
-      <c r="G53">
-        <v>10</v>
-      </c>
-      <c r="H53">
-        <v>10</v>
-      </c>
-      <c r="I53">
-        <v>4.725</v>
-      </c>
-      <c r="J53">
-        <v>47.25</v>
-      </c>
-      <c r="K53">
         <v>23.625</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M53"/>
+  <autoFilter ref="A1:M46"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9730,28 +9497,28 @@
         <v>卧柜</v>
       </c>
       <c r="D2" t="str">
-        <v>卧柜2505mm-柜1</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="E2" t="str">
         <v>分区1</v>
       </c>
       <c r="H2">
-        <v>1942</v>
+        <v>1988</v>
       </c>
       <c r="I2">
-        <v>1885</v>
+        <v>1905</v>
       </c>
       <c r="J2">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L2">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="M2" t="str">
-        <v>思念-黑芝麻汤圆455g 1列；思念大黄米黑芝麻汤圆454g 1列；【真值】芝士鸡肉卷奥尔良味120g 6列；【真值】芝士牛肉卷黑胡椒味120g 1列</v>
+        <v>冷冻食材_包心鱼丸/160g(shg) 9列；青虾滑95% 150g 1列</v>
       </c>
       <c r="N2" t="str">
         <v>正常使用</v>
@@ -9768,25 +9535,25 @@
         <v>卧柜</v>
       </c>
       <c r="D3" t="str">
-        <v>卧柜2505mm-柜1</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="E3" t="str">
         <v>分区2</v>
       </c>
       <c r="H3">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="I3">
         <v>230</v>
       </c>
       <c r="J3">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="K3">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L3">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="M3" t="str">
         <v>酥皮牛肉馅饼500g 1列</v>
@@ -9806,28 +9573,28 @@
         <v>卧柜</v>
       </c>
       <c r="D4" t="str">
-        <v>卧柜2505mm-柜2</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="E4" t="str">
         <v>分区1</v>
       </c>
       <c r="H4">
-        <v>1942</v>
+        <v>1988</v>
       </c>
       <c r="I4">
-        <v>1905</v>
+        <v>1860</v>
       </c>
       <c r="J4">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="K4">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L4">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="M4" t="str">
-        <v>冷冻食材_包心鱼丸/160g(shg) 9列；青虾滑95% 150g 1列</v>
+        <v>【真值】香脆小酥肉原味800g 4列；台式鸡排400g 1列；玉米布丁酥400g 1列</v>
       </c>
       <c r="N4" t="str">
         <v>正常使用</v>
@@ -9844,25 +9611,25 @@
         <v>卧柜</v>
       </c>
       <c r="D5" t="str">
-        <v>卧柜2505mm-柜2</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="E5" t="str">
         <v>分区2</v>
       </c>
       <c r="H5">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="I5">
         <v>277.5</v>
       </c>
       <c r="J5">
-        <v>122.5</v>
+        <v>82.5</v>
       </c>
       <c r="K5">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L5">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="M5" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g 1列</v>
@@ -9882,28 +9649,28 @@
         <v>卧柜</v>
       </c>
       <c r="D6" t="str">
-        <v>卧柜2505mm-柜3</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="E6" t="str">
         <v>分区1</v>
       </c>
       <c r="H6">
-        <v>1942</v>
+        <v>1488</v>
       </c>
       <c r="I6">
-        <v>1900</v>
+        <v>1440</v>
       </c>
       <c r="J6">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K6">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L6">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="M6" t="str">
-        <v>【真值】香脆小酥肉原味800g 6列；台式鸡排400g 1列；玉米布丁酥400g 1列</v>
+        <v>【真值】披萨芝士培根风味200g 8列</v>
       </c>
       <c r="N6" t="str">
         <v>正常使用</v>
@@ -9920,25 +9687,25 @@
         <v>卧柜</v>
       </c>
       <c r="D7" t="str">
-        <v>卧柜2505mm-柜3</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="E7" t="str">
         <v>分区2</v>
       </c>
       <c r="H7">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="I7">
         <v>250</v>
       </c>
       <c r="J7">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="K7">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L7">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="M7" t="str">
         <v>【真值】甄选黄油鸡蛋灌饼皮640g 1列</v>
@@ -9958,28 +9725,28 @@
         <v>卧柜</v>
       </c>
       <c r="D8" t="str">
-        <v>卧柜2505mm-柜4</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="E8" t="str">
         <v>分区1</v>
       </c>
       <c r="H8">
-        <v>1942</v>
+        <v>1488</v>
       </c>
       <c r="I8">
-        <v>1890</v>
+        <v>1485</v>
       </c>
       <c r="J8">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L8">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="M8" t="str">
-        <v>冻榴莲500g 7列</v>
+        <v>思念-黑芝麻汤圆455g 1列；思念大黄米黑芝麻汤圆454g 1列；【真值】芝士鸡肉卷奥尔良味120g 4列；【真值】芝士牛肉卷黑胡椒味120g 1列</v>
       </c>
       <c r="N8" t="str">
         <v>正常使用</v>
@@ -9996,25 +9763,25 @@
         <v>卧柜</v>
       </c>
       <c r="D9" t="str">
-        <v>卧柜2505mm-柜4</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="E9" t="str">
         <v>分区2</v>
       </c>
       <c r="H9">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="I9">
         <v>230</v>
       </c>
       <c r="J9">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="K9">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L9">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="M9" t="str">
         <v>酥皮香菇猪肉馅饼500g 1列</v>
@@ -10034,28 +9801,28 @@
         <v>卧柜</v>
       </c>
       <c r="D10" t="str">
-        <v>卧柜1886mm-柜5</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="E10" t="str">
         <v>分区1</v>
       </c>
       <c r="H10">
-        <v>1295</v>
+        <v>988</v>
       </c>
       <c r="I10">
-        <v>1260</v>
+        <v>935</v>
       </c>
       <c r="J10">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="K10">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L10">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="M10" t="str">
-        <v>【真值】披萨芝士培根风味200g 7列</v>
+        <v>肉馅玉米饺480g（两袋仅15.8元） 1列；生活馆_鲜肉小馄饨/++/512g 1列；生活馆_菌菇三鲜水饺/480g 1列</v>
       </c>
       <c r="N10" t="str">
         <v>正常使用</v>
@@ -10072,28 +9839,28 @@
         <v>卧柜</v>
       </c>
       <c r="D11" t="str">
-        <v>卧柜1886mm-柜5</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="E11" t="str">
         <v>分区2</v>
       </c>
       <c r="H11">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="I11">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="J11">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K11">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L11">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="M11" t="str">
-        <v>安格斯牛排150g 1列</v>
+        <v>毛肚/200g 1列</v>
       </c>
       <c r="N11" t="str">
         <v>正常使用</v>
@@ -10104,34 +9871,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C12" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D12" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="E12" t="str">
         <v>分区1</v>
       </c>
       <c r="H12">
-        <v>1295</v>
+        <v>988</v>
       </c>
       <c r="I12">
-        <v>1290</v>
+        <v>905</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="K12">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L12">
-        <v>500</v>
+        <v>463</v>
       </c>
       <c r="M12" t="str">
-        <v>宏宝莱老冰棍80g 1列；蒙牛随变转巧克力雪糕65g 1列；伊利巧脆棒雪糕75g 1列；伊利大布丁60g 1列；酷企鹅食用冰杯160g 1列；上上鲜 绿色心情绿莎莎雪糕70g 1列；伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g 1列</v>
+        <v>魔芋羽衣甘蓝水饺480g 1列；思念放心饺猪肉荠菜水饺 1列；【真值】披萨精品榴莲芝士180g 1列；【真值】披萨黑椒牛肉风味200g 1列</v>
       </c>
       <c r="N12" t="str">
         <v>正常使用</v>
@@ -10142,34 +9909,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C13" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D13" t="str">
-        <v>冰淇淋柜1886mm-柜6</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="E13" t="str">
         <v>分区2</v>
       </c>
       <c r="H13">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="I13">
-        <v>320</v>
+        <v>275</v>
       </c>
       <c r="J13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K13">
-        <v>719</v>
+        <v>697</v>
       </c>
       <c r="L13">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="M13" t="str">
-        <v>宏宝来俄式大脆筒牛奶味100g 1列</v>
+        <v>带鱼段400g 1列</v>
       </c>
       <c r="N13" t="str">
         <v>正常使用</v>
@@ -10180,34 +9947,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="C14" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="D14" t="str">
-        <v>立柜3m-柜7</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="E14" t="str">
-        <v>第1层</v>
+        <v>分区1</v>
       </c>
       <c r="H14">
-        <v>710</v>
+        <v>1677</v>
       </c>
       <c r="I14">
-        <v>660</v>
+        <v>1655</v>
       </c>
       <c r="J14">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="K14">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L14">
-        <v>250</v>
+        <v>424</v>
       </c>
       <c r="M14" t="str">
-        <v>【真值】纸皮烧麦蛋黄味240g 4列</v>
+        <v>宏宝莱老冰棍80g 1列；蒙牛随变转巧克力雪糕65g 1列；伊利巧脆棒雪糕75g 1列；伊利大布丁60g 1列；酷企鹅食用冰杯160g 1列；上上鲜 绿色心情绿莎莎雪糕70g 1列；伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g 1列；和路雪绿舌头54g 1列；和路雪可爱多香草67g 1列</v>
       </c>
       <c r="N14" t="str">
         <v>正常使用</v>
@@ -10218,34 +9985,34 @@
         <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="C15" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="D15" t="str">
-        <v>立柜3m-柜7</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="E15" t="str">
-        <v>第2层</v>
+        <v>分区2</v>
       </c>
       <c r="H15">
-        <v>710</v>
+        <v>325</v>
       </c>
       <c r="I15">
-        <v>540</v>
+        <v>320</v>
       </c>
       <c r="J15">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L15">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="M15" t="str">
-        <v>皓月新西兰羔羊卷WMT/450g 3列</v>
+        <v>宏宝来俄式大脆筒牛奶味100g 1列</v>
       </c>
       <c r="N15" t="str">
         <v>正常使用</v>
@@ -10262,19 +10029,19 @@
         <v>立柜</v>
       </c>
       <c r="D16" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E16" t="str">
-        <v>第3层</v>
+        <v>第1层</v>
       </c>
       <c r="H16">
         <v>710</v>
       </c>
       <c r="I16">
-        <v>580</v>
+        <v>540</v>
       </c>
       <c r="J16">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="K16">
         <v>534</v>
@@ -10283,7 +10050,7 @@
         <v>250</v>
       </c>
       <c r="M16" t="str">
-        <v>【真值】大个爆汁鲜肉包800g 2列</v>
+        <v>火锅三宝/450g（毛肚+千层肚+鸭肠） 3列</v>
       </c>
       <c r="N16" t="str">
         <v>正常使用</v>
@@ -10300,19 +10067,19 @@
         <v>立柜</v>
       </c>
       <c r="D17" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E17" t="str">
-        <v>第4层</v>
+        <v>第2层</v>
       </c>
       <c r="H17">
         <v>710</v>
       </c>
       <c r="I17">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="J17">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="K17">
         <v>534</v>
@@ -10321,7 +10088,7 @@
         <v>250</v>
       </c>
       <c r="M17" t="str">
-        <v>麻辣小龙虾1000g 2列</v>
+        <v>【真值】大个爆汁鲜肉包800g 1列；【真值】大个三鲜青菜包800g 1列</v>
       </c>
       <c r="N17" t="str">
         <v>正常使用</v>
@@ -10338,19 +10105,19 @@
         <v>立柜</v>
       </c>
       <c r="D18" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E18" t="str">
-        <v>第5层</v>
+        <v>第3层</v>
       </c>
       <c r="H18">
         <v>710</v>
       </c>
       <c r="I18">
-        <v>660</v>
+        <v>500</v>
       </c>
       <c r="J18">
-        <v>50</v>
+        <v>210</v>
       </c>
       <c r="K18">
         <v>534</v>
@@ -10359,7 +10126,7 @@
         <v>250</v>
       </c>
       <c r="M18" t="str">
-        <v>番茄肉酱意大利面280g 3列</v>
+        <v>麻辣小龙虾1000g 2列</v>
       </c>
       <c r="N18" t="str">
         <v>正常使用</v>
@@ -10376,19 +10143,19 @@
         <v>立柜</v>
       </c>
       <c r="D19" t="str">
-        <v>立柜3m-柜7</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E19" t="str">
-        <v>第6层</v>
+        <v>第4层</v>
       </c>
       <c r="H19">
         <v>710</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="J19">
-        <v>710</v>
+        <v>50</v>
       </c>
       <c r="K19">
         <v>534</v>
@@ -10397,10 +10164,10 @@
         <v>250</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>番茄肉酱意大利面280g 3列</v>
       </c>
       <c r="N19" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="20">
@@ -10414,19 +10181,19 @@
         <v>立柜</v>
       </c>
       <c r="D20" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E20" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="H20">
         <v>710</v>
       </c>
       <c r="I20">
-        <v>630</v>
+        <v>705</v>
       </c>
       <c r="J20">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>534</v>
@@ -10435,7 +10202,7 @@
         <v>250</v>
       </c>
       <c r="M20" t="str">
-        <v>【真好】乌米三丁纸皮烧麦240g 3列</v>
+        <v>【真值】纸皮烧麦香菇味240g 3列；【真好】乌米三丁纸皮烧麦240g 1列</v>
       </c>
       <c r="N20" t="str">
         <v>正常使用</v>
@@ -10452,19 +10219,19 @@
         <v>立柜</v>
       </c>
       <c r="D21" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E21" t="str">
-        <v>第2层</v>
+        <v>第6层</v>
       </c>
       <c r="H21">
         <v>710</v>
       </c>
       <c r="I21">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>110</v>
+        <v>710</v>
       </c>
       <c r="K21">
         <v>534</v>
@@ -10473,10 +10240,10 @@
         <v>250</v>
       </c>
       <c r="M21" t="str">
-        <v>双色开花馒头（紫薯味+南瓜味）360g 3列</v>
+        <v/>
       </c>
       <c r="N21" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="22">
@@ -10490,19 +10257,19 @@
         <v>立柜</v>
       </c>
       <c r="D22" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E22" t="str">
-        <v>第3层</v>
+        <v>第1层</v>
       </c>
       <c r="H22">
         <v>710</v>
       </c>
       <c r="I22">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="J22">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K22">
         <v>534</v>
@@ -10511,7 +10278,7 @@
         <v>250</v>
       </c>
       <c r="M22" t="str">
-        <v>鸡胸肉/400g 2列；潮香村眼肉牛排3片装 1列</v>
+        <v>双色开花馒头（紫薯味+南瓜味）360g 3列</v>
       </c>
       <c r="N22" t="str">
         <v>正常使用</v>
@@ -10528,19 +10295,19 @@
         <v>立柜</v>
       </c>
       <c r="D23" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E23" t="str">
-        <v>第4层</v>
+        <v>第2层</v>
       </c>
       <c r="H23">
         <v>710</v>
       </c>
       <c r="I23">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="J23">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="K23">
         <v>534</v>
@@ -10549,7 +10316,7 @@
         <v>250</v>
       </c>
       <c r="M23" t="str">
-        <v>【真值】纸皮烧麦鲜肉味240g 4列</v>
+        <v>鸡胸肉/400g 1列；安格斯牛排150g 1列；潮香村眼肉牛排3片装 1列</v>
       </c>
       <c r="N23" t="str">
         <v>正常使用</v>
@@ -10566,19 +10333,19 @@
         <v>立柜</v>
       </c>
       <c r="D24" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E24" t="str">
-        <v>第5层</v>
+        <v>第3层</v>
       </c>
       <c r="H24">
         <v>710</v>
       </c>
       <c r="I24">
-        <v>465</v>
+        <v>660</v>
       </c>
       <c r="J24">
-        <v>245</v>
+        <v>50</v>
       </c>
       <c r="K24">
         <v>534</v>
@@ -10587,7 +10354,7 @@
         <v>250</v>
       </c>
       <c r="M24" t="str">
-        <v>抽肠青虾仁150g 1列；黑鱼片250g 1列</v>
+        <v>【真值】纸皮烧麦蛋黄味240g 4列</v>
       </c>
       <c r="N24" t="str">
         <v>正常使用</v>
@@ -10604,19 +10371,19 @@
         <v>立柜</v>
       </c>
       <c r="D25" t="str">
-        <v>立柜3m-柜8</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E25" t="str">
-        <v>第6层</v>
+        <v>第4层</v>
       </c>
       <c r="H25">
         <v>710</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="J25">
-        <v>710</v>
+        <v>245</v>
       </c>
       <c r="K25">
         <v>534</v>
@@ -10625,10 +10392,10 @@
         <v>250</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>抽肠青虾仁150g 1列；黑鱼片250g 1列</v>
       </c>
       <c r="N25" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="26">
@@ -10642,19 +10409,19 @@
         <v>立柜</v>
       </c>
       <c r="D26" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E26" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="H26">
         <v>710</v>
       </c>
       <c r="I26">
-        <v>660</v>
+        <v>550</v>
       </c>
       <c r="J26">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="K26">
         <v>534</v>
@@ -10663,7 +10430,7 @@
         <v>250</v>
       </c>
       <c r="M26" t="str">
-        <v>【真值】纸皮烧麦香菇味240g 4列</v>
+        <v>整虾/冷冻南美白虾250g 2列</v>
       </c>
       <c r="N26" t="str">
         <v>正常使用</v>
@@ -10680,19 +10447,19 @@
         <v>立柜</v>
       </c>
       <c r="D27" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E27" t="str">
-        <v>第2层</v>
+        <v>第6层</v>
       </c>
       <c r="H27">
         <v>710</v>
       </c>
       <c r="I27">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>170</v>
+        <v>710</v>
       </c>
       <c r="K27">
         <v>534</v>
@@ -10701,10 +10468,10 @@
         <v>250</v>
       </c>
       <c r="M27" t="str">
-        <v>火锅三宝/450g（毛肚+千层肚+鸭肠） 3列</v>
+        <v/>
       </c>
       <c r="N27" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="28">
@@ -10718,19 +10485,19 @@
         <v>立柜</v>
       </c>
       <c r="D28" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E28" t="str">
-        <v>第3层</v>
+        <v>第1层</v>
       </c>
       <c r="H28">
         <v>710</v>
       </c>
       <c r="I28">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="J28">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K28">
         <v>534</v>
@@ -10739,7 +10506,7 @@
         <v>250</v>
       </c>
       <c r="M28" t="str">
-        <v>手作奶香黄油开花馒头360g 2列；思念放心饺猪肉荠菜水饺 1列</v>
+        <v>【真值】纸皮烧麦鲜肉味240g 4列</v>
       </c>
       <c r="N28" t="str">
         <v>正常使用</v>
@@ -10756,19 +10523,19 @@
         <v>立柜</v>
       </c>
       <c r="D29" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E29" t="str">
-        <v>第4层</v>
+        <v>第2层</v>
       </c>
       <c r="H29">
         <v>710</v>
       </c>
       <c r="I29">
-        <v>540</v>
+        <v>610</v>
       </c>
       <c r="J29">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>534</v>
@@ -10777,7 +10544,7 @@
         <v>250</v>
       </c>
       <c r="M29" t="str">
-        <v>【真值】披萨奥尔良风味鸡肉味200克 3列</v>
+        <v>手作奶香黄油开花馒头360g 2列；【真值】披萨奥尔良风味鸡肉味200克 1列</v>
       </c>
       <c r="N29" t="str">
         <v>正常使用</v>
@@ -10794,10 +10561,10 @@
         <v>立柜</v>
       </c>
       <c r="D30" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E30" t="str">
-        <v>第5层</v>
+        <v>第3层</v>
       </c>
       <c r="H30">
         <v>710</v>
@@ -10832,19 +10599,19 @@
         <v>立柜</v>
       </c>
       <c r="D31" t="str">
-        <v>立柜3m-柜9</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E31" t="str">
-        <v>第6层</v>
+        <v>第4层</v>
       </c>
       <c r="H31">
         <v>710</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="J31">
-        <v>710</v>
+        <v>230</v>
       </c>
       <c r="K31">
         <v>534</v>
@@ -10853,10 +10620,10 @@
         <v>250</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>皓月新西兰羔羊卷WMT/450g 1列；原切肥羊卷300g 1列</v>
       </c>
       <c r="N31" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="32">
@@ -10870,10 +10637,10 @@
         <v>立柜</v>
       </c>
       <c r="D32" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E32" t="str">
-        <v>第1层</v>
+        <v>第5层</v>
       </c>
       <c r="H32">
         <v>710</v>
@@ -10908,19 +10675,19 @@
         <v>立柜</v>
       </c>
       <c r="D33" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E33" t="str">
-        <v>第2层</v>
+        <v>第6层</v>
       </c>
       <c r="H33">
         <v>710</v>
       </c>
       <c r="I33">
-        <v>620</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>90</v>
+        <v>710</v>
       </c>
       <c r="K33">
         <v>534</v>
@@ -10929,10 +10696,10 @@
         <v>250</v>
       </c>
       <c r="M33" t="str">
-        <v>荠菜笋丁鸡胸肉水饺480g 2列</v>
+        <v/>
       </c>
       <c r="N33" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="34">
@@ -10946,19 +10713,19 @@
         <v>立柜</v>
       </c>
       <c r="D34" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜4</v>
       </c>
       <c r="E34" t="str">
-        <v>第3层</v>
+        <v>第1层</v>
       </c>
       <c r="H34">
         <v>710</v>
       </c>
       <c r="I34">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>85</v>
+        <v>710</v>
       </c>
       <c r="K34">
         <v>534</v>
@@ -10967,10 +10734,10 @@
         <v>250</v>
       </c>
       <c r="M34" t="str">
-        <v>肉馅玉米饺480g（两袋仅15.8元） 1列；生活馆_鲜肉小馄饨/++/512g 1列</v>
+        <v/>
       </c>
       <c r="N34" t="str">
-        <v>正常使用</v>
+        <v>其他品类预留</v>
       </c>
     </row>
     <row r="35">
@@ -10984,19 +10751,19 @@
         <v>立柜</v>
       </c>
       <c r="D35" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜4</v>
       </c>
       <c r="E35" t="str">
-        <v>第4层</v>
+        <v>第2层</v>
       </c>
       <c r="H35">
         <v>710</v>
       </c>
       <c r="I35">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>80</v>
+        <v>710</v>
       </c>
       <c r="K35">
         <v>534</v>
@@ -11005,10 +10772,10 @@
         <v>250</v>
       </c>
       <c r="M35" t="str">
-        <v>肉馅芹菜饺480g（两袋仅15.8元） 2列</v>
+        <v/>
       </c>
       <c r="N35" t="str">
-        <v>正常使用</v>
+        <v>其他品类预留</v>
       </c>
     </row>
     <row r="36">
@@ -11022,19 +10789,19 @@
         <v>立柜</v>
       </c>
       <c r="D36" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜4</v>
       </c>
       <c r="E36" t="str">
-        <v>第5层</v>
+        <v>第3层</v>
       </c>
       <c r="H36">
         <v>710</v>
       </c>
       <c r="I36">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>170</v>
+        <v>710</v>
       </c>
       <c r="K36">
         <v>534</v>
@@ -11043,10 +10810,10 @@
         <v>250</v>
       </c>
       <c r="M36" t="str">
-        <v>【真值】披萨精品榴莲芝士180g 2列；【真值】披萨黑椒牛肉风味200g 1列</v>
+        <v/>
       </c>
       <c r="N36" t="str">
-        <v>正常使用</v>
+        <v>其他品类预留</v>
       </c>
     </row>
     <row r="37">
@@ -11060,10 +10827,10 @@
         <v>立柜</v>
       </c>
       <c r="D37" t="str">
-        <v>立柜3m-柜10</v>
+        <v>立柜3m-柜4</v>
       </c>
       <c r="E37" t="str">
-        <v>第6层</v>
+        <v>第4层</v>
       </c>
       <c r="H37">
         <v>710</v>
@@ -11084,20 +10851,96 @@
         <v/>
       </c>
       <c r="N37" t="str">
+        <v>其他品类预留</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B38" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C38" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D38" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E38" t="str">
+        <v>第5层</v>
+      </c>
+      <c r="H38">
+        <v>710</v>
+      </c>
+      <c r="I38">
+        <v>625</v>
+      </c>
+      <c r="J38">
+        <v>85</v>
+      </c>
+      <c r="K38">
+        <v>534</v>
+      </c>
+      <c r="L38">
+        <v>250</v>
+      </c>
+      <c r="M38" t="str">
+        <v>肉馅芹菜饺480g（两袋仅15.8元） 1列；荠菜笋丁鸡胸肉水饺480g 1列</v>
+      </c>
+      <c r="N38" t="str">
+        <v>正常使用</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B39" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C39" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D39" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E39" t="str">
+        <v>第6层</v>
+      </c>
+      <c r="H39">
+        <v>710</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>710</v>
+      </c>
+      <c r="K39">
+        <v>534</v>
+      </c>
+      <c r="L39">
+        <v>250</v>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v>存储位</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N37"/>
+  <autoFilter ref="A1:N39"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11221,7 +11064,7 @@
         <v>D</v>
       </c>
       <c r="F4">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -11233,10 +11076,10 @@
         <v>火锅肉类</v>
       </c>
       <c r="J4" t="str">
-        <v>毛肚/200g</v>
+        <v>冰鲜鸭肠/200g</v>
       </c>
       <c r="K4" t="str">
-        <v>6970138494795</v>
+        <v>6970138494825</v>
       </c>
     </row>
     <row r="5">
@@ -11253,25 +11096,25 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E5" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="F5">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>火锅食材</v>
+        <v>预制主食</v>
       </c>
       <c r="I5" t="str">
-        <v>火锅肉类</v>
+        <v>冷冻烧麦</v>
       </c>
       <c r="J5" t="str">
-        <v>冰鲜鸭肠/200g</v>
+        <v>【真好】黑猪肉梅干菜纸皮烧麦240g</v>
       </c>
       <c r="K5" t="str">
-        <v>6970138494825</v>
+        <v>6975889850562</v>
       </c>
     </row>
     <row r="6">
@@ -11291,7 +11134,7 @@
         <v>C</v>
       </c>
       <c r="F6">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -11300,13 +11143,13 @@
         <v>预制主食</v>
       </c>
       <c r="I6" t="str">
-        <v>冷冻包子</v>
+        <v>冷冻烧麦</v>
       </c>
       <c r="J6" t="str">
-        <v>【真值】大个三鲜青菜包800g</v>
+        <v>【真好】黑松露纸皮烧麦240g</v>
       </c>
       <c r="K6" t="str">
-        <v>6939545903474</v>
+        <v>6975889850548</v>
       </c>
     </row>
     <row r="7">
@@ -11323,25 +11166,25 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E7" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="F7">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>预制主食</v>
+        <v>冷冻食材</v>
       </c>
       <c r="I7" t="str">
-        <v>冷冻烧麦</v>
+        <v>冷冻食材</v>
       </c>
       <c r="J7" t="str">
-        <v>【真好】黑猪肉梅干菜纸皮烧麦240g</v>
+        <v>冷冻鸡翅根/400g</v>
       </c>
       <c r="K7" t="str">
-        <v>6975889850562</v>
+        <v>6970005561735</v>
       </c>
     </row>
     <row r="8">
@@ -11358,25 +11201,25 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E8" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="F8">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>预制主食</v>
+        <v>冷冻食材</v>
       </c>
       <c r="I8" t="str">
-        <v>冷冻烧麦</v>
+        <v>冷冻食材</v>
       </c>
       <c r="J8" t="str">
-        <v>【真好】黑松露纸皮烧麦240g</v>
+        <v>鸡爪/400g</v>
       </c>
       <c r="K8" t="str">
-        <v>6975889850548</v>
+        <v>6970005561711</v>
       </c>
     </row>
     <row r="9">
@@ -11393,10 +11236,10 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E9" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="F9">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -11405,13 +11248,13 @@
         <v>冷冻食材</v>
       </c>
       <c r="I9" t="str">
-        <v>冷冻食材</v>
+        <v>冷冻水果</v>
       </c>
       <c r="J9" t="str">
-        <v>冷冻鸡翅根/400g</v>
+        <v>冻榴莲500g</v>
       </c>
       <c r="K9" t="str">
-        <v>6970005561735</v>
+        <v>6977480891210</v>
       </c>
     </row>
     <row r="10">
@@ -11428,25 +11271,25 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E10" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="F10">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>冷冻食材</v>
+        <v>预制主食</v>
       </c>
       <c r="I10" t="str">
-        <v>冷冻食材</v>
+        <v>馒头发糕</v>
       </c>
       <c r="J10" t="str">
-        <v>鸡爪/400g</v>
+        <v>生活馆_料多多薯香乳酪包/400g</v>
       </c>
       <c r="K10" t="str">
-        <v>6970005561711</v>
+        <v>6971997913342</v>
       </c>
     </row>
     <row r="11">
@@ -11463,25 +11306,25 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E11" t="str">
-        <v>D</v>
+        <v>未评级</v>
       </c>
       <c r="F11">
-        <v>64</v>
+        <v>9999</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>冷冻食材</v>
+        <v>预制主食</v>
       </c>
       <c r="I11" t="str">
-        <v>冷冻水产</v>
+        <v>馒头发糕</v>
       </c>
       <c r="J11" t="str">
-        <v>整虾/冷冻南美白虾250g</v>
+        <v>鲜奶馒头300g</v>
       </c>
       <c r="K11" t="str">
-        <v>6971806122033</v>
+        <v>6973560306940</v>
       </c>
     </row>
     <row r="12">
@@ -11495,28 +11338,28 @@
         <v>暂不纳入</v>
       </c>
       <c r="D12" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
+        <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E12" t="str">
-        <v>D</v>
+        <v>B</v>
       </c>
       <c r="F12">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>冷冻食材</v>
+        <v>雪糕冰品</v>
       </c>
       <c r="I12" t="str">
-        <v>冷冻水产</v>
+        <v>雪糕冰淇淋</v>
       </c>
       <c r="J12" t="str">
-        <v>带鱼段400g</v>
+        <v>雀巢8次方巧克力香草味84g</v>
       </c>
       <c r="K12" t="str">
-        <v>6971806121982</v>
+        <v>6918551807884</v>
       </c>
     </row>
     <row r="13">
@@ -11530,28 +11373,28 @@
         <v>暂不纳入</v>
       </c>
       <c r="D13" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
+        <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E13" t="str">
-        <v>C</v>
+        <v>未评级</v>
       </c>
       <c r="F13">
-        <v>39</v>
+        <v>9999</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>预制主食</v>
+        <v>雪糕冰品</v>
       </c>
       <c r="I13" t="str">
-        <v>馒头发糕</v>
+        <v>雪糕冰淇淋</v>
       </c>
       <c r="J13" t="str">
-        <v>生活馆_料多多薯香乳酪包/400g</v>
+        <v>小金条无核榴莲肉100g</v>
       </c>
       <c r="K13" t="str">
-        <v>6971997913342</v>
+        <v>6977480896154</v>
       </c>
     </row>
     <row r="14">
@@ -11565,7 +11408,7 @@
         <v>暂不纳入</v>
       </c>
       <c r="D14" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
+        <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E14" t="str">
         <v>未评级</v>
@@ -11577,16 +11420,16 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>预制主食</v>
+        <v>雪糕冰品</v>
       </c>
       <c r="I14" t="str">
-        <v>馒头发糕</v>
+        <v>雪糕冰淇淋</v>
       </c>
       <c r="J14" t="str">
-        <v>鲜奶馒头300g</v>
+        <v>伊利6重巧巧70g</v>
       </c>
       <c r="K14" t="str">
-        <v>6973560306940</v>
+        <v>6907992827353</v>
       </c>
     </row>
     <row r="15">
@@ -11603,311 +11446,31 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E15" t="str">
-        <v>D</v>
+        <v>未评级</v>
       </c>
       <c r="F15">
-        <v>61</v>
+        <v>9999</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>火锅食材</v>
+        <v>预制菜类</v>
       </c>
       <c r="I15" t="str">
-        <v>牛羊肉卷</v>
+        <v>炸物小吃</v>
       </c>
       <c r="J15" t="str">
-        <v>原切肥羊卷300g</v>
+        <v>美好小酥肉800g</v>
       </c>
       <c r="K15" t="str">
-        <v>6926557321051</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B16" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C16" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D16" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
-      </c>
-      <c r="E16" t="str">
-        <v>C</v>
-      </c>
-      <c r="F16">
-        <v>36</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v>预制主食</v>
-      </c>
-      <c r="I16" t="str">
-        <v>水饺馄饨</v>
-      </c>
-      <c r="J16" t="str">
-        <v>生活馆_菌菇三鲜水饺/480g</v>
-      </c>
-      <c r="K16" t="str">
-        <v>6970185773607</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B17" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C17" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D17" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
-      </c>
-      <c r="E17" t="str">
-        <v>C</v>
-      </c>
-      <c r="F17">
-        <v>54</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v>预制主食</v>
-      </c>
-      <c r="I17" t="str">
-        <v>水饺馄饨</v>
-      </c>
-      <c r="J17" t="str">
-        <v>魔芋羽衣甘蓝水饺480g</v>
-      </c>
-      <c r="K17" t="str">
-        <v>6970185773799</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B18" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C18" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D18" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E18" t="str">
-        <v>B</v>
-      </c>
-      <c r="F18">
-        <v>22</v>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I18" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J18" t="str">
-        <v>和路雪绿舌头54g</v>
-      </c>
-      <c r="K18" t="str">
-        <v>6909493800453</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B19" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C19" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D19" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E19" t="str">
-        <v>B</v>
-      </c>
-      <c r="F19">
-        <v>23</v>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
-      <c r="H19" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I19" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J19" t="str">
-        <v>雀巢8次方巧克力香草味84g</v>
-      </c>
-      <c r="K19" t="str">
-        <v>6918551807884</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B20" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C20" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D20" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E20" t="str">
-        <v>B</v>
-      </c>
-      <c r="F20">
-        <v>33</v>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I20" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J20" t="str">
-        <v>和路雪可爱多香草67g</v>
-      </c>
-      <c r="K20" t="str">
-        <v>6909493401032</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B21" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C21" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D21" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E21" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F21">
-        <v>9999</v>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
-      <c r="H21" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I21" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J21" t="str">
-        <v>小金条无核榴莲肉100g</v>
-      </c>
-      <c r="K21" t="str">
-        <v>6977480896154</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B22" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C22" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D22" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E22" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F22">
-        <v>9999</v>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I22" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J22" t="str">
-        <v>伊利6重巧巧70g</v>
-      </c>
-      <c r="K22" t="str">
-        <v>6907992827353</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>和县生活馆</v>
-      </c>
-      <c r="B23" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C23" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D23" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
-      </c>
-      <c r="E23" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F23">
-        <v>9999</v>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
-      <c r="H23" t="str">
-        <v>预制菜类</v>
-      </c>
-      <c r="I23" t="str">
-        <v>炸物小吃</v>
-      </c>
-      <c r="J23" t="str">
-        <v>美好小酥肉800g</v>
-      </c>
-      <c r="K23" t="str">
         <v>6971938880948</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K23"/>
+  <autoFilter ref="A1:K15"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/drafts/新增门店_严格排柜结果.xlsx
+++ b/data/drafts/新增门店_严格排柜结果.xlsx
@@ -15,9 +15,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">'10%触发_门店汇总'!A1:R2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'10%触发_SKU明细'!A1:AN72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'10%触发_外储明细'!A1:M48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'10%触发_柜段余量'!A1:N35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'10%触发_未排入SKU清单'!A1:K18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'10%触发_外储明细'!A1:M46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'10%触发_柜段余量'!A1:N39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'10%触发_未排入SKU清单'!A1:K15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">'71SKU有效池明细'!A1:Q72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">'测算规则说明'!A1:B3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'可调整参数'!A1:C4</definedName>
@@ -478,7 +478,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>小于等于10%触发</v>
@@ -492,35 +492,35 @@
       </c>
       <c r="E2">
         <f>COUNTIFS('10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F2">
         <f>$D2-$E2</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <f>COUNTIFS('10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$O$2:$O$72,"纳入",'10%触发_SKU明细'!$AH$2:$AH$72,0)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2">
         <f>COUNTIFS('10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$O$2:$O$72,"纳入",'10%触发_SKU明细'!$AH$2:$AH$72,"&gt;0")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2">
         <f>SUMIFS('10%触发_SKU明细'!$AI$2:$AI$72,'10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>999.7</v>
+        <v>971.7</v>
       </c>
       <c r="J2">
         <f>SUMIFS('10%触发_SKU明细'!$AJ$2:$AJ$72,'10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>499.8</v>
+        <v>485.8</v>
       </c>
       <c r="K2">
         <f>$J2*$R2</f>
-        <v>620.7</v>
+        <v>603.3</v>
       </c>
       <c r="L2">
         <f>ROUNDUP($K2*'可调整参数'!$B$3,0)</f>
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="M2" t="str">
         <f>IF($L2&gt;'可调整参数'!$B$4,"超754L","未超754L")</f>
@@ -678,7 +678,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>酥皮牛肉馅饼500g</v>
@@ -720,7 +720,7 @@
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R2">
         <v>230</v>
@@ -731,15 +731,15 @@
       </c>
       <c r="T2">
         <f>IF($O2&lt;&gt;"纳入",0,$P2*$Q2)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U2">
         <f>$T2</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V2">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$C$2:$C$72,$C2)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W2">
         <v>24</v>
@@ -774,27 +774,27 @@
       </c>
       <c r="AG2">
         <f>IF($O2&lt;&gt;"纳入",0,MIN($W2,MAX(0,$U2-$AF2)))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AH2">
         <f>IF(OR($O2&lt;&gt;"纳入",$AN2&lt;&gt;"是"),0,MAX(0,$W2-$AG2))</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AI2">
         <f>$AH2*$AA2</f>
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="AJ2">
         <f>$AI2/2</f>
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
       <c r="AK2">
         <f>IFERROR($U2/$AB2,0)</f>
-        <v>15.19</v>
+        <v>20.25</v>
       </c>
       <c r="AL2">
         <f>IFERROR($AH2/$AB2,0)</f>
-        <v>17.72</v>
+        <v>12.66</v>
       </c>
       <c r="AM2" t="str">
         <f>IF($AH2=0,"无外储",IF($AL2&gt;60,"高风险",IF($AL2&gt;30,"中风险","低风险")))</f>
@@ -806,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g</v>
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R3">
         <v>277.5</v>
@@ -859,15 +859,15 @@
       </c>
       <c r="T3">
         <f>IF($O3&lt;&gt;"纳入",0,$P3*$Q3)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="U3">
         <f>$T3</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V3">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A3,'10%触发_SKU明细'!$C$2:$C$72,$C3)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W3">
         <v>20</v>
@@ -902,27 +902,27 @@
       </c>
       <c r="AG3">
         <f>IF($O3&lt;&gt;"纳入",0,MIN($W3,MAX(0,$U3-$AF3)))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH3">
         <f>IF(OR($O3&lt;&gt;"纳入",$AN3&lt;&gt;"是"),0,MAX(0,$W3-$AG3))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI3">
         <f>$AH3*$AA3</f>
-        <v>16.9272</v>
+        <v>12.6954</v>
       </c>
       <c r="AJ3">
         <f>$AI3/2</f>
-        <v>8.4636</v>
+        <v>6.3477</v>
       </c>
       <c r="AK3">
         <f>IFERROR($U3/$AB3,0)</f>
-        <v>15.6</v>
+        <v>17.83</v>
       </c>
       <c r="AL3">
         <f>IFERROR($AH3/$AB3,0)</f>
-        <v>8.91</v>
+        <v>6.69</v>
       </c>
       <c r="AM3" t="str">
         <f>IF($AH3=0,"无外储",IF($AL3&gt;60,"高风险",IF($AL3&gt;30,"中风险","低风险")))</f>
@@ -934,7 +934,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>【真值】甄选黄油鸡蛋灌饼皮640g</v>
@@ -961,7 +961,7 @@
         <v>卧柜</v>
       </c>
       <c r="L4" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="M4" t="str">
         <v>分区2</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>酥皮香菇猪肉馅饼500g</v>
@@ -1089,7 +1089,7 @@
         <v>卧柜</v>
       </c>
       <c r="L5" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M5" t="str">
         <v>分区2</v>
@@ -1104,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R5">
         <v>230</v>
@@ -1115,15 +1115,15 @@
       </c>
       <c r="T5">
         <f>IF($O5&lt;&gt;"纳入",0,$P5*$Q5)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U5">
         <f>$T5</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V5">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A5,'10%触发_SKU明细'!$C$2:$C$72,$C5)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W5">
         <v>24</v>
@@ -1158,27 +1158,27 @@
       </c>
       <c r="AG5">
         <f>IF($O5&lt;&gt;"纳入",0,MIN($W5,MAX(0,$U5-$AF5)))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AH5">
         <f>IF(OR($O5&lt;&gt;"纳入",$AN5&lt;&gt;"是"),0,MAX(0,$W5-$AG5))</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AI5">
         <f>$AH5*$AA5</f>
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="AJ5">
         <f>$AI5/2</f>
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
       <c r="AK5">
         <f>IFERROR($U5/$AB5,0)</f>
-        <v>28.86</v>
+        <v>38.48</v>
       </c>
       <c r="AL5">
         <f>IFERROR($AH5/$AB5,0)</f>
-        <v>33.67</v>
+        <v>24.05</v>
       </c>
       <c r="AM5" t="str">
         <f>IF($AH5=0,"无外储",IF($AL5&gt;60,"高风险",IF($AL5&gt;30,"中风险","低风险")))</f>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>纸皮韭菜盒子280g</v>
@@ -1318,7 +1318,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>老上海葱油饼900g</v>
@@ -1446,7 +1446,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>毛肚/200g</v>
@@ -1470,13 +1470,13 @@
         <v>火锅肉类</v>
       </c>
       <c r="K8" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L8" t="str">
-        <v>立柜3m-柜3</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M8" t="str">
-        <v>第3层</v>
+        <v>分区2</v>
       </c>
       <c r="N8" t="str">
         <v>主陈列</v>
@@ -1485,29 +1485,29 @@
         <v>纳入</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="R8">
         <v>224</v>
       </c>
       <c r="S8">
         <f>IF($O8&lt;&gt;"纳入",0,$P8*$R8)</f>
-        <v>448</v>
+        <v>224</v>
       </c>
       <c r="T8">
         <f>IF($O8&lt;&gt;"纳入",0,$P8*$Q8)</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="U8">
         <f>$T8</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="V8">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A8,'10%触发_SKU明细'!$C$2:$C$72,$C8)</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="W8">
         <v>32</v>
@@ -1538,31 +1538,31 @@
       </c>
       <c r="AF8">
         <f>IF($O8&lt;&gt;"纳入",0,ROUNDUP($U8*'可调整参数'!$B$2,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG8">
         <f>IF($O8&lt;&gt;"纳入",0,MIN($W8,MAX(0,$U8-$AF8)))</f>
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AH8">
         <f>IF(OR($O8&lt;&gt;"纳入",$AN8&lt;&gt;"是"),0,MAX(0,$W8-$AG8))</f>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AI8">
         <f>$AH8*$AA8</f>
-        <v>29.7925</v>
+        <v>11.917</v>
       </c>
       <c r="AJ8">
         <f>$AI8/2</f>
-        <v>14.8963</v>
+        <v>5.9585</v>
       </c>
       <c r="AK8">
         <f>IFERROR($U8/$AB8,0)</f>
-        <v>16.1</v>
+        <v>50.32</v>
       </c>
       <c r="AL8">
         <f>IFERROR($AH8/$AB8,0)</f>
-        <v>50.32</v>
+        <v>20.13</v>
       </c>
       <c r="AM8" t="str">
         <f>IF($AH8=0,"无外储",IF($AL8&gt;60,"高风险",IF($AL8&gt;30,"中风险","低风险")))</f>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>火锅三宝/450g（毛肚+千层肚+鸭肠）</v>
@@ -1604,7 +1604,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M9" t="str">
-        <v>第2层</v>
+        <v>第1层</v>
       </c>
       <c r="N9" t="str">
         <v>主陈列</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
         <v>冰鲜鸭肠/200g</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
         <v>【真值】大个爆汁鲜肉包800g</v>
@@ -1860,7 +1860,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M11" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="N11" t="str">
         <v>主陈列</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
         <v>【真值】大个三鲜青菜包800g</v>
@@ -1988,7 +1988,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M12" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="N12" t="str">
         <v>主陈列</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
         <v>麻辣小龙虾1000g</v>
@@ -2116,7 +2116,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M13" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="N13" t="str">
         <v>主陈列</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>番茄肉酱意大利面280g</v>
@@ -2244,7 +2244,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M14" t="str">
-        <v>第1层</v>
+        <v>第4层</v>
       </c>
       <c r="N14" t="str">
         <v>主陈列</v>
@@ -2342,7 +2342,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>【真值】纸皮烧麦蛋黄味240g</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>【真值】纸皮烧麦鲜肉味240g</v>
@@ -2598,7 +2598,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>【真值】纸皮烧麦香菇味240g</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>【真好】乌米三丁纸皮烧麦240g</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>【真好】黑猪肉梅干菜纸皮烧麦240g</v>
@@ -2982,7 +2982,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>【真好】黑松露纸皮烧麦240g</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>鸡胸肉/400g</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>安格斯牛排150g</v>
@@ -3366,7 +3366,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>潮香村眼肉牛排3片装</v>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B24" t="str">
         <v>冷冻鸡翅根/400g</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B25" t="str">
         <v>鸡爪/400g</v>
@@ -3750,7 +3750,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B26" t="str">
         <v>抽肠青虾仁150g</v>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B27" t="str">
         <v>黑鱼片250g</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B28" t="str">
         <v>整虾/冷冻南美白虾250g</v>
@@ -4134,7 +4134,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
         <v>带鱼段400g</v>
@@ -4158,44 +4158,44 @@
         <v>冷冻水产</v>
       </c>
       <c r="K29" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="N29" t="str">
         <v>主陈列</v>
       </c>
       <c r="O29" t="str">
-        <v>暂不纳入</v>
+        <v>纳入</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="S29">
         <f>IF($O29&lt;&gt;"纳入",0,$P29*$R29)</f>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="T29">
         <f>IF($O29&lt;&gt;"纳入",0,$P29*$Q29)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U29">
         <f>$T29</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V29">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A29,'10%触发_SKU明细'!$C$2:$C$72,$C29)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W29">
         <v>20</v>
@@ -4226,31 +4226,31 @@
       </c>
       <c r="AF29">
         <f>IF($O29&lt;&gt;"纳入",0,ROUNDUP($U29*'可调整参数'!$B$2,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG29">
         <f>IF($O29&lt;&gt;"纳入",0,MIN($W29,MAX(0,$U29-$AF29)))</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH29">
         <f>IF(OR($O29&lt;&gt;"纳入",$AN29&lt;&gt;"是"),0,MAX(0,$W29-$AG29))</f>
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AI29">
         <f>$AH29*$AA29</f>
-        <v>45.1</v>
+        <v>15.785</v>
       </c>
       <c r="AJ29">
         <f>$AI29/2</f>
-        <v>22.55</v>
+        <v>7.8925</v>
       </c>
       <c r="AK29">
         <f>IFERROR($U29/$AB29,0)</f>
-        <v>0</v>
+        <v>55.13</v>
       </c>
       <c r="AL29">
         <f>IFERROR($AH29/$AB29,0)</f>
-        <v>73.5</v>
+        <v>25.73</v>
       </c>
       <c r="AM29" t="str">
         <f>IF($AH29=0,"无外储",IF($AL29&gt;60,"高风险",IF($AL29&gt;30,"中风险","低风险")))</f>
@@ -4262,7 +4262,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
         <v>冻榴莲500g</v>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
         <v>双色开花馒头（紫薯味+南瓜味）360g</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
         <v>手作奶香黄油开花馒头360g</v>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
         <v>生活馆_料多多薯香乳酪包/400g</v>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
         <v>鲜奶馒头300g</v>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
         <v>皓月新西兰羔羊卷WMT/450g</v>
@@ -5030,7 +5030,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B36" t="str">
         <v>原切肥羊卷300g</v>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B37" t="str">
         <v>【真好】黑猪肉爆汁烤肠原味400g</v>
@@ -5286,7 +5286,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B38" t="str">
         <v>肉馅芹菜饺480g（两袋仅15.8元）</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B39" t="str">
         <v>荠菜笋丁鸡胸肉水饺480g</v>
@@ -5542,7 +5542,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B40" t="str">
         <v>肉馅玉米饺480g（两袋仅15.8元）</v>
@@ -5569,7 +5569,7 @@
         <v>卧柜</v>
       </c>
       <c r="L40" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M40" t="str">
         <v>分区1</v>
@@ -5670,7 +5670,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B41" t="str">
         <v>生活馆_鲜肉小馄饨/++/512g</v>
@@ -5697,7 +5697,7 @@
         <v>卧柜</v>
       </c>
       <c r="L41" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M41" t="str">
         <v>分区1</v>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B42" t="str">
         <v>生活馆_菌菇三鲜水饺/480g</v>
@@ -5825,7 +5825,7 @@
         <v>卧柜</v>
       </c>
       <c r="L42" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M42" t="str">
         <v>分区1</v>
@@ -5926,7 +5926,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B43" t="str">
         <v>魔芋羽衣甘蓝水饺480g</v>
@@ -5953,7 +5953,7 @@
         <v>卧柜</v>
       </c>
       <c r="L43" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M43" t="str">
         <v>分区1</v>
@@ -6054,7 +6054,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B44" t="str">
         <v>思念放心饺猪肉荠菜水饺</v>
@@ -6081,7 +6081,7 @@
         <v>卧柜</v>
       </c>
       <c r="L44" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M44" t="str">
         <v>分区1</v>
@@ -6182,7 +6182,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B45" t="str">
         <v>【真值】披萨奥尔良风味鸡肉味200克</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B46" t="str">
         <v>【真值】披萨精品榴莲芝士180g</v>
@@ -6337,7 +6337,7 @@
         <v>卧柜</v>
       </c>
       <c r="L46" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M46" t="str">
         <v>分区1</v>
@@ -6349,7 +6349,7 @@
         <v>纳入</v>
       </c>
       <c r="P46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q46">
         <v>39</v>
@@ -6359,19 +6359,19 @@
       </c>
       <c r="S46">
         <f>IF($O46&lt;&gt;"纳入",0,$P46*$R46)</f>
-        <v>720</v>
+        <v>180</v>
       </c>
       <c r="T46">
         <f>IF($O46&lt;&gt;"纳入",0,$P46*$Q46)</f>
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="U46">
         <f>$T46</f>
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="V46">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A46,'10%触发_SKU明细'!$C$2:$C$72,$C46)</f>
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="W46">
         <v>30</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="AF46">
         <f>IF($O46&lt;&gt;"纳入",0,ROUNDUP($U46*'可调整参数'!$B$2,0))</f>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AG46">
         <f>IF($O46&lt;&gt;"纳入",0,MIN($W46,MAX(0,$U46-$AF46)))</f>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AK46">
         <f>IFERROR($U46/$AB46,0)</f>
-        <v>117.39</v>
+        <v>29.35</v>
       </c>
       <c r="AL46">
         <f>IFERROR($AH46/$AB46,0)</f>
@@ -6438,7 +6438,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B47" t="str">
         <v>【真值】披萨黑椒牛肉风味200g</v>
@@ -6465,7 +6465,7 @@
         <v>卧柜</v>
       </c>
       <c r="L47" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M47" t="str">
         <v>分区1</v>
@@ -6566,7 +6566,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B48" t="str">
         <v>【真值】披萨芝士培根风味200g</v>
@@ -6593,7 +6593,7 @@
         <v>卧柜</v>
       </c>
       <c r="L48" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="M48" t="str">
         <v>分区1</v>
@@ -6605,7 +6605,7 @@
         <v>纳入</v>
       </c>
       <c r="P48">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q48">
         <v>39</v>
@@ -6615,19 +6615,19 @@
       </c>
       <c r="S48">
         <f>IF($O48&lt;&gt;"纳入",0,$P48*$R48)</f>
-        <v>180</v>
+        <v>1440</v>
       </c>
       <c r="T48">
         <f>IF($O48&lt;&gt;"纳入",0,$P48*$Q48)</f>
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="U48">
         <f>$T48</f>
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="V48">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A48,'10%触发_SKU明细'!$C$2:$C$72,$C48)</f>
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="W48">
         <v>30</v>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="AF48">
         <f>IF($O48&lt;&gt;"纳入",0,ROUNDUP($U48*'可调整参数'!$B$2,0))</f>
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="AG48">
         <f>IF($O48&lt;&gt;"纳入",0,MIN($W48,MAX(0,$U48-$AF48)))</f>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AK48">
         <f>IFERROR($U48/$AB48,0)</f>
-        <v>32.93</v>
+        <v>263.47</v>
       </c>
       <c r="AL48">
         <f>IFERROR($AH48/$AB48,0)</f>
@@ -6694,7 +6694,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B49" t="str">
         <v>思念-黑芝麻汤圆455g</v>
@@ -6721,7 +6721,7 @@
         <v>卧柜</v>
       </c>
       <c r="L49" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M49" t="str">
         <v>分区1</v>
@@ -6736,7 +6736,7 @@
         <v>1</v>
       </c>
       <c r="Q49">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R49">
         <v>220</v>
@@ -6747,15 +6747,15 @@
       </c>
       <c r="T49">
         <f>IF($O49&lt;&gt;"纳入",0,$P49*$Q49)</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="U49">
         <f>$T49</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="V49">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A49,'10%触发_SKU明细'!$C$2:$C$72,$C49)</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="W49">
         <v>20</v>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="AF49">
         <f>IF($O49&lt;&gt;"纳入",0,ROUNDUP($U49*'可调整参数'!$B$2,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG49">
         <f>IF($O49&lt;&gt;"纳入",0,MIN($W49,MAX(0,$U49-$AF49)))</f>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="AK49">
         <f>IFERROR($U49/$AB49,0)</f>
-        <v>97.25</v>
+        <v>101.67</v>
       </c>
       <c r="AL49">
         <f>IFERROR($AH49/$AB49,0)</f>
@@ -6822,7 +6822,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B50" t="str">
         <v>思念大黄米黑芝麻汤圆454g</v>
@@ -6849,7 +6849,7 @@
         <v>卧柜</v>
       </c>
       <c r="L50" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M50" t="str">
         <v>分区1</v>
@@ -6950,7 +6950,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B51" t="str">
         <v>冷冻食材_潮汕风味牛肉丸/160g</v>
@@ -6980,7 +6980,7 @@
         <v>立柜3m-柜3</v>
       </c>
       <c r="M51" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="N51" t="str">
         <v>主陈列</v>
@@ -6989,7 +6989,7 @@
         <v>纳入</v>
       </c>
       <c r="P51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q51">
         <v>3</v>
@@ -6999,19 +6999,19 @@
       </c>
       <c r="S51">
         <f>IF($O51&lt;&gt;"纳入",0,$P51*$R51)</f>
-        <v>185</v>
+        <v>555</v>
       </c>
       <c r="T51">
         <f>IF($O51&lt;&gt;"纳入",0,$P51*$Q51)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="U51">
         <f>$T51</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V51">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A51,'10%触发_SKU明细'!$C$2:$C$72,$C51)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W51">
         <v>40</v>
@@ -7046,27 +7046,27 @@
       </c>
       <c r="AG51">
         <f>IF($O51&lt;&gt;"纳入",0,MIN($W51,MAX(0,$U51-$AF51)))</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AH51">
         <f>IF(OR($O51&lt;&gt;"纳入",$AN51&lt;&gt;"是"),0,MAX(0,$W51-$AG51))</f>
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AI51">
         <f>$AH51*$AA51</f>
-        <v>38.1368</v>
+        <v>32.1152</v>
       </c>
       <c r="AJ51">
         <f>$AI51/2</f>
-        <v>19.0684</v>
+        <v>16.0576</v>
       </c>
       <c r="AK51">
         <f>IFERROR($U51/$AB51,0)</f>
-        <v>1.57</v>
+        <v>4.72</v>
       </c>
       <c r="AL51">
         <f>IFERROR($AH51/$AB51,0)</f>
-        <v>19.94</v>
+        <v>16.8</v>
       </c>
       <c r="AM51" t="str">
         <f>IF($AH51=0,"无外储",IF($AL51&gt;60,"高风险",IF($AL51&gt;30,"中风险","低风险")))</f>
@@ -7078,7 +7078,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B52" t="str">
         <v>冷冻食材_包心鱼丸/160g(shg)</v>
@@ -7105,7 +7105,7 @@
         <v>卧柜</v>
       </c>
       <c r="L52" t="str">
-        <v>卧柜2505-柜2</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="M52" t="str">
         <v>分区1</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B53" t="str">
         <v>青虾滑95% 150g</v>
@@ -7233,7 +7233,7 @@
         <v>卧柜</v>
       </c>
       <c r="L53" t="str">
-        <v>卧柜2505-柜2</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="M53" t="str">
         <v>分区1</v>
@@ -7248,7 +7248,7 @@
         <v>1</v>
       </c>
       <c r="Q53">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="R53">
         <v>240</v>
@@ -7259,15 +7259,15 @@
       </c>
       <c r="T53">
         <f>IF($O53&lt;&gt;"纳入",0,$P53*$Q53)</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="U53">
         <f>$T53</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="V53">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A53,'10%触发_SKU明细'!$C$2:$C$72,$C53)</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="W53">
         <v>30</v>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AF53">
         <f>IF($O53&lt;&gt;"纳入",0,ROUNDUP($U53*'可调整参数'!$B$2,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG53">
         <f>IF($O53&lt;&gt;"纳入",0,MIN($W53,MAX(0,$U53-$AF53)))</f>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="AK53">
         <f>IFERROR($U53/$AB53,0)</f>
-        <v>100.1</v>
+        <v>104.65</v>
       </c>
       <c r="AL53">
         <f>IFERROR($AH53/$AB53,0)</f>
@@ -7334,7 +7334,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B54" t="str">
         <v>宏宝来俄式大脆筒牛奶味100g</v>
@@ -7462,7 +7462,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B55" t="str">
         <v>宏宝莱老冰棍80g</v>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B56" t="str">
         <v>蒙牛随变转巧克力雪糕65g</v>
@@ -7718,7 +7718,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B57" t="str">
         <v>伊利巧脆棒雪糕75g</v>
@@ -7846,7 +7846,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B58" t="str">
         <v>伊利大布丁60g</v>
@@ -7974,7 +7974,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B59" t="str">
         <v>酷企鹅食用冰杯160g</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B60" t="str">
         <v>上上鲜 绿色心情绿莎莎雪糕70g</v>
@@ -8230,7 +8230,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B61" t="str">
         <v>伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g</v>
@@ -8358,7 +8358,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B62" t="str">
         <v>和路雪绿舌头54g</v>
@@ -8381,39 +8381,45 @@
       <c r="H62" t="str">
         <v>雪糕冰淇淋</v>
       </c>
+      <c r="K62" t="str">
+        <v>冰淇淋柜</v>
+      </c>
       <c r="L62" t="str">
-        <v/>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>分区1</v>
+      </c>
+      <c r="N62" t="str">
+        <v>主陈列</v>
       </c>
       <c r="O62" t="str">
-        <v>暂不纳入</v>
+        <v>纳入</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="S62">
         <f>IF($O62&lt;&gt;"纳入",0,$P62*$R62)</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="T62">
         <f>IF($O62&lt;&gt;"纳入",0,$P62*$Q62)</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="U62">
         <f>$T62</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V62">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A62,'10%触发_SKU明细'!$C$2:$C$72,$C62)</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="W62">
         <v>36</v>
@@ -8444,31 +8450,31 @@
       </c>
       <c r="AF62">
         <f>IF($O62&lt;&gt;"纳入",0,ROUNDUP($U62*'可调整参数'!$B$2,0))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG62">
         <f>IF($O62&lt;&gt;"纳入",0,MIN($W62,MAX(0,$U62-$AF62)))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AH62">
         <f>IF(OR($O62&lt;&gt;"纳入",$AN62&lt;&gt;"是"),0,MAX(0,$W62-$AG62))</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AI62">
         <f>$AH62*$AA62</f>
-        <v>10.3968</v>
+        <v>0</v>
       </c>
       <c r="AJ62">
         <f>$AI62/2</f>
-        <v>5.1984</v>
+        <v>0</v>
       </c>
       <c r="AK62">
         <f>IFERROR($U62/$AB62,0)</f>
-        <v>0</v>
+        <v>142.89</v>
       </c>
       <c r="AL62">
         <f>IFERROR($AH62/$AB62,0)</f>
-        <v>26.79</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="str">
         <f>IF($AH62=0,"无外储",IF($AL62&gt;60,"高风险",IF($AL62&gt;30,"中风险","低风险")))</f>
@@ -8480,7 +8486,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B63" t="str">
         <v>雀巢8次方巧克力香草味84g</v>
@@ -8602,7 +8608,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B64" t="str">
         <v>和路雪可爱多香草67g</v>
@@ -8625,39 +8631,45 @@
       <c r="H64" t="str">
         <v>雪糕冰淇淋</v>
       </c>
+      <c r="K64" t="str">
+        <v>冰淇淋柜</v>
+      </c>
       <c r="L64" t="str">
-        <v/>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>分区1</v>
+      </c>
+      <c r="N64" t="str">
+        <v>主陈列</v>
       </c>
       <c r="O64" t="str">
-        <v>暂不纳入</v>
+        <v>纳入</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="S64">
         <f>IF($O64&lt;&gt;"纳入",0,$P64*$R64)</f>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="T64">
         <f>IF($O64&lt;&gt;"纳入",0,$P64*$Q64)</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="U64">
         <f>$T64</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="V64">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A64,'10%触发_SKU明细'!$C$2:$C$72,$C64)</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="W64">
         <v>24</v>
@@ -8688,31 +8700,31 @@
       </c>
       <c r="AF64">
         <f>IF($O64&lt;&gt;"纳入",0,ROUNDUP($U64*'可调整参数'!$B$2,0))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG64">
         <f>IF($O64&lt;&gt;"纳入",0,MIN($W64,MAX(0,$U64-$AF64)))</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH64">
         <f>IF(OR($O64&lt;&gt;"纳入",$AN64&lt;&gt;"是"),0,MAX(0,$W64-$AG64))</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI64">
         <f>$AH64*$AA64</f>
-        <v>13.392</v>
+        <v>0</v>
       </c>
       <c r="AJ64">
         <f>$AI64/2</f>
-        <v>6.696</v>
+        <v>0</v>
       </c>
       <c r="AK64">
         <f>IFERROR($U64/$AB64,0)</f>
-        <v>0</v>
+        <v>79.63</v>
       </c>
       <c r="AL64">
         <f>IFERROR($AH64/$AB64,0)</f>
-        <v>24.82</v>
+        <v>0</v>
       </c>
       <c r="AM64" t="str">
         <f>IF($AH64=0,"无外储",IF($AL64&gt;60,"高风险",IF($AL64&gt;30,"中风险","低风险")))</f>
@@ -8724,7 +8736,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B65" t="str">
         <v>小金条无核榴莲肉100g</v>
@@ -8846,7 +8858,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B66" t="str">
         <v>伊利6重巧巧70g</v>
@@ -8968,7 +8980,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B67" t="str">
         <v>【真值】芝士鸡肉卷奥尔良味120g</v>
@@ -8995,7 +9007,7 @@
         <v>卧柜</v>
       </c>
       <c r="L67" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M67" t="str">
         <v>分区1</v>
@@ -9007,7 +9019,7 @@
         <v>纳入</v>
       </c>
       <c r="P67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q67">
         <v>100</v>
@@ -9017,19 +9029,19 @@
       </c>
       <c r="S67">
         <f>IF($O67&lt;&gt;"纳入",0,$P67*$R67)</f>
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="T67">
         <f>IF($O67&lt;&gt;"纳入",0,$P67*$Q67)</f>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="U67">
         <f>$T67</f>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="V67">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A67,'10%触发_SKU明细'!$C$2:$C$72,$C67)</f>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="W67">
         <v>40</v>
@@ -9060,7 +9072,7 @@
       </c>
       <c r="AF67">
         <f>IF($O67&lt;&gt;"纳入",0,ROUNDUP($U67*'可调整参数'!$B$2,0))</f>
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AG67">
         <f>IF($O67&lt;&gt;"纳入",0,MIN($W67,MAX(0,$U67-$AF67)))</f>
@@ -9080,7 +9092,7 @@
       </c>
       <c r="AK67">
         <f>IFERROR($U67/$AB67,0)</f>
-        <v>64.4</v>
+        <v>257.58</v>
       </c>
       <c r="AL67">
         <f>IFERROR($AH67/$AB67,0)</f>
@@ -9096,7 +9108,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B68" t="str">
         <v>【真值】芝士牛肉卷黑胡椒味120g</v>
@@ -9123,7 +9135,7 @@
         <v>卧柜</v>
       </c>
       <c r="L68" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M68" t="str">
         <v>分区1</v>
@@ -9224,7 +9236,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B69" t="str">
         <v>【真值】香脆小酥肉原味800g</v>
@@ -9251,7 +9263,7 @@
         <v>卧柜</v>
       </c>
       <c r="L69" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M69" t="str">
         <v>分区1</v>
@@ -9352,7 +9364,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B70" t="str">
         <v>台式鸡排400g</v>
@@ -9379,7 +9391,7 @@
         <v>卧柜</v>
       </c>
       <c r="L70" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M70" t="str">
         <v>分区1</v>
@@ -9480,7 +9492,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B71" t="str">
         <v>玉米布丁酥400g</v>
@@ -9507,7 +9519,7 @@
         <v>卧柜</v>
       </c>
       <c r="L71" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M71" t="str">
         <v>分区1</v>
@@ -9608,7 +9620,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B72" t="str">
         <v>美好小酥肉800g</v>
@@ -9744,7 +9756,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9789,7 +9801,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>酥皮牛肉馅饼500g</v>
@@ -9810,21 +9822,21 @@
         <v>24</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>1.955</v>
       </c>
       <c r="J2">
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="K2">
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g</v>
@@ -9845,21 +9857,21 @@
         <v>20</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>2.1159</v>
       </c>
       <c r="J3">
-        <v>16.9272</v>
+        <v>12.6954</v>
       </c>
       <c r="K3">
-        <v>8.4636</v>
+        <v>6.3477</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>酥皮香菇猪肉馅饼500g</v>
@@ -9871,7 +9883,7 @@
         <v>C</v>
       </c>
       <c r="E4" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="F4" t="str">
         <v>分区2</v>
@@ -9880,21 +9892,21 @@
         <v>24</v>
       </c>
       <c r="H4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>1.955</v>
       </c>
       <c r="J4">
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="K4">
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>纸皮韭菜盒子280g</v>
@@ -9929,7 +9941,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>老上海葱油饼900g</v>
@@ -9964,7 +9976,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>毛肚/200g</v>
@@ -9976,30 +9988,30 @@
         <v>D</v>
       </c>
       <c r="E7" t="str">
-        <v>立柜3m-柜3</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="F7" t="str">
-        <v>第3层</v>
+        <v>分区2</v>
       </c>
       <c r="G7">
         <v>32</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>1.1917</v>
       </c>
       <c r="J7">
-        <v>29.7925</v>
+        <v>11.917</v>
       </c>
       <c r="K7">
-        <v>14.8963</v>
+        <v>5.9585</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>火锅三宝/450g（毛肚+千层肚+鸭肠）</v>
@@ -10014,7 +10026,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="F8" t="str">
-        <v>第2层</v>
+        <v>第1层</v>
       </c>
       <c r="G8">
         <v>12</v>
@@ -10034,7 +10046,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>冰鲜鸭肠/200g</v>
@@ -10069,7 +10081,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
         <v>【真值】大个爆汁鲜肉包800g</v>
@@ -10084,7 +10096,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="F10" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -10104,7 +10116,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
         <v>【真值】大个三鲜青菜包800g</v>
@@ -10119,7 +10131,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="F11" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -10139,7 +10151,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
         <v>麻辣小龙虾1000g</v>
@@ -10154,7 +10166,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="F12" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="G12">
         <v>9</v>
@@ -10174,7 +10186,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
         <v>番茄肉酱意大利面280g</v>
@@ -10189,7 +10201,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="F13" t="str">
-        <v>第1层</v>
+        <v>第4层</v>
       </c>
       <c r="G13">
         <v>36</v>
@@ -10209,7 +10221,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>【真值】纸皮烧麦蛋黄味240g</v>
@@ -10244,7 +10256,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>【真值】纸皮烧麦鲜肉味240g</v>
@@ -10279,7 +10291,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>【真值】纸皮烧麦香菇味240g</v>
@@ -10314,7 +10326,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>【真好】乌米三丁纸皮烧麦240g</v>
@@ -10349,7 +10361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>【真好】黑猪肉梅干菜纸皮烧麦240g</v>
@@ -10384,7 +10396,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>【真好】黑松露纸皮烧麦240g</v>
@@ -10419,7 +10431,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>鸡胸肉/400g</v>
@@ -10454,7 +10466,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>安格斯牛排150g</v>
@@ -10489,7 +10501,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>潮香村眼肉牛排3片装</v>
@@ -10524,7 +10536,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>冷冻鸡翅根/400g</v>
@@ -10559,7 +10571,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B24" t="str">
         <v>鸡爪/400g</v>
@@ -10594,7 +10606,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B25" t="str">
         <v>抽肠青虾仁150g</v>
@@ -10629,7 +10641,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B26" t="str">
         <v>黑鱼片250g</v>
@@ -10664,7 +10676,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B27" t="str">
         <v>整虾/冷冻南美白虾250g</v>
@@ -10699,7 +10711,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B28" t="str">
         <v>带鱼段400g</v>
@@ -10711,30 +10723,30 @@
         <v>D</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="G28">
         <v>20</v>
       </c>
       <c r="H28">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>2.255</v>
       </c>
       <c r="J28">
-        <v>45.1</v>
+        <v>15.785</v>
       </c>
       <c r="K28">
-        <v>22.55</v>
+        <v>7.8925</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
         <v>冻榴莲500g</v>
@@ -10769,7 +10781,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
         <v>双色开花馒头（紫薯味+南瓜味）360g</v>
@@ -10804,7 +10816,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
         <v>手作奶香黄油开花馒头360g</v>
@@ -10839,7 +10851,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
         <v>生活馆_料多多薯香乳酪包/400g</v>
@@ -10874,7 +10886,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
         <v>鲜奶馒头300g</v>
@@ -10909,7 +10921,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
         <v>皓月新西兰羔羊卷WMT/450g</v>
@@ -10944,7 +10956,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
         <v>原切肥羊卷300g</v>
@@ -10979,7 +10991,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B36" t="str">
         <v>【真好】黑猪肉爆汁烤肠原味400g</v>
@@ -11014,7 +11026,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B37" t="str">
         <v>肉馅芹菜饺480g（两袋仅15.8元）</v>
@@ -11049,7 +11061,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B38" t="str">
         <v>荠菜笋丁鸡胸肉水饺480g</v>
@@ -11084,7 +11096,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B39" t="str">
         <v>【真值】披萨奥尔良风味鸡肉味200克</v>
@@ -11119,7 +11131,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B40" t="str">
         <v>冷冻食材_潮汕风味牛肉丸/160g</v>
@@ -11134,27 +11146,27 @@
         <v>立柜3m-柜3</v>
       </c>
       <c r="F40" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="G40">
         <v>40</v>
       </c>
       <c r="H40">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I40">
         <v>1.0036</v>
       </c>
       <c r="J40">
-        <v>38.1368</v>
+        <v>32.1152</v>
       </c>
       <c r="K40">
-        <v>19.0684</v>
+        <v>16.0576</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B41" t="str">
         <v>宏宝来俄式大脆筒牛奶味100g</v>
@@ -11189,7 +11201,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B42" t="str">
         <v>酷企鹅食用冰杯160g</v>
@@ -11224,13 +11236,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B43" t="str">
-        <v>和路雪绿舌头54g</v>
+        <v>雀巢8次方巧克力香草味84g</v>
       </c>
       <c r="C43" t="str">
-        <v>6909493800453</v>
+        <v>6918551807884</v>
       </c>
       <c r="D43" t="str">
         <v>B</v>
@@ -11242,33 +11254,33 @@
         <v/>
       </c>
       <c r="G43">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="H43">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="I43">
-        <v>0.2888</v>
+        <v>0.2721</v>
       </c>
       <c r="J43">
-        <v>10.3968</v>
+        <v>4.8978</v>
       </c>
       <c r="K43">
-        <v>5.1984</v>
+        <v>2.4489</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B44" t="str">
-        <v>雀巢8次方巧克力香草味84g</v>
+        <v>小金条无核榴莲肉100g</v>
       </c>
       <c r="C44" t="str">
-        <v>6918551807884</v>
+        <v>6977480896154</v>
       </c>
       <c r="D44" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -11277,33 +11289,33 @@
         <v/>
       </c>
       <c r="G44">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="H44">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="I44">
-        <v>0.2721</v>
+        <v>0.3776</v>
       </c>
       <c r="J44">
-        <v>4.8978</v>
+        <v>22.656</v>
       </c>
       <c r="K44">
-        <v>2.4489</v>
+        <v>11.328</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B45" t="str">
-        <v>和路雪可爱多香草67g</v>
+        <v>伊利6重巧巧70g</v>
       </c>
       <c r="C45" t="str">
-        <v>6909493401032</v>
+        <v>6907992827353</v>
       </c>
       <c r="D45" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -11312,30 +11324,30 @@
         <v/>
       </c>
       <c r="G45">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H45">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I45">
-        <v>0.558</v>
+        <v>0.275</v>
       </c>
       <c r="J45">
-        <v>13.392</v>
+        <v>9.625</v>
       </c>
       <c r="K45">
-        <v>6.696</v>
+        <v>4.8125</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B46" t="str">
-        <v>小金条无核榴莲肉100g</v>
+        <v>美好小酥肉800g</v>
       </c>
       <c r="C46" t="str">
-        <v>6977480896154</v>
+        <v>6971938880948</v>
       </c>
       <c r="D46" t="str">
         <v>未评级</v>
@@ -11347,102 +11359,32 @@
         <v/>
       </c>
       <c r="G46">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="H46">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I46">
-        <v>0.3776</v>
+        <v>4.725</v>
       </c>
       <c r="J46">
-        <v>22.656</v>
+        <v>47.25</v>
       </c>
       <c r="K46">
-        <v>11.328</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B47" t="str">
-        <v>伊利6重巧巧70g</v>
-      </c>
-      <c r="C47" t="str">
-        <v>6907992827353</v>
-      </c>
-      <c r="D47" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="E47" t="str">
-        <v/>
-      </c>
-      <c r="F47" t="str">
-        <v/>
-      </c>
-      <c r="G47">
-        <v>35</v>
-      </c>
-      <c r="H47">
-        <v>35</v>
-      </c>
-      <c r="I47">
-        <v>0.275</v>
-      </c>
-      <c r="J47">
-        <v>9.625</v>
-      </c>
-      <c r="K47">
-        <v>4.8125</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B48" t="str">
-        <v>美好小酥肉800g</v>
-      </c>
-      <c r="C48" t="str">
-        <v>6971938880948</v>
-      </c>
-      <c r="D48" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="E48" t="str">
-        <v/>
-      </c>
-      <c r="F48" t="str">
-        <v/>
-      </c>
-      <c r="G48">
-        <v>10</v>
-      </c>
-      <c r="H48">
-        <v>10</v>
-      </c>
-      <c r="I48">
-        <v>4.725</v>
-      </c>
-      <c r="J48">
-        <v>47.25</v>
-      </c>
-      <c r="K48">
         <v>23.625</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M48"/>
+  <autoFilter ref="A1:M46"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11490,7 +11432,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>卧柜</v>
@@ -11509,20 +11451,20 @@
       </c>
       <c r="I2">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$L$2:$L$72,$D2,'10%触发_SKU明细'!$M$2:$M$72,$E2,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>1965</v>
+        <v>1905</v>
       </c>
       <c r="J2">
         <f>$H2-$I2</f>
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="K2">
         <v>697</v>
       </c>
       <c r="L2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M2" t="str">
-        <v>【真值】披萨精品榴莲芝士180g 4列；【真值】披萨黑椒牛肉风味200g 1列；【真值】披萨芝士培根风味200g 1列；思念-黑芝麻汤圆455g 1列；思念大黄米黑芝麻汤圆454g 1列；【真值】芝士鸡肉卷奥尔良味120g 1列；【真值】芝士牛肉卷黑胡椒味120g 1列</v>
+        <v>冷冻食材_包心鱼丸/160g(shg) 9列；青虾滑95% 150g 1列</v>
       </c>
       <c r="N2" t="str">
         <v>正常使用</v>
@@ -11530,7 +11472,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>卧柜</v>
@@ -11559,7 +11501,7 @@
         <v>697</v>
       </c>
       <c r="L3">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M3" t="str">
         <v>酥皮牛肉馅饼500g 1列</v>
@@ -11570,7 +11512,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>卧柜</v>
@@ -11589,20 +11531,20 @@
       </c>
       <c r="I4">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A4,'10%触发_SKU明细'!$L$2:$L$72,$D4,'10%触发_SKU明细'!$M$2:$M$72,$E4,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>1905</v>
+        <v>1860</v>
       </c>
       <c r="J4">
         <f>$H4-$I4</f>
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="K4">
         <v>697</v>
       </c>
       <c r="L4">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M4" t="str">
-        <v>冷冻食材_包心鱼丸/160g(shg) 9列；青虾滑95% 150g 1列</v>
+        <v>【真值】香脆小酥肉原味800g 4列；台式鸡排400g 1列；玉米布丁酥400g 1列</v>
       </c>
       <c r="N4" t="str">
         <v>正常使用</v>
@@ -11610,7 +11552,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>卧柜</v>
@@ -11639,7 +11581,7 @@
         <v>697</v>
       </c>
       <c r="L5">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M5" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g 1列</v>
@@ -11650,7 +11592,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>卧柜</v>
@@ -11659,30 +11601,30 @@
         <v>卧柜</v>
       </c>
       <c r="D6" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="E6" t="str">
         <v>分区1</v>
       </c>
       <c r="H6">
-        <v>1988</v>
+        <v>1488</v>
       </c>
       <c r="I6">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A6,'10%触发_SKU明细'!$L$2:$L$72,$D6,'10%触发_SKU明细'!$M$2:$M$72,$E6,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>1860</v>
+        <v>1440</v>
       </c>
       <c r="J6">
         <f>$H6-$I6</f>
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="K6">
         <v>697</v>
       </c>
       <c r="L6">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M6" t="str">
-        <v>【真值】香脆小酥肉原味800g 4列；台式鸡排400g 1列；玉米布丁酥400g 1列</v>
+        <v>【真值】披萨芝士培根风味200g 8列</v>
       </c>
       <c r="N6" t="str">
         <v>正常使用</v>
@@ -11690,7 +11632,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>卧柜</v>
@@ -11699,7 +11641,7 @@
         <v>卧柜</v>
       </c>
       <c r="D7" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="E7" t="str">
         <v>分区2</v>
@@ -11719,7 +11661,7 @@
         <v>697</v>
       </c>
       <c r="L7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M7" t="str">
         <v>【真值】甄选黄油鸡蛋灌饼皮640g 1列</v>
@@ -11730,7 +11672,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>卧柜</v>
@@ -11739,7 +11681,7 @@
         <v>卧柜</v>
       </c>
       <c r="D8" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="E8" t="str">
         <v>分区1</v>
@@ -11749,20 +11691,20 @@
       </c>
       <c r="I8">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A8,'10%触发_SKU明细'!$L$2:$L$72,$D8,'10%触发_SKU明细'!$M$2:$M$72,$E8,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="J8">
         <f>$H8-$I8</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <v>697</v>
       </c>
       <c r="L8">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M8" t="str">
-        <v>肉馅玉米饺480g（两袋仅15.8元） 1列；生活馆_鲜肉小馄饨/++/512g 1列；生活馆_菌菇三鲜水饺/480g 1列；魔芋羽衣甘蓝水饺480g 1列；思念放心饺猪肉荠菜水饺 1列</v>
+        <v>思念-黑芝麻汤圆455g 1列；思念大黄米黑芝麻汤圆454g 1列；【真值】芝士鸡肉卷奥尔良味120g 4列；【真值】芝士牛肉卷黑胡椒味120g 1列</v>
       </c>
       <c r="N8" t="str">
         <v>正常使用</v>
@@ -11770,7 +11712,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>卧柜</v>
@@ -11779,7 +11721,7 @@
         <v>卧柜</v>
       </c>
       <c r="D9" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="E9" t="str">
         <v>分区2</v>
@@ -11799,7 +11741,7 @@
         <v>697</v>
       </c>
       <c r="L9">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M9" t="str">
         <v>酥皮香菇猪肉馅饼500g 1列</v>
@@ -11810,39 +11752,39 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C10" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D10" t="str">
-        <v>冰淇淋柜1900-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="E10" t="str">
         <v>分区1</v>
       </c>
       <c r="H10">
-        <v>1386</v>
+        <v>988</v>
       </c>
       <c r="I10">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A10,'10%触发_SKU明细'!$L$2:$L$72,$D10,'10%触发_SKU明细'!$M$2:$M$72,$E10,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>1290</v>
+        <v>935</v>
       </c>
       <c r="J10">
         <f>$H10-$I10</f>
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="K10">
-        <v>697.5</v>
+        <v>697</v>
       </c>
       <c r="L10">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="M10" t="str">
-        <v>宏宝莱老冰棍80g 1列；蒙牛随变转巧克力雪糕65g 1列；伊利巧脆棒雪糕75g 1列；伊利大布丁60g 1列；酷企鹅食用冰杯160g 1列；上上鲜 绿色心情绿莎莎雪糕70g 1列；伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g 1列</v>
+        <v>肉馅玉米饺480g（两袋仅15.8元） 1列；生活馆_鲜肉小馄饨/++/512g 1列；生活馆_菌菇三鲜水饺/480g 1列</v>
       </c>
       <c r="N10" t="str">
         <v>正常使用</v>
@@ -11850,39 +11792,39 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C11" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D11" t="str">
-        <v>冰淇淋柜1900-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="E11" t="str">
         <v>分区2</v>
       </c>
       <c r="H11">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="I11">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A11,'10%触发_SKU明细'!$L$2:$L$72,$D11,'10%触发_SKU明细'!$M$2:$M$72,$E11,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="J11">
         <f>$H11-$I11</f>
-        <v>5</v>
+        <v>136</v>
       </c>
       <c r="K11">
-        <v>697.5</v>
+        <v>697</v>
       </c>
       <c r="L11">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="M11" t="str">
-        <v>宏宝来俄式大脆筒牛奶味100g 1列</v>
+        <v>毛肚/200g 1列</v>
       </c>
       <c r="N11" t="str">
         <v>正常使用</v>
@@ -11890,39 +11832,39 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C12" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D12" t="str">
-        <v>立柜3m-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="E12" t="str">
-        <v>第1层</v>
+        <v>分区1</v>
       </c>
       <c r="H12">
-        <v>710</v>
+        <v>988</v>
       </c>
       <c r="I12">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A12,'10%触发_SKU明细'!$L$2:$L$72,$D12,'10%触发_SKU明细'!$M$2:$M$72,$E12,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>660</v>
+        <v>905</v>
       </c>
       <c r="J12">
         <f>$H12-$I12</f>
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="K12">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L12">
-        <v>250</v>
+        <v>463</v>
       </c>
       <c r="M12" t="str">
-        <v>番茄肉酱意大利面280g 3列</v>
+        <v>魔芋羽衣甘蓝水饺480g 1列；思念放心饺猪肉荠菜水饺 1列；【真值】披萨精品榴莲芝士180g 1列；【真值】披萨黑椒牛肉风味200g 1列</v>
       </c>
       <c r="N12" t="str">
         <v>正常使用</v>
@@ -11930,39 +11872,39 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C13" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D13" t="str">
-        <v>立柜3m-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="E13" t="str">
-        <v>第2层</v>
+        <v>分区2</v>
       </c>
       <c r="H13">
-        <v>710</v>
+        <v>360</v>
       </c>
       <c r="I13">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A13,'10%触发_SKU明细'!$L$2:$L$72,$D13,'10%触发_SKU明细'!$M$2:$M$72,$E13,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>540</v>
+        <v>275</v>
       </c>
       <c r="J13">
         <f>$H13-$I13</f>
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="K13">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L13">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="M13" t="str">
-        <v>火锅三宝/450g（毛肚+千层肚+鸭肠） 3列</v>
+        <v>带鱼段400g 1列</v>
       </c>
       <c r="N13" t="str">
         <v>正常使用</v>
@@ -11970,39 +11912,39 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="C14" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="D14" t="str">
-        <v>立柜3m-柜1</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="E14" t="str">
-        <v>第3层</v>
+        <v>分区1</v>
       </c>
       <c r="H14">
-        <v>710</v>
+        <v>1677</v>
       </c>
       <c r="I14">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A14,'10%触发_SKU明细'!$L$2:$L$72,$D14,'10%触发_SKU明细'!$M$2:$M$72,$E14,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>580</v>
+        <v>1655</v>
       </c>
       <c r="J14">
         <f>$H14-$I14</f>
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="K14">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L14">
-        <v>250</v>
+        <v>424</v>
       </c>
       <c r="M14" t="str">
-        <v>【真值】大个爆汁鲜肉包800g 1列；【真值】大个三鲜青菜包800g 1列</v>
+        <v>宏宝莱老冰棍80g 1列；蒙牛随变转巧克力雪糕65g 1列；伊利巧脆棒雪糕75g 1列；伊利大布丁60g 1列；酷企鹅食用冰杯160g 1列；上上鲜 绿色心情绿莎莎雪糕70g 1列；伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g 1列；和路雪绿舌头54g 1列；和路雪可爱多香草67g 1列</v>
       </c>
       <c r="N14" t="str">
         <v>正常使用</v>
@@ -12010,39 +11952,39 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="C15" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="D15" t="str">
-        <v>立柜3m-柜1</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="E15" t="str">
-        <v>第4层</v>
+        <v>分区2</v>
       </c>
       <c r="H15">
-        <v>710</v>
+        <v>325</v>
       </c>
       <c r="I15">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A15,'10%触发_SKU明细'!$L$2:$L$72,$D15,'10%触发_SKU明细'!$M$2:$M$72,$E15,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="J15">
         <f>$H15-$I15</f>
-        <v>210</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L15">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="M15" t="str">
-        <v>麻辣小龙虾1000g 2列</v>
+        <v>宏宝来俄式大脆筒牛奶味100g 1列</v>
       </c>
       <c r="N15" t="str">
         <v>正常使用</v>
@@ -12050,7 +11992,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>立柜</v>
@@ -12062,18 +12004,18 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="E16" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="H16">
         <v>710</v>
       </c>
       <c r="I16">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A16,'10%触发_SKU明细'!$L$2:$L$72,$D16,'10%触发_SKU明细'!$M$2:$M$72,$E16,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>705</v>
+        <v>540</v>
       </c>
       <c r="J16">
         <f>$H16-$I16</f>
-        <v>5</v>
+        <v>170</v>
       </c>
       <c r="K16">
         <v>534</v>
@@ -12082,7 +12024,7 @@
         <v>250</v>
       </c>
       <c r="M16" t="str">
-        <v>【真值】纸皮烧麦香菇味240g 3列；【真好】乌米三丁纸皮烧麦240g 1列</v>
+        <v>火锅三宝/450g（毛肚+千层肚+鸭肠） 3列</v>
       </c>
       <c r="N16" t="str">
         <v>正常使用</v>
@@ -12090,7 +12032,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>立柜</v>
@@ -12102,18 +12044,18 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="E17" t="str">
-        <v>第6层</v>
+        <v>第2层</v>
       </c>
       <c r="H17">
         <v>710</v>
       </c>
       <c r="I17">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A17,'10%触发_SKU明细'!$L$2:$L$72,$D17,'10%触发_SKU明细'!$M$2:$M$72,$E17,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="J17">
         <f>$H17-$I17</f>
-        <v>710</v>
+        <v>130</v>
       </c>
       <c r="K17">
         <v>534</v>
@@ -12122,15 +12064,15 @@
         <v>250</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>【真值】大个爆汁鲜肉包800g 1列；【真值】大个三鲜青菜包800g 1列</v>
       </c>
       <c r="N17" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>立柜</v>
@@ -12139,21 +12081,21 @@
         <v>立柜</v>
       </c>
       <c r="D18" t="str">
-        <v>立柜3m-柜2</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E18" t="str">
-        <v>第1层</v>
+        <v>第3层</v>
       </c>
       <c r="H18">
         <v>710</v>
       </c>
       <c r="I18">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A18,'10%触发_SKU明细'!$L$2:$L$72,$D18,'10%触发_SKU明细'!$M$2:$M$72,$E18,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J18">
         <f>$H18-$I18</f>
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="K18">
         <v>534</v>
@@ -12162,7 +12104,7 @@
         <v>250</v>
       </c>
       <c r="M18" t="str">
-        <v>双色开花馒头（紫薯味+南瓜味）360g 3列</v>
+        <v>麻辣小龙虾1000g 2列</v>
       </c>
       <c r="N18" t="str">
         <v>正常使用</v>
@@ -12170,7 +12112,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>立柜</v>
@@ -12179,21 +12121,21 @@
         <v>立柜</v>
       </c>
       <c r="D19" t="str">
-        <v>立柜3m-柜2</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E19" t="str">
-        <v>第2层</v>
+        <v>第4层</v>
       </c>
       <c r="H19">
         <v>710</v>
       </c>
       <c r="I19">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A19,'10%触发_SKU明细'!$L$2:$L$72,$D19,'10%触发_SKU明细'!$M$2:$M$72,$E19,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="J19">
         <f>$H19-$I19</f>
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K19">
         <v>534</v>
@@ -12202,7 +12144,7 @@
         <v>250</v>
       </c>
       <c r="M19" t="str">
-        <v>鸡胸肉/400g 1列；安格斯牛排150g 1列；潮香村眼肉牛排3片装 1列</v>
+        <v>番茄肉酱意大利面280g 3列</v>
       </c>
       <c r="N19" t="str">
         <v>正常使用</v>
@@ -12210,7 +12152,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>立柜</v>
@@ -12219,21 +12161,21 @@
         <v>立柜</v>
       </c>
       <c r="D20" t="str">
-        <v>立柜3m-柜2</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E20" t="str">
-        <v>第3层</v>
+        <v>第5层</v>
       </c>
       <c r="H20">
         <v>710</v>
       </c>
       <c r="I20">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A20,'10%触发_SKU明细'!$L$2:$L$72,$D20,'10%触发_SKU明细'!$M$2:$M$72,$E20,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>660</v>
+        <v>705</v>
       </c>
       <c r="J20">
         <f>$H20-$I20</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>534</v>
@@ -12242,7 +12184,7 @@
         <v>250</v>
       </c>
       <c r="M20" t="str">
-        <v>【真值】纸皮烧麦蛋黄味240g 4列</v>
+        <v>【真值】纸皮烧麦香菇味240g 3列；【真好】乌米三丁纸皮烧麦240g 1列</v>
       </c>
       <c r="N20" t="str">
         <v>正常使用</v>
@@ -12250,7 +12192,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>立柜</v>
@@ -12259,21 +12201,21 @@
         <v>立柜</v>
       </c>
       <c r="D21" t="str">
-        <v>立柜3m-柜2</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E21" t="str">
-        <v>第4层</v>
+        <v>第6层</v>
       </c>
       <c r="H21">
         <v>710</v>
       </c>
       <c r="I21">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A21,'10%触发_SKU明细'!$L$2:$L$72,$D21,'10%触发_SKU明细'!$M$2:$M$72,$E21,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <f>$H21-$I21</f>
-        <v>245</v>
+        <v>710</v>
       </c>
       <c r="K21">
         <v>534</v>
@@ -12282,15 +12224,15 @@
         <v>250</v>
       </c>
       <c r="M21" t="str">
-        <v>抽肠青虾仁150g 1列；黑鱼片250g 1列</v>
+        <v/>
       </c>
       <c r="N21" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>立柜</v>
@@ -12302,18 +12244,18 @@
         <v>立柜3m-柜2</v>
       </c>
       <c r="E22" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="H22">
         <v>710</v>
       </c>
       <c r="I22">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A22,'10%触发_SKU明细'!$L$2:$L$72,$D22,'10%触发_SKU明细'!$M$2:$M$72,$E22,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="J22">
         <f>$H22-$I22</f>
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="K22">
         <v>534</v>
@@ -12322,7 +12264,7 @@
         <v>250</v>
       </c>
       <c r="M22" t="str">
-        <v>整虾/冷冻南美白虾250g 2列</v>
+        <v>双色开花馒头（紫薯味+南瓜味）360g 3列</v>
       </c>
       <c r="N22" t="str">
         <v>正常使用</v>
@@ -12330,7 +12272,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>立柜</v>
@@ -12342,18 +12284,18 @@
         <v>立柜3m-柜2</v>
       </c>
       <c r="E23" t="str">
-        <v>第6层</v>
+        <v>第2层</v>
       </c>
       <c r="H23">
         <v>710</v>
       </c>
       <c r="I23">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A23,'10%触发_SKU明细'!$L$2:$L$72,$D23,'10%触发_SKU明细'!$M$2:$M$72,$E23,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="J23">
         <f>$H23-$I23</f>
-        <v>710</v>
+        <v>35</v>
       </c>
       <c r="K23">
         <v>534</v>
@@ -12362,15 +12304,15 @@
         <v>250</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>鸡胸肉/400g 1列；安格斯牛排150g 1列；潮香村眼肉牛排3片装 1列</v>
       </c>
       <c r="N23" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B24" t="str">
         <v>立柜</v>
@@ -12379,10 +12321,10 @@
         <v>立柜</v>
       </c>
       <c r="D24" t="str">
-        <v>立柜3m-柜3</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E24" t="str">
-        <v>第1层</v>
+        <v>第3层</v>
       </c>
       <c r="H24">
         <v>710</v>
@@ -12402,7 +12344,7 @@
         <v>250</v>
       </c>
       <c r="M24" t="str">
-        <v>【真值】纸皮烧麦鲜肉味240g 4列</v>
+        <v>【真值】纸皮烧麦蛋黄味240g 4列</v>
       </c>
       <c r="N24" t="str">
         <v>正常使用</v>
@@ -12410,7 +12352,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B25" t="str">
         <v>立柜</v>
@@ -12419,21 +12361,21 @@
         <v>立柜</v>
       </c>
       <c r="D25" t="str">
-        <v>立柜3m-柜3</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E25" t="str">
-        <v>第2层</v>
+        <v>第4层</v>
       </c>
       <c r="H25">
         <v>710</v>
       </c>
       <c r="I25">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A25,'10%触发_SKU明细'!$L$2:$L$72,$D25,'10%触发_SKU明细'!$M$2:$M$72,$E25,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>610</v>
+        <v>465</v>
       </c>
       <c r="J25">
         <f>$H25-$I25</f>
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="K25">
         <v>534</v>
@@ -12442,7 +12384,7 @@
         <v>250</v>
       </c>
       <c r="M25" t="str">
-        <v>手作奶香黄油开花馒头360g 2列；【真值】披萨奥尔良风味鸡肉味200克 1列</v>
+        <v>抽肠青虾仁150g 1列；黑鱼片250g 1列</v>
       </c>
       <c r="N25" t="str">
         <v>正常使用</v>
@@ -12450,7 +12392,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B26" t="str">
         <v>立柜</v>
@@ -12459,21 +12401,21 @@
         <v>立柜</v>
       </c>
       <c r="D26" t="str">
-        <v>立柜3m-柜3</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E26" t="str">
-        <v>第3层</v>
+        <v>第5层</v>
       </c>
       <c r="H26">
         <v>710</v>
       </c>
       <c r="I26">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A26,'10%触发_SKU明细'!$L$2:$L$72,$D26,'10%触发_SKU明细'!$M$2:$M$72,$E26,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>448</v>
+        <v>550</v>
       </c>
       <c r="J26">
         <f>$H26-$I26</f>
-        <v>262</v>
+        <v>160</v>
       </c>
       <c r="K26">
         <v>534</v>
@@ -12482,7 +12424,7 @@
         <v>250</v>
       </c>
       <c r="M26" t="str">
-        <v>毛肚/200g 2列</v>
+        <v>整虾/冷冻南美白虾250g 2列</v>
       </c>
       <c r="N26" t="str">
         <v>正常使用</v>
@@ -12490,7 +12432,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B27" t="str">
         <v>立柜</v>
@@ -12499,21 +12441,21 @@
         <v>立柜</v>
       </c>
       <c r="D27" t="str">
-        <v>立柜3m-柜3</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E27" t="str">
-        <v>第4层</v>
+        <v>第6层</v>
       </c>
       <c r="H27">
         <v>710</v>
       </c>
       <c r="I27">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A27,'10%触发_SKU明细'!$L$2:$L$72,$D27,'10%触发_SKU明细'!$M$2:$M$72,$E27,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <f>$H27-$I27</f>
-        <v>45</v>
+        <v>710</v>
       </c>
       <c r="K27">
         <v>534</v>
@@ -12522,15 +12464,15 @@
         <v>250</v>
       </c>
       <c r="M27" t="str">
-        <v>皓月新西兰羔羊卷WMT/450g 1列；原切肥羊卷300g 1列；冷冻食材_潮汕风味牛肉丸/160g 1列</v>
+        <v/>
       </c>
       <c r="N27" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B28" t="str">
         <v>立柜</v>
@@ -12542,18 +12484,18 @@
         <v>立柜3m-柜3</v>
       </c>
       <c r="E28" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="H28">
         <v>710</v>
       </c>
       <c r="I28">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A28,'10%触发_SKU明细'!$L$2:$L$72,$D28,'10%触发_SKU明细'!$M$2:$M$72,$E28,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="J28">
         <f>$H28-$I28</f>
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K28">
         <v>534</v>
@@ -12562,7 +12504,7 @@
         <v>250</v>
       </c>
       <c r="M28" t="str">
-        <v>【真好】黑猪肉爆汁烤肠原味400g 3列</v>
+        <v>【真值】纸皮烧麦鲜肉味240g 4列</v>
       </c>
       <c r="N28" t="str">
         <v>正常使用</v>
@@ -12570,7 +12512,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
         <v>立柜</v>
@@ -12582,18 +12524,18 @@
         <v>立柜3m-柜3</v>
       </c>
       <c r="E29" t="str">
-        <v>第6层</v>
+        <v>第2层</v>
       </c>
       <c r="H29">
         <v>710</v>
       </c>
       <c r="I29">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A29,'10%触发_SKU明细'!$L$2:$L$72,$D29,'10%触发_SKU明细'!$M$2:$M$72,$E29,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="J29">
         <f>$H29-$I29</f>
-        <v>710</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>534</v>
@@ -12602,15 +12544,15 @@
         <v>250</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>手作奶香黄油开花馒头360g 2列；【真值】披萨奥尔良风味鸡肉味200克 1列</v>
       </c>
       <c r="N29" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
         <v>立柜</v>
@@ -12619,21 +12561,21 @@
         <v>立柜</v>
       </c>
       <c r="D30" t="str">
-        <v>立柜3m-柜4</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E30" t="str">
-        <v>第1层</v>
+        <v>第3层</v>
       </c>
       <c r="H30">
         <v>710</v>
       </c>
       <c r="I30">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A30,'10%触发_SKU明细'!$L$2:$L$72,$D30,'10%触发_SKU明细'!$M$2:$M$72,$E30,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="J30">
         <f>$H30-$I30</f>
-        <v>710</v>
+        <v>155</v>
       </c>
       <c r="K30">
         <v>534</v>
@@ -12642,15 +12584,15 @@
         <v>250</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>冷冻食材_潮汕风味牛肉丸/160g 3列</v>
       </c>
       <c r="N30" t="str">
-        <v>其他品类预留</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
         <v>立柜</v>
@@ -12659,21 +12601,21 @@
         <v>立柜</v>
       </c>
       <c r="D31" t="str">
-        <v>立柜3m-柜4</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E31" t="str">
-        <v>第2层</v>
+        <v>第4层</v>
       </c>
       <c r="H31">
         <v>710</v>
       </c>
       <c r="I31">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A31,'10%触发_SKU明细'!$L$2:$L$72,$D31,'10%触发_SKU明细'!$M$2:$M$72,$E31,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="J31">
         <f>$H31-$I31</f>
-        <v>710</v>
+        <v>230</v>
       </c>
       <c r="K31">
         <v>534</v>
@@ -12682,15 +12624,15 @@
         <v>250</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>皓月新西兰羔羊卷WMT/450g 1列；原切肥羊卷300g 1列</v>
       </c>
       <c r="N31" t="str">
-        <v>其他品类预留</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
         <v>立柜</v>
@@ -12699,21 +12641,21 @@
         <v>立柜</v>
       </c>
       <c r="D32" t="str">
-        <v>立柜3m-柜4</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E32" t="str">
-        <v>第3层</v>
+        <v>第5层</v>
       </c>
       <c r="H32">
         <v>710</v>
       </c>
       <c r="I32">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A32,'10%触发_SKU明细'!$L$2:$L$72,$D32,'10%触发_SKU明细'!$M$2:$M$72,$E32,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="J32">
         <f>$H32-$I32</f>
-        <v>710</v>
+        <v>35</v>
       </c>
       <c r="K32">
         <v>534</v>
@@ -12722,15 +12664,15 @@
         <v>250</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>【真好】黑猪肉爆汁烤肠原味400g 3列</v>
       </c>
       <c r="N32" t="str">
-        <v>其他品类预留</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
         <v>立柜</v>
@@ -12739,10 +12681,10 @@
         <v>立柜</v>
       </c>
       <c r="D33" t="str">
-        <v>立柜3m-柜4</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E33" t="str">
-        <v>第4层</v>
+        <v>第6层</v>
       </c>
       <c r="H33">
         <v>710</v>
@@ -12765,12 +12707,12 @@
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>其他品类预留</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
         <v>立柜</v>
@@ -12782,18 +12724,18 @@
         <v>立柜3m-柜4</v>
       </c>
       <c r="E34" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="H34">
         <v>710</v>
       </c>
       <c r="I34">
         <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A34,'10%触发_SKU明细'!$L$2:$L$72,$D34,'10%触发_SKU明细'!$M$2:$M$72,$E34,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <f>$H34-$I34</f>
-        <v>85</v>
+        <v>710</v>
       </c>
       <c r="K34">
         <v>534</v>
@@ -12802,15 +12744,15 @@
         <v>250</v>
       </c>
       <c r="M34" t="str">
-        <v>肉馅芹菜饺480g（两袋仅15.8元） 1列；荠菜笋丁鸡胸肉水饺480g 1列</v>
+        <v/>
       </c>
       <c r="N34" t="str">
-        <v>正常使用</v>
+        <v>其他品类预留</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
         <v>立柜</v>
@@ -12822,7 +12764,7 @@
         <v>立柜3m-柜4</v>
       </c>
       <c r="E35" t="str">
-        <v>第6层</v>
+        <v>第2层</v>
       </c>
       <c r="H35">
         <v>710</v>
@@ -12845,20 +12787,180 @@
         <v/>
       </c>
       <c r="N35" t="str">
+        <v>其他品类预留</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B36" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C36" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D36" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E36" t="str">
+        <v>第3层</v>
+      </c>
+      <c r="H36">
+        <v>710</v>
+      </c>
+      <c r="I36">
+        <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A36,'10%触发_SKU明细'!$L$2:$L$72,$D36,'10%触发_SKU明细'!$M$2:$M$72,$E36,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <f>$H36-$I36</f>
+        <v>710</v>
+      </c>
+      <c r="K36">
+        <v>534</v>
+      </c>
+      <c r="L36">
+        <v>250</v>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v>其他品类预留</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B37" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C37" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D37" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E37" t="str">
+        <v>第4层</v>
+      </c>
+      <c r="H37">
+        <v>710</v>
+      </c>
+      <c r="I37">
+        <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A37,'10%触发_SKU明细'!$L$2:$L$72,$D37,'10%触发_SKU明细'!$M$2:$M$72,$E37,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <f>$H37-$I37</f>
+        <v>710</v>
+      </c>
+      <c r="K37">
+        <v>534</v>
+      </c>
+      <c r="L37">
+        <v>250</v>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v>其他品类预留</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B38" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C38" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D38" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E38" t="str">
+        <v>第5层</v>
+      </c>
+      <c r="H38">
+        <v>710</v>
+      </c>
+      <c r="I38">
+        <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A38,'10%触发_SKU明细'!$L$2:$L$72,$D38,'10%触发_SKU明细'!$M$2:$M$72,$E38,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
+        <v>625</v>
+      </c>
+      <c r="J38">
+        <f>$H38-$I38</f>
+        <v>85</v>
+      </c>
+      <c r="K38">
+        <v>534</v>
+      </c>
+      <c r="L38">
+        <v>250</v>
+      </c>
+      <c r="M38" t="str">
+        <v>肉馅芹菜饺480g（两袋仅15.8元） 1列；荠菜笋丁鸡胸肉水饺480g 1列</v>
+      </c>
+      <c r="N38" t="str">
+        <v>正常使用</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B39" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C39" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D39" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E39" t="str">
+        <v>第6层</v>
+      </c>
+      <c r="H39">
+        <v>710</v>
+      </c>
+      <c r="I39">
+        <f>SUMIFS('10%触发_SKU明细'!$S$2:$S$72,'10%触发_SKU明细'!$A$2:$A$72,$A39,'10%触发_SKU明细'!$L$2:$L$72,$D39,'10%触发_SKU明细'!$M$2:$M$72,$E39,'10%触发_SKU明细'!$O$2:$O$72,"纳入")</f>
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <f>$H39-$I39</f>
+        <v>710</v>
+      </c>
+      <c r="K39">
+        <v>534</v>
+      </c>
+      <c r="L39">
+        <v>250</v>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v>存储位</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N35"/>
+  <autoFilter ref="A1:N39"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -12897,7 +12999,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>小于等于10%触发</v>
@@ -12932,7 +13034,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>小于等于10%触发</v>
@@ -12967,7 +13069,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>小于等于10%触发</v>
@@ -13002,7 +13104,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>小于等于10%触发</v>
@@ -13037,7 +13139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>小于等于10%触发</v>
@@ -13072,7 +13174,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>小于等于10%触发</v>
@@ -13107,7 +13209,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>小于等于10%触发</v>
@@ -13142,7 +13244,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>小于等于10%触发</v>
@@ -13154,10 +13256,10 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E9" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="F9">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -13166,18 +13268,18 @@
         <v>冷冻食材</v>
       </c>
       <c r="I9" t="str">
-        <v>冷冻水产</v>
+        <v>冷冻水果</v>
       </c>
       <c r="J9" t="str">
-        <v>带鱼段400g</v>
+        <v>冻榴莲500g</v>
       </c>
       <c r="K9" t="str">
-        <v>6971806121982</v>
+        <v>6977480891210</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
         <v>小于等于10%触发</v>
@@ -13189,30 +13291,30 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E10" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>冷冻食材</v>
+        <v>预制主食</v>
       </c>
       <c r="I10" t="str">
-        <v>冷冻水果</v>
+        <v>馒头发糕</v>
       </c>
       <c r="J10" t="str">
-        <v>冻榴莲500g</v>
+        <v>生活馆_料多多薯香乳酪包/400g</v>
       </c>
       <c r="K10" t="str">
-        <v>6977480891210</v>
+        <v>6971997913342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
         <v>小于等于10%触发</v>
@@ -13224,10 +13326,10 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E11" t="str">
-        <v>C</v>
+        <v>未评级</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>9999</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -13239,15 +13341,15 @@
         <v>馒头发糕</v>
       </c>
       <c r="J11" t="str">
-        <v>生活馆_料多多薯香乳酪包/400g</v>
+        <v>鲜奶馒头300g</v>
       </c>
       <c r="K11" t="str">
-        <v>6971997913342</v>
+        <v>6973560306940</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
         <v>小于等于10%触发</v>
@@ -13256,33 +13358,33 @@
         <v>暂不纳入</v>
       </c>
       <c r="D12" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
+        <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E12" t="str">
-        <v>未评级</v>
+        <v>B</v>
       </c>
       <c r="F12">
-        <v>9999</v>
+        <v>23</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>预制主食</v>
+        <v>雪糕冰品</v>
       </c>
       <c r="I12" t="str">
-        <v>馒头发糕</v>
+        <v>雪糕冰淇淋</v>
       </c>
       <c r="J12" t="str">
-        <v>鲜奶馒头300g</v>
+        <v>雀巢8次方巧克力香草味84g</v>
       </c>
       <c r="K12" t="str">
-        <v>6973560306940</v>
+        <v>6918551807884</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
         <v>小于等于10%触发</v>
@@ -13294,10 +13396,10 @@
         <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E13" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="F13">
-        <v>22</v>
+        <v>9999</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -13309,15 +13411,15 @@
         <v>雪糕冰淇淋</v>
       </c>
       <c r="J13" t="str">
-        <v>和路雪绿舌头54g</v>
+        <v>小金条无核榴莲肉100g</v>
       </c>
       <c r="K13" t="str">
-        <v>6909493800453</v>
+        <v>6977480896154</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>小于等于10%触发</v>
@@ -13329,10 +13431,10 @@
         <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E14" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="F14">
-        <v>23</v>
+        <v>9999</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -13344,15 +13446,15 @@
         <v>雪糕冰淇淋</v>
       </c>
       <c r="J14" t="str">
-        <v>雀巢8次方巧克力香草味84g</v>
+        <v>伊利6重巧巧70g</v>
       </c>
       <c r="K14" t="str">
-        <v>6918551807884</v>
+        <v>6907992827353</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>小于等于10%触发</v>
@@ -13361,139 +13463,34 @@
         <v>暂不纳入</v>
       </c>
       <c r="D15" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
+        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E15" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="F15">
-        <v>33</v>
+        <v>9999</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>雪糕冰品</v>
+        <v>预制菜类</v>
       </c>
       <c r="I15" t="str">
-        <v>雪糕冰淇淋</v>
+        <v>炸物小吃</v>
       </c>
       <c r="J15" t="str">
-        <v>和路雪可爱多香草67g</v>
+        <v>美好小酥肉800g</v>
       </c>
       <c r="K15" t="str">
-        <v>6909493401032</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B16" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C16" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D16" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E16" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F16">
-        <v>9999</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I16" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J16" t="str">
-        <v>小金条无核榴莲肉100g</v>
-      </c>
-      <c r="K16" t="str">
-        <v>6977480896154</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B17" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C17" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D17" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E17" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F17">
-        <v>9999</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I17" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J17" t="str">
-        <v>伊利6重巧巧70g</v>
-      </c>
-      <c r="K17" t="str">
-        <v>6907992827353</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B18" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C18" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D18" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
-      </c>
-      <c r="E18" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F18">
-        <v>9999</v>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v>预制菜类</v>
-      </c>
-      <c r="I18" t="str">
-        <v>炸物小吃</v>
-      </c>
-      <c r="J18" t="str">
-        <v>美好小酥肉800g</v>
-      </c>
-      <c r="K18" t="str">
         <v>6971938880948</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K18"/>
+  <autoFilter ref="A1:K15"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/drafts/新增门店_严格排柜结果.xlsx
+++ b/data/drafts/新增门店_严格排柜结果.xlsx
@@ -15,9 +15,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">'10%触发_门店汇总'!A1:R2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'10%触发_SKU明细'!A1:AP72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'10%触发_外储明细'!A1:W48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'10%触发_柜段余量'!A1:N35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'10%触发_未排入SKU清单'!A1:K18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'10%触发_外储明细'!A1:W46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'10%触发_柜段余量'!A1:N39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'10%触发_未排入SKU清单'!A1:K15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5">'71SKU有效池明细'!A1:S72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">'测算规则说明'!A1:B3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7">'可调整参数'!A1:C4</definedName>
@@ -478,7 +478,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>小于等于10%触发</v>
@@ -492,35 +492,35 @@
       </c>
       <c r="E2">
         <f>COUNTIFS('10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F2">
         <f>$D2-$E2</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <f>COUNTIFS('10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$P$2:$P$72,"纳入",'10%触发_SKU明细'!$AA$2:$AA$72,0)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H2">
         <f>COUNTIFS('10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$P$2:$P$72,"纳入",'10%触发_SKU明细'!$AA$2:$AA$72,"&gt;0")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2">
         <f>SUMIFS('10%触发_SKU明细'!$AB$2:$AB$72,'10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>999.7</v>
+        <v>971.7</v>
       </c>
       <c r="J2">
         <f>SUMIFS('10%触发_SKU明细'!$AC$2:$AC$72,'10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>499.8</v>
+        <v>485.8</v>
       </c>
       <c r="K2">
         <f>$J2*$R2</f>
-        <v>620.7</v>
+        <v>603.3</v>
       </c>
       <c r="L2">
         <f>ROUNDUP($K2*'可调整参数'!$B$3,0)</f>
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="M2" t="str">
         <f>IF($L2&gt;'可调整参数'!$B$4,"超754L","未超754L")</f>
@@ -684,7 +684,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>酥皮牛肉馅饼500g</v>
@@ -742,15 +742,15 @@
         <v>230</v>
       </c>
       <c r="U2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V2">
         <f>IF($P2&lt;&gt;"纳入",0,$R2*$U2)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W2">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$C$2:$C$72,$C2)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X2">
         <f>IF($P2&lt;&gt;"纳入",0,ROUNDUP($V2*'可调整参数'!$B$2,0))</f>
@@ -758,31 +758,31 @@
       </c>
       <c r="Y2">
         <f>IF($P2&lt;&gt;"纳入",0,MAX(0,$V2-$X2))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Z2">
         <f>IF($P2&lt;&gt;"纳入",0,MIN($Q2,$Y2))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA2">
         <f>IF(OR($P2&lt;&gt;"纳入",$AO2&lt;&gt;"是"),0,MAX(0,$Q2-$Z2))</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AB2">
         <f>$AA2*$AN2</f>
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="AC2">
         <f>$AB2/2</f>
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
       <c r="AD2">
         <f>IFERROR($V2/$AG2,0)</f>
-        <v>15.19</v>
+        <v>20.25</v>
       </c>
       <c r="AE2">
         <f>IFERROR($AA2/$AG2,0)</f>
-        <v>17.72</v>
+        <v>12.66</v>
       </c>
       <c r="AF2" t="str">
         <f>IF($AA2=0,"无外储",IF($AE2&gt;60,"高风险",IF($AE2&gt;30,"中风险","低风险")))</f>
@@ -821,7 +821,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g</v>
@@ -879,15 +879,15 @@
         <v>277.5</v>
       </c>
       <c r="U3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V3">
         <f>IF($P3&lt;&gt;"纳入",0,$R3*$U3)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W3">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A3,'10%触发_SKU明细'!$C$2:$C$72,$C3)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X3">
         <f>IF($P3&lt;&gt;"纳入",0,ROUNDUP($V3*'可调整参数'!$B$2,0))</f>
@@ -895,31 +895,31 @@
       </c>
       <c r="Y3">
         <f>IF($P3&lt;&gt;"纳入",0,MAX(0,$V3-$X3))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z3">
         <f>IF($P3&lt;&gt;"纳入",0,MIN($Q3,$Y3))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA3">
         <f>IF(OR($P3&lt;&gt;"纳入",$AO3&lt;&gt;"是"),0,MAX(0,$Q3-$Z3))</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB3">
         <f>$AA3*$AN3</f>
-        <v>16.9272</v>
+        <v>12.6954</v>
       </c>
       <c r="AC3">
         <f>$AB3/2</f>
-        <v>8.4636</v>
+        <v>6.3477</v>
       </c>
       <c r="AD3">
         <f>IFERROR($V3/$AG3,0)</f>
-        <v>15.6</v>
+        <v>17.83</v>
       </c>
       <c r="AE3">
         <f>IFERROR($AA3/$AG3,0)</f>
-        <v>8.91</v>
+        <v>6.69</v>
       </c>
       <c r="AF3" t="str">
         <f>IF($AA3=0,"无外储",IF($AE3&gt;60,"高风险",IF($AE3&gt;30,"中风险","低风险")))</f>
@@ -958,7 +958,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>【真值】甄选黄油鸡蛋灌饼皮640g</v>
@@ -988,7 +988,7 @@
         <v>卧柜</v>
       </c>
       <c r="L4" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="M4" t="str">
         <v>分区2</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>酥皮香菇猪肉馅饼500g</v>
@@ -1125,7 +1125,7 @@
         <v>卧柜</v>
       </c>
       <c r="L5" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M5" t="str">
         <v>分区2</v>
@@ -1153,15 +1153,15 @@
         <v>230</v>
       </c>
       <c r="U5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V5">
         <f>IF($P5&lt;&gt;"纳入",0,$R5*$U5)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W5">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A5,'10%触发_SKU明细'!$C$2:$C$72,$C5)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X5">
         <f>IF($P5&lt;&gt;"纳入",0,ROUNDUP($V5*'可调整参数'!$B$2,0))</f>
@@ -1169,31 +1169,31 @@
       </c>
       <c r="Y5">
         <f>IF($P5&lt;&gt;"纳入",0,MAX(0,$V5-$X5))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Z5">
         <f>IF($P5&lt;&gt;"纳入",0,MIN($Q5,$Y5))</f>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA5">
         <f>IF(OR($P5&lt;&gt;"纳入",$AO5&lt;&gt;"是"),0,MAX(0,$Q5-$Z5))</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AB5">
         <f>$AA5*$AN5</f>
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="AC5">
         <f>$AB5/2</f>
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
       <c r="AD5">
         <f>IFERROR($V5/$AG5,0)</f>
-        <v>28.86</v>
+        <v>38.48</v>
       </c>
       <c r="AE5">
         <f>IFERROR($AA5/$AG5,0)</f>
-        <v>33.67</v>
+        <v>24.05</v>
       </c>
       <c r="AF5" t="str">
         <f>IF($AA5=0,"无外储",IF($AE5&gt;60,"高风险",IF($AE5&gt;30,"中风险","低风险")))</f>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>纸皮韭菜盒子280g</v>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>老上海葱油饼900g</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>毛肚/200g</v>
@@ -1533,13 +1533,13 @@
         <v>火锅食材</v>
       </c>
       <c r="K8" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L8" t="str">
-        <v>立柜3m-柜3</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M8" t="str">
-        <v>第3层</v>
+        <v>分区2</v>
       </c>
       <c r="N8" t="str">
         <v>主陈列</v>
@@ -1554,57 +1554,57 @@
         <v>32</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8">
         <v>224</v>
       </c>
       <c r="T8">
         <f>IF($P8&lt;&gt;"纳入",0,$R8*$S8)</f>
-        <v>448</v>
+        <v>224</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="V8">
         <f>IF($P8&lt;&gt;"纳入",0,$R8*$U8)</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="W8">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A8,'10%触发_SKU明细'!$C$2:$C$72,$C8)</f>
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="X8">
         <f>IF($P8&lt;&gt;"纳入",0,ROUNDUP($V8*'可调整参数'!$B$2,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8">
         <f>IF($P8&lt;&gt;"纳入",0,MAX(0,$V8-$X8))</f>
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Z8">
         <f>IF($P8&lt;&gt;"纳入",0,MIN($Q8,$Y8))</f>
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AA8">
         <f>IF(OR($P8&lt;&gt;"纳入",$AO8&lt;&gt;"是"),0,MAX(0,$Q8-$Z8))</f>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <f>$AA8*$AN8</f>
-        <v>29.7925</v>
+        <v>11.917</v>
       </c>
       <c r="AC8">
         <f>$AB8/2</f>
-        <v>14.8963</v>
+        <v>5.9585</v>
       </c>
       <c r="AD8">
         <f>IFERROR($V8/$AG8,0)</f>
-        <v>16.1</v>
+        <v>50.32</v>
       </c>
       <c r="AE8">
         <f>IFERROR($AA8/$AG8,0)</f>
-        <v>50.32</v>
+        <v>20.13</v>
       </c>
       <c r="AF8" t="str">
         <f>IF($AA8=0,"无外储",IF($AE8&gt;60,"高风险",IF($AE8&gt;30,"中风险","低风险")))</f>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>火锅三宝/450g（毛肚+千层肚+鸭肠）</v>
@@ -1676,7 +1676,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M9" t="str">
-        <v>第2层</v>
+        <v>第1层</v>
       </c>
       <c r="N9" t="str">
         <v>主陈列</v>
@@ -1780,7 +1780,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
         <v>冰鲜鸭肠/200g</v>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
         <v>【真值】大个爆汁鲜肉包800g</v>
@@ -1950,7 +1950,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M11" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="N11" t="str">
         <v>主陈列</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
         <v>【真值】大个三鲜青菜包800g</v>
@@ -2087,7 +2087,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M12" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="N12" t="str">
         <v>主陈列</v>
@@ -2191,7 +2191,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
         <v>麻辣小龙虾1000g</v>
@@ -2224,7 +2224,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M13" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="N13" t="str">
         <v>主陈列</v>
@@ -2328,7 +2328,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>番茄肉酱意大利面280g</v>
@@ -2361,7 +2361,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="M14" t="str">
-        <v>第1层</v>
+        <v>第4层</v>
       </c>
       <c r="N14" t="str">
         <v>主陈列</v>
@@ -2465,7 +2465,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>【真值】纸皮烧麦蛋黄味240g</v>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>【真值】纸皮烧麦鲜肉味240g</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>【真值】纸皮烧麦香菇味240g</v>
@@ -2876,7 +2876,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>【真好】乌米三丁纸皮烧麦240g</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>【真好】黑猪肉梅干菜纸皮烧麦240g</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>【真好】黑松露纸皮烧麦240g</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>鸡胸肉/400g</v>
@@ -3424,7 +3424,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>安格斯牛排150g</v>
@@ -3561,7 +3561,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>潮香村眼肉牛排3片装</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B24" t="str">
         <v>冷冻鸡翅根/400g</v>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B25" t="str">
         <v>鸡爪/400g</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B26" t="str">
         <v>抽肠青虾仁150g</v>
@@ -4109,7 +4109,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B27" t="str">
         <v>黑鱼片250g</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B28" t="str">
         <v>整虾/冷冻南美白虾250g</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
         <v>带鱼段400g</v>
@@ -4410,13 +4410,13 @@
         <v>冷冻食材</v>
       </c>
       <c r="K29" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="L29" t="str">
-        <v/>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="N29" t="str">
         <v>主陈列</v>
@@ -4425,63 +4425,63 @@
         <v>主陈列</v>
       </c>
       <c r="P29" t="str">
-        <v>暂不纳入</v>
+        <v>纳入</v>
       </c>
       <c r="Q29">
         <v>20</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="T29">
         <f>IF($P29&lt;&gt;"纳入",0,$R29*$S29)</f>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V29">
         <f>IF($P29&lt;&gt;"纳入",0,$R29*$U29)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W29">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A29,'10%触发_SKU明细'!$C$2:$C$72,$C29)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X29">
         <f>IF($P29&lt;&gt;"纳入",0,ROUNDUP($V29*'可调整参数'!$B$2,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y29">
         <f>IF($P29&lt;&gt;"纳入",0,MAX(0,$V29-$X29))</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z29">
         <f>IF($P29&lt;&gt;"纳入",0,MIN($Q29,$Y29))</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA29">
         <f>IF(OR($P29&lt;&gt;"纳入",$AO29&lt;&gt;"是"),0,MAX(0,$Q29-$Z29))</f>
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <f>$AA29*$AN29</f>
-        <v>45.1</v>
+        <v>15.785</v>
       </c>
       <c r="AC29">
         <f>$AB29/2</f>
-        <v>22.55</v>
+        <v>7.8925</v>
       </c>
       <c r="AD29">
         <f>IFERROR($V29/$AG29,0)</f>
-        <v>0</v>
+        <v>55.13</v>
       </c>
       <c r="AE29">
         <f>IFERROR($AA29/$AG29,0)</f>
-        <v>73.5</v>
+        <v>25.73</v>
       </c>
       <c r="AF29" t="str">
         <f>IF($AA29=0,"无外储",IF($AE29&gt;60,"高风险",IF($AE29&gt;30,"中风险","低风险")))</f>
@@ -4520,7 +4520,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
         <v>冻榴莲500g</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
         <v>双色开花馒头（紫薯味+南瓜味）360g</v>
@@ -4794,7 +4794,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
         <v>手作奶香黄油开花馒头360g</v>
@@ -4931,7 +4931,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
         <v>生活馆_料多多薯香乳酪包/400g</v>
@@ -5068,7 +5068,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
         <v>鲜奶馒头300g</v>
@@ -5205,7 +5205,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
         <v>皓月新西兰羔羊卷WMT/450g</v>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B36" t="str">
         <v>原切肥羊卷300g</v>
@@ -5479,7 +5479,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B37" t="str">
         <v>【真好】黑猪肉爆汁烤肠原味400g</v>
@@ -5616,7 +5616,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B38" t="str">
         <v>肉馅芹菜饺480g（两袋仅15.8元）</v>
@@ -5753,7 +5753,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B39" t="str">
         <v>荠菜笋丁鸡胸肉水饺480g</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B40" t="str">
         <v>肉馅玉米饺480g（两袋仅15.8元）</v>
@@ -5920,7 +5920,7 @@
         <v>卧柜</v>
       </c>
       <c r="L40" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M40" t="str">
         <v>分区1</v>
@@ -6027,7 +6027,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B41" t="str">
         <v>生活馆_鲜肉小馄饨/++/512g</v>
@@ -6057,7 +6057,7 @@
         <v>卧柜</v>
       </c>
       <c r="L41" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M41" t="str">
         <v>分区1</v>
@@ -6164,7 +6164,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B42" t="str">
         <v>生活馆_菌菇三鲜水饺/480g</v>
@@ -6194,7 +6194,7 @@
         <v>卧柜</v>
       </c>
       <c r="L42" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="M42" t="str">
         <v>分区1</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B43" t="str">
         <v>魔芋羽衣甘蓝水饺480g</v>
@@ -6331,7 +6331,7 @@
         <v>卧柜</v>
       </c>
       <c r="L43" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M43" t="str">
         <v>分区1</v>
@@ -6438,7 +6438,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B44" t="str">
         <v>思念放心饺猪肉荠菜水饺</v>
@@ -6468,7 +6468,7 @@
         <v>卧柜</v>
       </c>
       <c r="L44" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M44" t="str">
         <v>分区1</v>
@@ -6575,7 +6575,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B45" t="str">
         <v>【真值】披萨奥尔良风味鸡肉味200克</v>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B46" t="str">
         <v>【真值】披萨精品榴莲芝士180g</v>
@@ -6742,7 +6742,7 @@
         <v>卧柜</v>
       </c>
       <c r="L46" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M46" t="str">
         <v>分区1</v>
@@ -6760,33 +6760,33 @@
         <v>30</v>
       </c>
       <c r="R46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S46">
         <v>180</v>
       </c>
       <c r="T46">
         <f>IF($P46&lt;&gt;"纳入",0,$R46*$S46)</f>
-        <v>720</v>
+        <v>180</v>
       </c>
       <c r="U46">
         <v>39</v>
       </c>
       <c r="V46">
         <f>IF($P46&lt;&gt;"纳入",0,$R46*$U46)</f>
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="W46">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A46,'10%触发_SKU明细'!$C$2:$C$72,$C46)</f>
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="X46">
         <f>IF($P46&lt;&gt;"纳入",0,ROUNDUP($V46*'可调整参数'!$B$2,0))</f>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y46">
         <f>IF($P46&lt;&gt;"纳入",0,MAX(0,$V46-$X46))</f>
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="Z46">
         <f>IF($P46&lt;&gt;"纳入",0,MIN($Q46,$Y46))</f>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="AD46">
         <f>IFERROR($V46/$AG46,0)</f>
-        <v>117.39</v>
+        <v>29.35</v>
       </c>
       <c r="AE46">
         <f>IFERROR($AA46/$AG46,0)</f>
@@ -6849,7 +6849,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B47" t="str">
         <v>【真值】披萨黑椒牛肉风味200g</v>
@@ -6879,7 +6879,7 @@
         <v>卧柜</v>
       </c>
       <c r="L47" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="M47" t="str">
         <v>分区1</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B48" t="str">
         <v>【真值】披萨芝士培根风味200g</v>
@@ -7016,7 +7016,7 @@
         <v>卧柜</v>
       </c>
       <c r="L48" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="M48" t="str">
         <v>分区1</v>
@@ -7034,33 +7034,33 @@
         <v>30</v>
       </c>
       <c r="R48">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S48">
         <v>180</v>
       </c>
       <c r="T48">
         <f>IF($P48&lt;&gt;"纳入",0,$R48*$S48)</f>
-        <v>180</v>
+        <v>1440</v>
       </c>
       <c r="U48">
         <v>39</v>
       </c>
       <c r="V48">
         <f>IF($P48&lt;&gt;"纳入",0,$R48*$U48)</f>
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="W48">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A48,'10%触发_SKU明细'!$C$2:$C$72,$C48)</f>
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="X48">
         <f>IF($P48&lt;&gt;"纳入",0,ROUNDUP($V48*'可调整参数'!$B$2,0))</f>
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="Y48">
         <f>IF($P48&lt;&gt;"纳入",0,MAX(0,$V48-$X48))</f>
-        <v>35</v>
+        <v>280</v>
       </c>
       <c r="Z48">
         <f>IF($P48&lt;&gt;"纳入",0,MIN($Q48,$Y48))</f>
@@ -7080,7 +7080,7 @@
       </c>
       <c r="AD48">
         <f>IFERROR($V48/$AG48,0)</f>
-        <v>32.93</v>
+        <v>263.47</v>
       </c>
       <c r="AE48">
         <f>IFERROR($AA48/$AG48,0)</f>
@@ -7123,7 +7123,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B49" t="str">
         <v>思念-黑芝麻汤圆455g</v>
@@ -7153,7 +7153,7 @@
         <v>卧柜</v>
       </c>
       <c r="L49" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M49" t="str">
         <v>分区1</v>
@@ -7181,23 +7181,23 @@
         <v>220</v>
       </c>
       <c r="U49">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="V49">
         <f>IF($P49&lt;&gt;"纳入",0,$R49*$U49)</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="W49">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A49,'10%触发_SKU明细'!$C$2:$C$72,$C49)</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="X49">
         <f>IF($P49&lt;&gt;"纳入",0,ROUNDUP($V49*'可调整参数'!$B$2,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y49">
         <f>IF($P49&lt;&gt;"纳入",0,MAX(0,$V49-$X49))</f>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Z49">
         <f>IF($P49&lt;&gt;"纳入",0,MIN($Q49,$Y49))</f>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="AD49">
         <f>IFERROR($V49/$AG49,0)</f>
-        <v>97.25</v>
+        <v>101.67</v>
       </c>
       <c r="AE49">
         <f>IFERROR($AA49/$AG49,0)</f>
@@ -7260,7 +7260,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B50" t="str">
         <v>思念大黄米黑芝麻汤圆454g</v>
@@ -7290,7 +7290,7 @@
         <v>卧柜</v>
       </c>
       <c r="L50" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M50" t="str">
         <v>分区1</v>
@@ -7397,7 +7397,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B51" t="str">
         <v>冷冻食材_潮汕风味牛肉丸/160g</v>
@@ -7430,7 +7430,7 @@
         <v>立柜3m-柜3</v>
       </c>
       <c r="M51" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="N51" t="str">
         <v>主陈列</v>
@@ -7445,25 +7445,25 @@
         <v>40</v>
       </c>
       <c r="R51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S51">
         <v>185</v>
       </c>
       <c r="T51">
         <f>IF($P51&lt;&gt;"纳入",0,$R51*$S51)</f>
-        <v>185</v>
+        <v>555</v>
       </c>
       <c r="U51">
         <v>3</v>
       </c>
       <c r="V51">
         <f>IF($P51&lt;&gt;"纳入",0,$R51*$U51)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W51">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A51,'10%触发_SKU明细'!$C$2:$C$72,$C51)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="X51">
         <f>IF($P51&lt;&gt;"纳入",0,ROUNDUP($V51*'可调整参数'!$B$2,0))</f>
@@ -7471,31 +7471,31 @@
       </c>
       <c r="Y51">
         <f>IF($P51&lt;&gt;"纳入",0,MAX(0,$V51-$X51))</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Z51">
         <f>IF($P51&lt;&gt;"纳入",0,MIN($Q51,$Y51))</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AA51">
         <f>IF(OR($P51&lt;&gt;"纳入",$AO51&lt;&gt;"是"),0,MAX(0,$Q51-$Z51))</f>
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB51">
         <f>$AA51*$AN51</f>
-        <v>38.1368</v>
+        <v>32.1152</v>
       </c>
       <c r="AC51">
         <f>$AB51/2</f>
-        <v>19.0684</v>
+        <v>16.0576</v>
       </c>
       <c r="AD51">
         <f>IFERROR($V51/$AG51,0)</f>
-        <v>1.57</v>
+        <v>4.72</v>
       </c>
       <c r="AE51">
         <f>IFERROR($AA51/$AG51,0)</f>
-        <v>19.94</v>
+        <v>16.8</v>
       </c>
       <c r="AF51" t="str">
         <f>IF($AA51=0,"无外储",IF($AE51&gt;60,"高风险",IF($AE51&gt;30,"中风险","低风险")))</f>
@@ -7534,7 +7534,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B52" t="str">
         <v>冷冻食材_包心鱼丸/160g(shg)</v>
@@ -7564,7 +7564,7 @@
         <v>卧柜</v>
       </c>
       <c r="L52" t="str">
-        <v>卧柜2505-柜2</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="M52" t="str">
         <v>分区1</v>
@@ -7671,7 +7671,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B53" t="str">
         <v>青虾滑95% 150g</v>
@@ -7701,7 +7701,7 @@
         <v>卧柜</v>
       </c>
       <c r="L53" t="str">
-        <v>卧柜2505-柜2</v>
+        <v>卧柜2505-柜1</v>
       </c>
       <c r="M53" t="str">
         <v>分区1</v>
@@ -7729,23 +7729,23 @@
         <v>240</v>
       </c>
       <c r="U53">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="V53">
         <f>IF($P53&lt;&gt;"纳入",0,$R53*$U53)</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="W53">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A53,'10%触发_SKU明细'!$C$2:$C$72,$C53)</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="X53">
         <f>IF($P53&lt;&gt;"纳入",0,ROUNDUP($V53*'可调整参数'!$B$2,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y53">
         <f>IF($P53&lt;&gt;"纳入",0,MAX(0,$V53-$X53))</f>
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Z53">
         <f>IF($P53&lt;&gt;"纳入",0,MIN($Q53,$Y53))</f>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="AD53">
         <f>IFERROR($V53/$AG53,0)</f>
-        <v>100.1</v>
+        <v>104.65</v>
       </c>
       <c r="AE53">
         <f>IFERROR($AA53/$AG53,0)</f>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B54" t="str">
         <v>宏宝来俄式大脆筒牛奶味100g</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B55" t="str">
         <v>宏宝莱老冰棍80g</v>
@@ -8082,7 +8082,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B56" t="str">
         <v>蒙牛随变转巧克力雪糕65g</v>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B57" t="str">
         <v>伊利巧脆棒雪糕75g</v>
@@ -8356,7 +8356,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B58" t="str">
         <v>伊利大布丁60g</v>
@@ -8493,7 +8493,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B59" t="str">
         <v>酷企鹅食用冰杯160g</v>
@@ -8630,7 +8630,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B60" t="str">
         <v>上上鲜 绿色心情绿莎莎雪糕70g</v>
@@ -8767,7 +8767,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B61" t="str">
         <v>伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g</v>
@@ -8904,7 +8904,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B62" t="str">
         <v>和路雪绿舌头54g</v>
@@ -8930,76 +8930,79 @@
       <c r="J62" t="str">
         <v>雪糕冰品</v>
       </c>
+      <c r="K62" t="str">
+        <v>冰淇淋柜</v>
+      </c>
       <c r="L62" t="str">
-        <v/>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>分区1</v>
       </c>
       <c r="N62" t="str">
-        <v>单陈列</v>
+        <v>主陈列</v>
       </c>
       <c r="O62" t="str">
         <v>主陈列</v>
       </c>
       <c r="P62" t="str">
-        <v>暂不纳入</v>
+        <v>纳入</v>
       </c>
       <c r="Q62">
         <v>36</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="T62">
         <f>IF($P62&lt;&gt;"纳入",0,$R62*$S62)</f>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="V62">
         <f>IF($P62&lt;&gt;"纳入",0,$R62*$U62)</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="W62">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A62,'10%触发_SKU明细'!$C$2:$C$72,$C62)</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="X62">
         <f>IF($P62&lt;&gt;"纳入",0,ROUNDUP($V62*'可调整参数'!$B$2,0))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y62">
         <f>IF($P62&lt;&gt;"纳入",0,MAX(0,$V62-$X62))</f>
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="Z62">
         <f>IF($P62&lt;&gt;"纳入",0,MIN($Q62,$Y62))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA62">
         <f>IF(OR($P62&lt;&gt;"纳入",$AO62&lt;&gt;"是"),0,MAX(0,$Q62-$Z62))</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AB62">
         <f>$AA62*$AN62</f>
-        <v>10.3968</v>
+        <v>0</v>
       </c>
       <c r="AC62">
         <f>$AB62/2</f>
-        <v>5.1984</v>
+        <v>0</v>
       </c>
       <c r="AD62">
         <f>IFERROR($V62/$AG62,0)</f>
-        <v>0</v>
+        <v>142.89</v>
       </c>
       <c r="AE62">
         <f>IFERROR($AA62/$AG62,0)</f>
-        <v>26.79</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="str">
         <f>IF($AA62=0,"无外储",IF($AE62&gt;60,"高风险",IF($AE62&gt;30,"中风险","低风险")))</f>
@@ -9038,7 +9041,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B63" t="str">
         <v>雀巢8次方巧克力香草味84g</v>
@@ -9172,7 +9175,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B64" t="str">
         <v>和路雪可爱多香草67g</v>
@@ -9198,76 +9201,79 @@
       <c r="J64" t="str">
         <v>雪糕冰品</v>
       </c>
+      <c r="K64" t="str">
+        <v>冰淇淋柜</v>
+      </c>
       <c r="L64" t="str">
-        <v/>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>分区1</v>
       </c>
       <c r="N64" t="str">
-        <v>单陈列</v>
+        <v>主陈列</v>
       </c>
       <c r="O64" t="str">
         <v>主陈列</v>
       </c>
       <c r="P64" t="str">
-        <v>暂不纳入</v>
+        <v>纳入</v>
       </c>
       <c r="Q64">
         <v>24</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="T64">
         <f>IF($P64&lt;&gt;"纳入",0,$R64*$S64)</f>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="V64">
         <f>IF($P64&lt;&gt;"纳入",0,$R64*$U64)</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="W64">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A64,'10%触发_SKU明细'!$C$2:$C$72,$C64)</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="X64">
         <f>IF($P64&lt;&gt;"纳入",0,ROUNDUP($V64*'可调整参数'!$B$2,0))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y64">
         <f>IF($P64&lt;&gt;"纳入",0,MAX(0,$V64-$X64))</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="Z64">
         <f>IF($P64&lt;&gt;"纳入",0,MIN($Q64,$Y64))</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA64">
         <f>IF(OR($P64&lt;&gt;"纳入",$AO64&lt;&gt;"是"),0,MAX(0,$Q64-$Z64))</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AB64">
         <f>$AA64*$AN64</f>
-        <v>13.392</v>
+        <v>0</v>
       </c>
       <c r="AC64">
         <f>$AB64/2</f>
-        <v>6.696</v>
+        <v>0</v>
       </c>
       <c r="AD64">
         <f>IFERROR($V64/$AG64,0)</f>
-        <v>0</v>
+        <v>79.63</v>
       </c>
       <c r="AE64">
         <f>IFERROR($AA64/$AG64,0)</f>
-        <v>24.82</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="str">
         <f>IF($AA64=0,"无外储",IF($AE64&gt;60,"高风险",IF($AE64&gt;30,"中风险","低风险")))</f>
@@ -9306,7 +9312,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B65" t="str">
         <v>小金条无核榴莲肉100g</v>
@@ -9440,7 +9446,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B66" t="str">
         <v>伊利6重巧巧70g</v>
@@ -9574,7 +9580,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B67" t="str">
         <v>【真值】芝士鸡肉卷奥尔良味120g</v>
@@ -9604,7 +9610,7 @@
         <v>卧柜</v>
       </c>
       <c r="L67" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M67" t="str">
         <v>分区1</v>
@@ -9622,33 +9628,33 @@
         <v>40</v>
       </c>
       <c r="R67">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S67">
         <v>200</v>
       </c>
       <c r="T67">
         <f>IF($P67&lt;&gt;"纳入",0,$R67*$S67)</f>
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="U67">
         <v>100</v>
       </c>
       <c r="V67">
         <f>IF($P67&lt;&gt;"纳入",0,$R67*$U67)</f>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="W67">
         <f>SUMIFS('10%触发_SKU明细'!$V$2:$V$72,'10%触发_SKU明细'!$A$2:$A$72,$A67,'10%触发_SKU明细'!$C$2:$C$72,$C67)</f>
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="X67">
         <f>IF($P67&lt;&gt;"纳入",0,ROUNDUP($V67*'可调整参数'!$B$2,0))</f>
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="Y67">
         <f>IF($P67&lt;&gt;"纳入",0,MAX(0,$V67-$X67))</f>
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="Z67">
         <f>IF($P67&lt;&gt;"纳入",0,MIN($Q67,$Y67))</f>
@@ -9668,7 +9674,7 @@
       </c>
       <c r="AD67">
         <f>IFERROR($V67/$AG67,0)</f>
-        <v>64.4</v>
+        <v>257.58</v>
       </c>
       <c r="AE67">
         <f>IFERROR($AA67/$AG67,0)</f>
@@ -9711,7 +9717,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B68" t="str">
         <v>【真值】芝士牛肉卷黑胡椒味120g</v>
@@ -9741,7 +9747,7 @@
         <v>卧柜</v>
       </c>
       <c r="L68" t="str">
-        <v>卧柜2505-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="M68" t="str">
         <v>分区1</v>
@@ -9848,7 +9854,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B69" t="str">
         <v>【真值】香脆小酥肉原味800g</v>
@@ -9878,7 +9884,7 @@
         <v>卧柜</v>
       </c>
       <c r="L69" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M69" t="str">
         <v>分区1</v>
@@ -9985,7 +9991,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B70" t="str">
         <v>台式鸡排400g</v>
@@ -10015,7 +10021,7 @@
         <v>卧柜</v>
       </c>
       <c r="L70" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M70" t="str">
         <v>分区1</v>
@@ -10122,7 +10128,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B71" t="str">
         <v>玉米布丁酥400g</v>
@@ -10152,7 +10158,7 @@
         <v>卧柜</v>
       </c>
       <c r="L71" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2505-柜2</v>
       </c>
       <c r="M71" t="str">
         <v>分区1</v>
@@ -10259,7 +10265,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B72" t="str">
         <v>美好小酥肉800g</v>
@@ -10404,7 +10410,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W48"/>
+  <dimension ref="A1:W46"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10479,7 +10485,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>酥皮牛肉馅饼500g</v>
@@ -10515,36 +10521,36 @@
         <v>24</v>
       </c>
       <c r="N2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O2">
         <v>2</v>
       </c>
       <c r="P2">
+        <v>14</v>
+      </c>
+      <c r="Q2">
+        <v>14</v>
+      </c>
+      <c r="R2">
         <v>10</v>
-      </c>
-      <c r="Q2">
-        <v>10</v>
-      </c>
-      <c r="R2">
-        <v>14</v>
       </c>
       <c r="S2">
         <v>1.955</v>
       </c>
       <c r="T2">
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="U2">
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
       <c r="V2">
-        <v>17.72</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g</v>
@@ -10580,36 +10586,36 @@
         <v>20</v>
       </c>
       <c r="N3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O3">
         <v>2</v>
       </c>
       <c r="P3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S3">
         <v>2.1159</v>
       </c>
       <c r="T3">
-        <v>16.9272</v>
+        <v>12.6954</v>
       </c>
       <c r="U3">
-        <v>8.4636</v>
+        <v>6.3477</v>
       </c>
       <c r="V3">
-        <v>8.91</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>酥皮香菇猪肉馅饼500g</v>
@@ -10633,7 +10639,7 @@
         <v>卧柜</v>
       </c>
       <c r="J4" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="K4" t="str">
         <v>分区2</v>
@@ -10645,36 +10651,36 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O4">
         <v>2</v>
       </c>
       <c r="P4">
+        <v>14</v>
+      </c>
+      <c r="Q4">
+        <v>14</v>
+      </c>
+      <c r="R4">
         <v>10</v>
-      </c>
-      <c r="Q4">
-        <v>10</v>
-      </c>
-      <c r="R4">
-        <v>14</v>
       </c>
       <c r="S4">
         <v>1.955</v>
       </c>
       <c r="T4">
-        <v>27.37</v>
+        <v>19.55</v>
       </c>
       <c r="U4">
-        <v>13.685</v>
+        <v>9.775</v>
       </c>
       <c r="V4">
-        <v>33.67</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>纸皮韭菜盒子280g</v>
@@ -10739,7 +10745,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>老上海葱油饼900g</v>
@@ -10804,7 +10810,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>毛肚/200g</v>
@@ -10825,13 +10831,13 @@
         <v>火锅肉类</v>
       </c>
       <c r="I7" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="J7" t="str">
-        <v>立柜3m-柜3</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="K7" t="str">
-        <v>第3层</v>
+        <v>分区2</v>
       </c>
       <c r="L7" t="str">
         <v>主陈列</v>
@@ -10840,36 +10846,36 @@
         <v>32</v>
       </c>
       <c r="N7">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Q7">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="R7">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>1.1917</v>
       </c>
       <c r="T7">
-        <v>29.7925</v>
+        <v>11.917</v>
       </c>
       <c r="U7">
-        <v>14.8963</v>
+        <v>5.9585</v>
       </c>
       <c r="V7">
-        <v>50.32</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>火锅三宝/450g（毛肚+千层肚+鸭肠）</v>
@@ -10896,7 +10902,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="K8" t="str">
-        <v>第2层</v>
+        <v>第1层</v>
       </c>
       <c r="L8" t="str">
         <v>主陈列</v>
@@ -10934,7 +10940,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>冰鲜鸭肠/200g</v>
@@ -10999,7 +11005,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
         <v>【真值】大个爆汁鲜肉包800g</v>
@@ -11026,7 +11032,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="K10" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="L10" t="str">
         <v>主陈列</v>
@@ -11064,7 +11070,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
         <v>【真值】大个三鲜青菜包800g</v>
@@ -11091,7 +11097,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="K11" t="str">
-        <v>第3层</v>
+        <v>第2层</v>
       </c>
       <c r="L11" t="str">
         <v>主陈列</v>
@@ -11129,7 +11135,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
         <v>麻辣小龙虾1000g</v>
@@ -11156,7 +11162,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="K12" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="L12" t="str">
         <v>主陈列</v>
@@ -11194,7 +11200,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
         <v>番茄肉酱意大利面280g</v>
@@ -11221,7 +11227,7 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="K13" t="str">
-        <v>第1层</v>
+        <v>第4层</v>
       </c>
       <c r="L13" t="str">
         <v>主陈列</v>
@@ -11259,7 +11265,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>【真值】纸皮烧麦蛋黄味240g</v>
@@ -11324,7 +11330,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>【真值】纸皮烧麦鲜肉味240g</v>
@@ -11389,7 +11395,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>【真值】纸皮烧麦香菇味240g</v>
@@ -11454,7 +11460,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>【真好】乌米三丁纸皮烧麦240g</v>
@@ -11519,7 +11525,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>【真好】黑猪肉梅干菜纸皮烧麦240g</v>
@@ -11584,7 +11590,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>【真好】黑松露纸皮烧麦240g</v>
@@ -11649,7 +11655,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>鸡胸肉/400g</v>
@@ -11714,7 +11720,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>安格斯牛排150g</v>
@@ -11779,7 +11785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>潮香村眼肉牛排3片装</v>
@@ -11844,7 +11850,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>冷冻鸡翅根/400g</v>
@@ -11909,7 +11915,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B24" t="str">
         <v>鸡爪/400g</v>
@@ -11974,7 +11980,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B25" t="str">
         <v>抽肠青虾仁150g</v>
@@ -12039,7 +12045,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B26" t="str">
         <v>黑鱼片250g</v>
@@ -12104,7 +12110,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B27" t="str">
         <v>整虾/冷冻南美白虾250g</v>
@@ -12169,7 +12175,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B28" t="str">
         <v>带鱼段400g</v>
@@ -12190,13 +12196,13 @@
         <v>冷冻水产</v>
       </c>
       <c r="I28" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>分区2</v>
       </c>
       <c r="L28" t="str">
         <v>主陈列</v>
@@ -12205,36 +12211,36 @@
         <v>20</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="R28">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>2.255</v>
       </c>
       <c r="T28">
-        <v>45.1</v>
+        <v>15.785</v>
       </c>
       <c r="U28">
-        <v>22.55</v>
+        <v>7.8925</v>
       </c>
       <c r="V28">
-        <v>73.5</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
         <v>冻榴莲500g</v>
@@ -12299,7 +12305,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
         <v>双色开花馒头（紫薯味+南瓜味）360g</v>
@@ -12364,7 +12370,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
         <v>手作奶香黄油开花馒头360g</v>
@@ -12429,7 +12435,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
         <v>生活馆_料多多薯香乳酪包/400g</v>
@@ -12494,7 +12500,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
         <v>鲜奶馒头300g</v>
@@ -12559,7 +12565,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
         <v>皓月新西兰羔羊卷WMT/450g</v>
@@ -12624,7 +12630,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
         <v>原切肥羊卷300g</v>
@@ -12689,7 +12695,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B36" t="str">
         <v>【真好】黑猪肉爆汁烤肠原味400g</v>
@@ -12754,7 +12760,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B37" t="str">
         <v>肉馅芹菜饺480g（两袋仅15.8元）</v>
@@ -12819,7 +12825,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B38" t="str">
         <v>荠菜笋丁鸡胸肉水饺480g</v>
@@ -12884,7 +12890,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B39" t="str">
         <v>【真值】披萨奥尔良风味鸡肉味200克</v>
@@ -12949,7 +12955,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B40" t="str">
         <v>冷冻食材_潮汕风味牛肉丸/160g</v>
@@ -12976,7 +12982,7 @@
         <v>立柜3m-柜3</v>
       </c>
       <c r="K40" t="str">
-        <v>第4层</v>
+        <v>第3层</v>
       </c>
       <c r="L40" t="str">
         <v>主陈列</v>
@@ -12985,36 +12991,36 @@
         <v>40</v>
       </c>
       <c r="N40">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R40">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="S40">
         <v>1.0036</v>
       </c>
       <c r="T40">
-        <v>38.1368</v>
+        <v>32.1152</v>
       </c>
       <c r="U40">
-        <v>19.0684</v>
+        <v>16.0576</v>
       </c>
       <c r="V40">
-        <v>19.94</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B41" t="str">
         <v>宏宝来俄式大脆筒牛奶味100g</v>
@@ -13079,7 +13085,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B42" t="str">
         <v>酷企鹅食用冰杯160g</v>
@@ -13144,19 +13150,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B43" t="str">
-        <v>和路雪绿舌头54g</v>
+        <v>雀巢8次方巧克力香草味84g</v>
       </c>
       <c r="C43" t="str">
-        <v>6909493800453</v>
+        <v>6918551807884</v>
       </c>
       <c r="D43" t="str">
         <v>B</v>
       </c>
       <c r="E43">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F43" t="str">
         <v>雪糕冰品</v>
@@ -13174,7 +13180,7 @@
         <v>主陈列</v>
       </c>
       <c r="M43">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -13189,36 +13195,36 @@
         <v>0</v>
       </c>
       <c r="R43">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="S43">
-        <v>0.2888</v>
+        <v>0.2721</v>
       </c>
       <c r="T43">
-        <v>10.3968</v>
+        <v>4.8978</v>
       </c>
       <c r="U43">
-        <v>5.1984</v>
+        <v>2.4489</v>
       </c>
       <c r="V43">
-        <v>26.79</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B44" t="str">
-        <v>雀巢8次方巧克力香草味84g</v>
+        <v>小金条无核榴莲肉100g</v>
       </c>
       <c r="C44" t="str">
-        <v>6918551807884</v>
+        <v>6977480896154</v>
       </c>
       <c r="D44" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="E44">
-        <v>23</v>
+        <v>9999</v>
       </c>
       <c r="F44" t="str">
         <v>雪糕冰品</v>
@@ -13236,7 +13242,7 @@
         <v>主陈列</v>
       </c>
       <c r="M44">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="N44">
         <v>0</v>
@@ -13251,36 +13257,36 @@
         <v>0</v>
       </c>
       <c r="R44">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="S44">
-        <v>0.2721</v>
+        <v>0.3776</v>
       </c>
       <c r="T44">
-        <v>4.8978</v>
+        <v>22.656</v>
       </c>
       <c r="U44">
-        <v>2.4489</v>
+        <v>11.328</v>
       </c>
       <c r="V44">
-        <v>14.61</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B45" t="str">
-        <v>和路雪可爱多香草67g</v>
+        <v>伊利6重巧巧70g</v>
       </c>
       <c r="C45" t="str">
-        <v>6909493401032</v>
+        <v>6907992827353</v>
       </c>
       <c r="D45" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="E45">
-        <v>33</v>
+        <v>9999</v>
       </c>
       <c r="F45" t="str">
         <v>雪糕冰品</v>
@@ -13298,7 +13304,7 @@
         <v>主陈列</v>
       </c>
       <c r="M45">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -13313,30 +13319,30 @@
         <v>0</v>
       </c>
       <c r="R45">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="S45">
-        <v>0.558</v>
+        <v>0.275</v>
       </c>
       <c r="T45">
-        <v>13.392</v>
+        <v>9.625</v>
       </c>
       <c r="U45">
-        <v>6.696</v>
+        <v>4.8125</v>
       </c>
       <c r="V45">
-        <v>24.82</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B46" t="str">
-        <v>小金条无核榴莲肉100g</v>
+        <v>美好小酥肉800g</v>
       </c>
       <c r="C46" t="str">
-        <v>6977480896154</v>
+        <v>6971938880948</v>
       </c>
       <c r="D46" t="str">
         <v>未评级</v>
@@ -13345,10 +13351,13 @@
         <v>9999</v>
       </c>
       <c r="F46" t="str">
-        <v>雪糕冰品</v>
+        <v>预制菜类</v>
       </c>
       <c r="H46" t="str">
-        <v>雪糕冰淇淋</v>
+        <v>炸物小吃</v>
+      </c>
+      <c r="I46" t="str">
+        <v>立柜</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -13360,7 +13369,7 @@
         <v>主陈列</v>
       </c>
       <c r="M46">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -13375,159 +13384,32 @@
         <v>0</v>
       </c>
       <c r="R46">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="S46">
-        <v>0.3776</v>
+        <v>4.725</v>
       </c>
       <c r="T46">
-        <v>22.656</v>
+        <v>47.25</v>
       </c>
       <c r="U46">
-        <v>11.328</v>
-      </c>
-      <c r="V46">
-        <v>35.15</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B47" t="str">
-        <v>伊利6重巧巧70g</v>
-      </c>
-      <c r="C47" t="str">
-        <v>6907992827353</v>
-      </c>
-      <c r="D47" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="E47">
-        <v>9999</v>
-      </c>
-      <c r="F47" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="H47" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J47" t="str">
-        <v/>
-      </c>
-      <c r="K47" t="str">
-        <v/>
-      </c>
-      <c r="L47" t="str">
-        <v>主陈列</v>
-      </c>
-      <c r="M47">
-        <v>35</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>35</v>
-      </c>
-      <c r="S47">
-        <v>0.275</v>
-      </c>
-      <c r="T47">
-        <v>9.625</v>
-      </c>
-      <c r="U47">
-        <v>4.8125</v>
-      </c>
-      <c r="V47">
-        <v>50.86</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B48" t="str">
-        <v>美好小酥肉800g</v>
-      </c>
-      <c r="C48" t="str">
-        <v>6971938880948</v>
-      </c>
-      <c r="D48" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="E48">
-        <v>9999</v>
-      </c>
-      <c r="F48" t="str">
-        <v>预制菜类</v>
-      </c>
-      <c r="H48" t="str">
-        <v>炸物小吃</v>
-      </c>
-      <c r="I48" t="str">
-        <v>立柜</v>
-      </c>
-      <c r="J48" t="str">
-        <v/>
-      </c>
-      <c r="K48" t="str">
-        <v/>
-      </c>
-      <c r="L48" t="str">
-        <v>主陈列</v>
-      </c>
-      <c r="M48">
-        <v>10</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>10</v>
-      </c>
-      <c r="S48">
-        <v>4.725</v>
-      </c>
-      <c r="T48">
-        <v>47.25</v>
-      </c>
-      <c r="U48">
         <v>23.625</v>
       </c>
-      <c r="V48" t="str">
+      <c r="V46" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W48"/>
+  <autoFilter ref="A1:W46"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W46"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13575,7 +13457,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>卧柜</v>
@@ -13594,20 +13476,20 @@
       </c>
       <c r="I2">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A2,'10%触发_SKU明细'!$L$2:$L$72,$D2,'10%触发_SKU明细'!$M$2:$M$72,$E2,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>1965</v>
+        <v>1905</v>
       </c>
       <c r="J2">
         <f>$H2-$I2</f>
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="K2">
         <v>697</v>
       </c>
       <c r="L2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M2" t="str">
-        <v>【真值】披萨精品榴莲芝士180g 4列；【真值】披萨黑椒牛肉风味200g 1列；【真值】披萨芝士培根风味200g 1列；思念-黑芝麻汤圆455g 1列；思念大黄米黑芝麻汤圆454g 1列；【真值】芝士鸡肉卷奥尔良味120g 1列；【真值】芝士牛肉卷黑胡椒味120g 1列</v>
+        <v>冷冻食材_包心鱼丸/160g(shg) 9列；青虾滑95% 150g 1列</v>
       </c>
       <c r="N2" t="str">
         <v>正常使用</v>
@@ -13615,7 +13497,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>卧柜</v>
@@ -13644,7 +13526,7 @@
         <v>697</v>
       </c>
       <c r="L3">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M3" t="str">
         <v>酥皮牛肉馅饼500g 1列</v>
@@ -13655,7 +13537,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>卧柜</v>
@@ -13674,20 +13556,20 @@
       </c>
       <c r="I4">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A4,'10%触发_SKU明细'!$L$2:$L$72,$D4,'10%触发_SKU明细'!$M$2:$M$72,$E4,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>1905</v>
+        <v>1860</v>
       </c>
       <c r="J4">
         <f>$H4-$I4</f>
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="K4">
         <v>697</v>
       </c>
       <c r="L4">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M4" t="str">
-        <v>冷冻食材_包心鱼丸/160g(shg) 9列；青虾滑95% 150g 1列</v>
+        <v>【真值】香脆小酥肉原味800g 4列；台式鸡排400g 1列；玉米布丁酥400g 1列</v>
       </c>
       <c r="N4" t="str">
         <v>正常使用</v>
@@ -13695,7 +13577,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>卧柜</v>
@@ -13724,7 +13606,7 @@
         <v>697</v>
       </c>
       <c r="L5">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M5" t="str">
         <v>【真好】甄选黄油手抓饼/++/800g 1列</v>
@@ -13735,7 +13617,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>卧柜</v>
@@ -13744,30 +13626,30 @@
         <v>卧柜</v>
       </c>
       <c r="D6" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="E6" t="str">
         <v>分区1</v>
       </c>
       <c r="H6">
-        <v>1988</v>
+        <v>1488</v>
       </c>
       <c r="I6">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A6,'10%触发_SKU明细'!$L$2:$L$72,$D6,'10%触发_SKU明细'!$M$2:$M$72,$E6,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>1860</v>
+        <v>1440</v>
       </c>
       <c r="J6">
         <f>$H6-$I6</f>
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="K6">
         <v>697</v>
       </c>
       <c r="L6">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M6" t="str">
-        <v>【真值】香脆小酥肉原味800g 4列；台式鸡排400g 1列；玉米布丁酥400g 1列</v>
+        <v>【真值】披萨芝士培根风味200g 8列</v>
       </c>
       <c r="N6" t="str">
         <v>正常使用</v>
@@ -13775,7 +13657,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>卧柜</v>
@@ -13784,7 +13666,7 @@
         <v>卧柜</v>
       </c>
       <c r="D7" t="str">
-        <v>卧柜2505-柜3</v>
+        <v>卧柜2000-柜1</v>
       </c>
       <c r="E7" t="str">
         <v>分区2</v>
@@ -13804,7 +13686,7 @@
         <v>697</v>
       </c>
       <c r="L7">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M7" t="str">
         <v>【真值】甄选黄油鸡蛋灌饼皮640g 1列</v>
@@ -13815,7 +13697,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>卧柜</v>
@@ -13824,7 +13706,7 @@
         <v>卧柜</v>
       </c>
       <c r="D8" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="E8" t="str">
         <v>分区1</v>
@@ -13834,20 +13716,20 @@
       </c>
       <c r="I8">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A8,'10%触发_SKU明细'!$L$2:$L$72,$D8,'10%触发_SKU明细'!$M$2:$M$72,$E8,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>1480</v>
+        <v>1485</v>
       </c>
       <c r="J8">
         <f>$H8-$I8</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <v>697</v>
       </c>
       <c r="L8">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M8" t="str">
-        <v>肉馅玉米饺480g（两袋仅15.8元） 1列；生活馆_鲜肉小馄饨/++/512g 1列；生活馆_菌菇三鲜水饺/480g 1列；魔芋羽衣甘蓝水饺480g 1列；思念放心饺猪肉荠菜水饺 1列</v>
+        <v>思念-黑芝麻汤圆455g 1列；思念大黄米黑芝麻汤圆454g 1列；【真值】芝士鸡肉卷奥尔良味120g 4列；【真值】芝士牛肉卷黑胡椒味120g 1列</v>
       </c>
       <c r="N8" t="str">
         <v>正常使用</v>
@@ -13855,7 +13737,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>卧柜</v>
@@ -13864,7 +13746,7 @@
         <v>卧柜</v>
       </c>
       <c r="D9" t="str">
-        <v>卧柜2000-柜1</v>
+        <v>卧柜2000-柜2</v>
       </c>
       <c r="E9" t="str">
         <v>分区2</v>
@@ -13884,7 +13766,7 @@
         <v>697</v>
       </c>
       <c r="L9">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M9" t="str">
         <v>酥皮香菇猪肉馅饼500g 1列</v>
@@ -13895,39 +13777,39 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C10" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D10" t="str">
-        <v>冰淇淋柜1900-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="E10" t="str">
         <v>分区1</v>
       </c>
       <c r="H10">
-        <v>1386</v>
+        <v>988</v>
       </c>
       <c r="I10">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A10,'10%触发_SKU明细'!$L$2:$L$72,$D10,'10%触发_SKU明细'!$M$2:$M$72,$E10,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>1290</v>
+        <v>935</v>
       </c>
       <c r="J10">
         <f>$H10-$I10</f>
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="K10">
-        <v>697.5</v>
+        <v>697</v>
       </c>
       <c r="L10">
-        <v>424</v>
+        <v>463</v>
       </c>
       <c r="M10" t="str">
-        <v>宏宝莱老冰棍80g 1列；蒙牛随变转巧克力雪糕65g 1列；伊利巧脆棒雪糕75g 1列；伊利大布丁60g 1列；酷企鹅食用冰杯160g 1列；上上鲜 绿色心情绿莎莎雪糕70g 1列；伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g 1列</v>
+        <v>肉馅玉米饺480g（两袋仅15.8元） 1列；生活馆_鲜肉小馄饨/++/512g 1列；生活馆_菌菇三鲜水饺/480g 1列</v>
       </c>
       <c r="N10" t="str">
         <v>正常使用</v>
@@ -13935,39 +13817,39 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C11" t="str">
-        <v>冰淇淋柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D11" t="str">
-        <v>冰淇淋柜1900-柜1</v>
+        <v>卧柜1500-柜1</v>
       </c>
       <c r="E11" t="str">
         <v>分区2</v>
       </c>
       <c r="H11">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="I11">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A11,'10%触发_SKU明细'!$L$2:$L$72,$D11,'10%触发_SKU明细'!$M$2:$M$72,$E11,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>320</v>
+        <v>224</v>
       </c>
       <c r="J11">
         <f>$H11-$I11</f>
-        <v>5</v>
+        <v>136</v>
       </c>
       <c r="K11">
-        <v>697.5</v>
+        <v>697</v>
       </c>
       <c r="L11">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="M11" t="str">
-        <v>宏宝来俄式大脆筒牛奶味100g 1列</v>
+        <v>毛肚/200g 1列</v>
       </c>
       <c r="N11" t="str">
         <v>正常使用</v>
@@ -13975,39 +13857,39 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C12" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D12" t="str">
-        <v>立柜3m-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="E12" t="str">
-        <v>第1层</v>
+        <v>分区1</v>
       </c>
       <c r="H12">
-        <v>710</v>
+        <v>988</v>
       </c>
       <c r="I12">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A12,'10%触发_SKU明细'!$L$2:$L$72,$D12,'10%触发_SKU明细'!$M$2:$M$72,$E12,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>660</v>
+        <v>905</v>
       </c>
       <c r="J12">
         <f>$H12-$I12</f>
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="K12">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L12">
-        <v>250</v>
+        <v>463</v>
       </c>
       <c r="M12" t="str">
-        <v>番茄肉酱意大利面280g 3列</v>
+        <v>魔芋羽衣甘蓝水饺480g 1列；思念放心饺猪肉荠菜水饺 1列；【真值】披萨精品榴莲芝士180g 1列；【真值】披萨黑椒牛肉风味200g 1列</v>
       </c>
       <c r="N12" t="str">
         <v>正常使用</v>
@@ -14015,39 +13897,39 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="C13" t="str">
-        <v>立柜</v>
+        <v>卧柜</v>
       </c>
       <c r="D13" t="str">
-        <v>立柜3m-柜1</v>
+        <v>卧柜1500-柜2</v>
       </c>
       <c r="E13" t="str">
-        <v>第2层</v>
+        <v>分区2</v>
       </c>
       <c r="H13">
-        <v>710</v>
+        <v>360</v>
       </c>
       <c r="I13">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A13,'10%触发_SKU明细'!$L$2:$L$72,$D13,'10%触发_SKU明细'!$M$2:$M$72,$E13,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>540</v>
+        <v>275</v>
       </c>
       <c r="J13">
         <f>$H13-$I13</f>
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="K13">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L13">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="M13" t="str">
-        <v>火锅三宝/450g（毛肚+千层肚+鸭肠） 3列</v>
+        <v>带鱼段400g 1列</v>
       </c>
       <c r="N13" t="str">
         <v>正常使用</v>
@@ -14055,39 +13937,39 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="C14" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="D14" t="str">
-        <v>立柜3m-柜1</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="E14" t="str">
-        <v>第3层</v>
+        <v>分区1</v>
       </c>
       <c r="H14">
-        <v>710</v>
+        <v>1677</v>
       </c>
       <c r="I14">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A14,'10%触发_SKU明细'!$L$2:$L$72,$D14,'10%触发_SKU明细'!$M$2:$M$72,$E14,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>580</v>
+        <v>1655</v>
       </c>
       <c r="J14">
         <f>$H14-$I14</f>
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="K14">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L14">
-        <v>250</v>
+        <v>424</v>
       </c>
       <c r="M14" t="str">
-        <v>【真值】大个爆汁鲜肉包800g 1列；【真值】大个三鲜青菜包800g 1列</v>
+        <v>宏宝莱老冰棍80g 1列；蒙牛随变转巧克力雪糕65g 1列；伊利巧脆棒雪糕75g 1列；伊利大布丁60g 1列；酷企鹅食用冰杯160g 1列；上上鲜 绿色心情绿莎莎雪糕70g 1列；伊利巧乐兹巧克力香草口味大脆筒冰淇淋85g 1列；和路雪绿舌头54g 1列；和路雪可爱多香草67g 1列</v>
       </c>
       <c r="N14" t="str">
         <v>正常使用</v>
@@ -14095,39 +13977,39 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="C15" t="str">
-        <v>立柜</v>
+        <v>冰淇淋柜</v>
       </c>
       <c r="D15" t="str">
-        <v>立柜3m-柜1</v>
+        <v>冰淇淋柜1900-柜1</v>
       </c>
       <c r="E15" t="str">
-        <v>第4层</v>
+        <v>分区2</v>
       </c>
       <c r="H15">
-        <v>710</v>
+        <v>325</v>
       </c>
       <c r="I15">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A15,'10%触发_SKU明细'!$L$2:$L$72,$D15,'10%触发_SKU明细'!$M$2:$M$72,$E15,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="J15">
         <f>$H15-$I15</f>
-        <v>210</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>534</v>
+        <v>697</v>
       </c>
       <c r="L15">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="M15" t="str">
-        <v>麻辣小龙虾1000g 2列</v>
+        <v>宏宝来俄式大脆筒牛奶味100g 1列</v>
       </c>
       <c r="N15" t="str">
         <v>正常使用</v>
@@ -14135,7 +14017,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B16" t="str">
         <v>立柜</v>
@@ -14147,18 +14029,18 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="E16" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="H16">
         <v>710</v>
       </c>
       <c r="I16">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A16,'10%触发_SKU明细'!$L$2:$L$72,$D16,'10%触发_SKU明细'!$M$2:$M$72,$E16,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>705</v>
+        <v>540</v>
       </c>
       <c r="J16">
         <f>$H16-$I16</f>
-        <v>5</v>
+        <v>170</v>
       </c>
       <c r="K16">
         <v>534</v>
@@ -14167,7 +14049,7 @@
         <v>250</v>
       </c>
       <c r="M16" t="str">
-        <v>【真值】纸皮烧麦香菇味240g 3列；【真好】乌米三丁纸皮烧麦240g 1列</v>
+        <v>火锅三宝/450g（毛肚+千层肚+鸭肠） 3列</v>
       </c>
       <c r="N16" t="str">
         <v>正常使用</v>
@@ -14175,7 +14057,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B17" t="str">
         <v>立柜</v>
@@ -14187,18 +14069,18 @@
         <v>立柜3m-柜1</v>
       </c>
       <c r="E17" t="str">
-        <v>第6层</v>
+        <v>第2层</v>
       </c>
       <c r="H17">
         <v>710</v>
       </c>
       <c r="I17">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A17,'10%触发_SKU明细'!$L$2:$L$72,$D17,'10%触发_SKU明细'!$M$2:$M$72,$E17,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="J17">
         <f>$H17-$I17</f>
-        <v>710</v>
+        <v>130</v>
       </c>
       <c r="K17">
         <v>534</v>
@@ -14207,15 +14089,15 @@
         <v>250</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>【真值】大个爆汁鲜肉包800g 1列；【真值】大个三鲜青菜包800g 1列</v>
       </c>
       <c r="N17" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B18" t="str">
         <v>立柜</v>
@@ -14224,21 +14106,21 @@
         <v>立柜</v>
       </c>
       <c r="D18" t="str">
-        <v>立柜3m-柜2</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E18" t="str">
-        <v>第1层</v>
+        <v>第3层</v>
       </c>
       <c r="H18">
         <v>710</v>
       </c>
       <c r="I18">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A18,'10%触发_SKU明细'!$L$2:$L$72,$D18,'10%触发_SKU明细'!$M$2:$M$72,$E18,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J18">
         <f>$H18-$I18</f>
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="K18">
         <v>534</v>
@@ -14247,7 +14129,7 @@
         <v>250</v>
       </c>
       <c r="M18" t="str">
-        <v>双色开花馒头（紫薯味+南瓜味）360g 3列</v>
+        <v>麻辣小龙虾1000g 2列</v>
       </c>
       <c r="N18" t="str">
         <v>正常使用</v>
@@ -14255,7 +14137,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B19" t="str">
         <v>立柜</v>
@@ -14264,21 +14146,21 @@
         <v>立柜</v>
       </c>
       <c r="D19" t="str">
-        <v>立柜3m-柜2</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E19" t="str">
-        <v>第2层</v>
+        <v>第4层</v>
       </c>
       <c r="H19">
         <v>710</v>
       </c>
       <c r="I19">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A19,'10%触发_SKU明细'!$L$2:$L$72,$D19,'10%触发_SKU明细'!$M$2:$M$72,$E19,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="J19">
         <f>$H19-$I19</f>
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K19">
         <v>534</v>
@@ -14287,7 +14169,7 @@
         <v>250</v>
       </c>
       <c r="M19" t="str">
-        <v>鸡胸肉/400g 1列；安格斯牛排150g 1列；潮香村眼肉牛排3片装 1列</v>
+        <v>番茄肉酱意大利面280g 3列</v>
       </c>
       <c r="N19" t="str">
         <v>正常使用</v>
@@ -14295,7 +14177,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B20" t="str">
         <v>立柜</v>
@@ -14304,21 +14186,21 @@
         <v>立柜</v>
       </c>
       <c r="D20" t="str">
-        <v>立柜3m-柜2</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E20" t="str">
-        <v>第3层</v>
+        <v>第5层</v>
       </c>
       <c r="H20">
         <v>710</v>
       </c>
       <c r="I20">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A20,'10%触发_SKU明细'!$L$2:$L$72,$D20,'10%触发_SKU明细'!$M$2:$M$72,$E20,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>660</v>
+        <v>705</v>
       </c>
       <c r="J20">
         <f>$H20-$I20</f>
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>534</v>
@@ -14327,7 +14209,7 @@
         <v>250</v>
       </c>
       <c r="M20" t="str">
-        <v>【真值】纸皮烧麦蛋黄味240g 4列</v>
+        <v>【真值】纸皮烧麦香菇味240g 3列；【真好】乌米三丁纸皮烧麦240g 1列</v>
       </c>
       <c r="N20" t="str">
         <v>正常使用</v>
@@ -14335,7 +14217,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B21" t="str">
         <v>立柜</v>
@@ -14344,21 +14226,21 @@
         <v>立柜</v>
       </c>
       <c r="D21" t="str">
-        <v>立柜3m-柜2</v>
+        <v>立柜3m-柜1</v>
       </c>
       <c r="E21" t="str">
-        <v>第4层</v>
+        <v>第6层</v>
       </c>
       <c r="H21">
         <v>710</v>
       </c>
       <c r="I21">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A21,'10%触发_SKU明细'!$L$2:$L$72,$D21,'10%触发_SKU明细'!$M$2:$M$72,$E21,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>465</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <f>$H21-$I21</f>
-        <v>245</v>
+        <v>710</v>
       </c>
       <c r="K21">
         <v>534</v>
@@ -14367,15 +14249,15 @@
         <v>250</v>
       </c>
       <c r="M21" t="str">
-        <v>抽肠青虾仁150g 1列；黑鱼片250g 1列</v>
+        <v/>
       </c>
       <c r="N21" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B22" t="str">
         <v>立柜</v>
@@ -14387,18 +14269,18 @@
         <v>立柜3m-柜2</v>
       </c>
       <c r="E22" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="H22">
         <v>710</v>
       </c>
       <c r="I22">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A22,'10%触发_SKU明细'!$L$2:$L$72,$D22,'10%触发_SKU明细'!$M$2:$M$72,$E22,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="J22">
         <f>$H22-$I22</f>
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="K22">
         <v>534</v>
@@ -14407,7 +14289,7 @@
         <v>250</v>
       </c>
       <c r="M22" t="str">
-        <v>整虾/冷冻南美白虾250g 2列</v>
+        <v>双色开花馒头（紫薯味+南瓜味）360g 3列</v>
       </c>
       <c r="N22" t="str">
         <v>正常使用</v>
@@ -14415,7 +14297,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B23" t="str">
         <v>立柜</v>
@@ -14427,18 +14309,18 @@
         <v>立柜3m-柜2</v>
       </c>
       <c r="E23" t="str">
-        <v>第6层</v>
+        <v>第2层</v>
       </c>
       <c r="H23">
         <v>710</v>
       </c>
       <c r="I23">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A23,'10%触发_SKU明细'!$L$2:$L$72,$D23,'10%触发_SKU明细'!$M$2:$M$72,$E23,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="J23">
         <f>$H23-$I23</f>
-        <v>710</v>
+        <v>35</v>
       </c>
       <c r="K23">
         <v>534</v>
@@ -14447,15 +14329,15 @@
         <v>250</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>鸡胸肉/400g 1列；安格斯牛排150g 1列；潮香村眼肉牛排3片装 1列</v>
       </c>
       <c r="N23" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B24" t="str">
         <v>立柜</v>
@@ -14464,10 +14346,10 @@
         <v>立柜</v>
       </c>
       <c r="D24" t="str">
-        <v>立柜3m-柜3</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E24" t="str">
-        <v>第1层</v>
+        <v>第3层</v>
       </c>
       <c r="H24">
         <v>710</v>
@@ -14487,7 +14369,7 @@
         <v>250</v>
       </c>
       <c r="M24" t="str">
-        <v>【真值】纸皮烧麦鲜肉味240g 4列</v>
+        <v>【真值】纸皮烧麦蛋黄味240g 4列</v>
       </c>
       <c r="N24" t="str">
         <v>正常使用</v>
@@ -14495,7 +14377,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B25" t="str">
         <v>立柜</v>
@@ -14504,21 +14386,21 @@
         <v>立柜</v>
       </c>
       <c r="D25" t="str">
-        <v>立柜3m-柜3</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E25" t="str">
-        <v>第2层</v>
+        <v>第4层</v>
       </c>
       <c r="H25">
         <v>710</v>
       </c>
       <c r="I25">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A25,'10%触发_SKU明细'!$L$2:$L$72,$D25,'10%触发_SKU明细'!$M$2:$M$72,$E25,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>610</v>
+        <v>465</v>
       </c>
       <c r="J25">
         <f>$H25-$I25</f>
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="K25">
         <v>534</v>
@@ -14527,7 +14409,7 @@
         <v>250</v>
       </c>
       <c r="M25" t="str">
-        <v>手作奶香黄油开花馒头360g 2列；【真值】披萨奥尔良风味鸡肉味200克 1列</v>
+        <v>抽肠青虾仁150g 1列；黑鱼片250g 1列</v>
       </c>
       <c r="N25" t="str">
         <v>正常使用</v>
@@ -14535,7 +14417,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B26" t="str">
         <v>立柜</v>
@@ -14544,21 +14426,21 @@
         <v>立柜</v>
       </c>
       <c r="D26" t="str">
-        <v>立柜3m-柜3</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E26" t="str">
-        <v>第3层</v>
+        <v>第5层</v>
       </c>
       <c r="H26">
         <v>710</v>
       </c>
       <c r="I26">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A26,'10%触发_SKU明细'!$L$2:$L$72,$D26,'10%触发_SKU明细'!$M$2:$M$72,$E26,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>448</v>
+        <v>550</v>
       </c>
       <c r="J26">
         <f>$H26-$I26</f>
-        <v>262</v>
+        <v>160</v>
       </c>
       <c r="K26">
         <v>534</v>
@@ -14567,7 +14449,7 @@
         <v>250</v>
       </c>
       <c r="M26" t="str">
-        <v>毛肚/200g 2列</v>
+        <v>整虾/冷冻南美白虾250g 2列</v>
       </c>
       <c r="N26" t="str">
         <v>正常使用</v>
@@ -14575,7 +14457,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B27" t="str">
         <v>立柜</v>
@@ -14584,21 +14466,21 @@
         <v>立柜</v>
       </c>
       <c r="D27" t="str">
-        <v>立柜3m-柜3</v>
+        <v>立柜3m-柜2</v>
       </c>
       <c r="E27" t="str">
-        <v>第4层</v>
+        <v>第6层</v>
       </c>
       <c r="H27">
         <v>710</v>
       </c>
       <c r="I27">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A27,'10%触发_SKU明细'!$L$2:$L$72,$D27,'10%触发_SKU明细'!$M$2:$M$72,$E27,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>665</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <f>$H27-$I27</f>
-        <v>45</v>
+        <v>710</v>
       </c>
       <c r="K27">
         <v>534</v>
@@ -14607,15 +14489,15 @@
         <v>250</v>
       </c>
       <c r="M27" t="str">
-        <v>皓月新西兰羔羊卷WMT/450g 1列；原切肥羊卷300g 1列；冷冻食材_潮汕风味牛肉丸/160g 1列</v>
+        <v/>
       </c>
       <c r="N27" t="str">
-        <v>正常使用</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B28" t="str">
         <v>立柜</v>
@@ -14627,18 +14509,18 @@
         <v>立柜3m-柜3</v>
       </c>
       <c r="E28" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="H28">
         <v>710</v>
       </c>
       <c r="I28">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A28,'10%触发_SKU明细'!$L$2:$L$72,$D28,'10%触发_SKU明细'!$M$2:$M$72,$E28,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="J28">
         <f>$H28-$I28</f>
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K28">
         <v>534</v>
@@ -14647,7 +14529,7 @@
         <v>250</v>
       </c>
       <c r="M28" t="str">
-        <v>【真好】黑猪肉爆汁烤肠原味400g 3列</v>
+        <v>【真值】纸皮烧麦鲜肉味240g 4列</v>
       </c>
       <c r="N28" t="str">
         <v>正常使用</v>
@@ -14655,7 +14537,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B29" t="str">
         <v>立柜</v>
@@ -14667,18 +14549,18 @@
         <v>立柜3m-柜3</v>
       </c>
       <c r="E29" t="str">
-        <v>第6层</v>
+        <v>第2层</v>
       </c>
       <c r="H29">
         <v>710</v>
       </c>
       <c r="I29">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A29,'10%触发_SKU明细'!$L$2:$L$72,$D29,'10%触发_SKU明细'!$M$2:$M$72,$E29,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="J29">
         <f>$H29-$I29</f>
-        <v>710</v>
+        <v>100</v>
       </c>
       <c r="K29">
         <v>534</v>
@@ -14687,15 +14569,15 @@
         <v>250</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>手作奶香黄油开花馒头360g 2列；【真值】披萨奥尔良风味鸡肉味200克 1列</v>
       </c>
       <c r="N29" t="str">
-        <v>存储位</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B30" t="str">
         <v>立柜</v>
@@ -14704,21 +14586,21 @@
         <v>立柜</v>
       </c>
       <c r="D30" t="str">
-        <v>立柜3m-柜4</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E30" t="str">
-        <v>第1层</v>
+        <v>第3层</v>
       </c>
       <c r="H30">
         <v>710</v>
       </c>
       <c r="I30">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A30,'10%触发_SKU明细'!$L$2:$L$72,$D30,'10%触发_SKU明细'!$M$2:$M$72,$E30,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="J30">
         <f>$H30-$I30</f>
-        <v>710</v>
+        <v>155</v>
       </c>
       <c r="K30">
         <v>534</v>
@@ -14727,15 +14609,15 @@
         <v>250</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>冷冻食材_潮汕风味牛肉丸/160g 3列</v>
       </c>
       <c r="N30" t="str">
-        <v>其他品类预留</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B31" t="str">
         <v>立柜</v>
@@ -14744,21 +14626,21 @@
         <v>立柜</v>
       </c>
       <c r="D31" t="str">
-        <v>立柜3m-柜4</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E31" t="str">
-        <v>第2层</v>
+        <v>第4层</v>
       </c>
       <c r="H31">
         <v>710</v>
       </c>
       <c r="I31">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A31,'10%触发_SKU明细'!$L$2:$L$72,$D31,'10%触发_SKU明细'!$M$2:$M$72,$E31,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="J31">
         <f>$H31-$I31</f>
-        <v>710</v>
+        <v>230</v>
       </c>
       <c r="K31">
         <v>534</v>
@@ -14767,15 +14649,15 @@
         <v>250</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>皓月新西兰羔羊卷WMT/450g 1列；原切肥羊卷300g 1列</v>
       </c>
       <c r="N31" t="str">
-        <v>其他品类预留</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B32" t="str">
         <v>立柜</v>
@@ -14784,21 +14666,21 @@
         <v>立柜</v>
       </c>
       <c r="D32" t="str">
-        <v>立柜3m-柜4</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E32" t="str">
-        <v>第3层</v>
+        <v>第5层</v>
       </c>
       <c r="H32">
         <v>710</v>
       </c>
       <c r="I32">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A32,'10%触发_SKU明细'!$L$2:$L$72,$D32,'10%触发_SKU明细'!$M$2:$M$72,$E32,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>0</v>
+        <v>675</v>
       </c>
       <c r="J32">
         <f>$H32-$I32</f>
-        <v>710</v>
+        <v>35</v>
       </c>
       <c r="K32">
         <v>534</v>
@@ -14807,15 +14689,15 @@
         <v>250</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>【真好】黑猪肉爆汁烤肠原味400g 3列</v>
       </c>
       <c r="N32" t="str">
-        <v>其他品类预留</v>
+        <v>正常使用</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B33" t="str">
         <v>立柜</v>
@@ -14824,10 +14706,10 @@
         <v>立柜</v>
       </c>
       <c r="D33" t="str">
-        <v>立柜3m-柜4</v>
+        <v>立柜3m-柜3</v>
       </c>
       <c r="E33" t="str">
-        <v>第4层</v>
+        <v>第6层</v>
       </c>
       <c r="H33">
         <v>710</v>
@@ -14850,12 +14732,12 @@
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>其他品类预留</v>
+        <v>存储位</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B34" t="str">
         <v>立柜</v>
@@ -14867,18 +14749,18 @@
         <v>立柜3m-柜4</v>
       </c>
       <c r="E34" t="str">
-        <v>第5层</v>
+        <v>第1层</v>
       </c>
       <c r="H34">
         <v>710</v>
       </c>
       <c r="I34">
         <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A34,'10%触发_SKU明细'!$L$2:$L$72,$D34,'10%触发_SKU明细'!$M$2:$M$72,$E34,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <f>$H34-$I34</f>
-        <v>85</v>
+        <v>710</v>
       </c>
       <c r="K34">
         <v>534</v>
@@ -14887,15 +14769,15 @@
         <v>250</v>
       </c>
       <c r="M34" t="str">
-        <v>肉馅芹菜饺480g（两袋仅15.8元） 1列；荠菜笋丁鸡胸肉水饺480g 1列</v>
+        <v/>
       </c>
       <c r="N34" t="str">
-        <v>正常使用</v>
+        <v>其他品类预留</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B35" t="str">
         <v>立柜</v>
@@ -14907,7 +14789,7 @@
         <v>立柜3m-柜4</v>
       </c>
       <c r="E35" t="str">
-        <v>第6层</v>
+        <v>第2层</v>
       </c>
       <c r="H35">
         <v>710</v>
@@ -14930,20 +14812,180 @@
         <v/>
       </c>
       <c r="N35" t="str">
+        <v>其他品类预留</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B36" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C36" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D36" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E36" t="str">
+        <v>第3层</v>
+      </c>
+      <c r="H36">
+        <v>710</v>
+      </c>
+      <c r="I36">
+        <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A36,'10%触发_SKU明细'!$L$2:$L$72,$D36,'10%触发_SKU明细'!$M$2:$M$72,$E36,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <f>$H36-$I36</f>
+        <v>710</v>
+      </c>
+      <c r="K36">
+        <v>534</v>
+      </c>
+      <c r="L36">
+        <v>250</v>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v>其他品类预留</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B37" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C37" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D37" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E37" t="str">
+        <v>第4层</v>
+      </c>
+      <c r="H37">
+        <v>710</v>
+      </c>
+      <c r="I37">
+        <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A37,'10%触发_SKU明细'!$L$2:$L$72,$D37,'10%触发_SKU明细'!$M$2:$M$72,$E37,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <f>$H37-$I37</f>
+        <v>710</v>
+      </c>
+      <c r="K37">
+        <v>534</v>
+      </c>
+      <c r="L37">
+        <v>250</v>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v>其他品类预留</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B38" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C38" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D38" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E38" t="str">
+        <v>第5层</v>
+      </c>
+      <c r="H38">
+        <v>710</v>
+      </c>
+      <c r="I38">
+        <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A38,'10%触发_SKU明细'!$L$2:$L$72,$D38,'10%触发_SKU明细'!$M$2:$M$72,$E38,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
+        <v>625</v>
+      </c>
+      <c r="J38">
+        <f>$H38-$I38</f>
+        <v>85</v>
+      </c>
+      <c r="K38">
+        <v>534</v>
+      </c>
+      <c r="L38">
+        <v>250</v>
+      </c>
+      <c r="M38" t="str">
+        <v>肉馅芹菜饺480g（两袋仅15.8元） 1列；荠菜笋丁鸡胸肉水饺480g 1列</v>
+      </c>
+      <c r="N38" t="str">
+        <v>正常使用</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>和县生活馆</v>
+      </c>
+      <c r="B39" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="C39" t="str">
+        <v>立柜</v>
+      </c>
+      <c r="D39" t="str">
+        <v>立柜3m-柜4</v>
+      </c>
+      <c r="E39" t="str">
+        <v>第6层</v>
+      </c>
+      <c r="H39">
+        <v>710</v>
+      </c>
+      <c r="I39">
+        <f>SUMIFS('10%触发_SKU明细'!$T$2:$T$72,'10%触发_SKU明细'!$A$2:$A$72,$A39,'10%触发_SKU明细'!$L$2:$L$72,$D39,'10%触发_SKU明细'!$M$2:$M$72,$E39,'10%触发_SKU明细'!$P$2:$P$72,"纳入")</f>
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <f>$H39-$I39</f>
+        <v>710</v>
+      </c>
+      <c r="K39">
+        <v>534</v>
+      </c>
+      <c r="L39">
+        <v>250</v>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v>存储位</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N35"/>
+  <autoFilter ref="A1:N39"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14982,7 +15024,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B2" t="str">
         <v>小于等于10%触发</v>
@@ -15017,7 +15059,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B3" t="str">
         <v>小于等于10%触发</v>
@@ -15052,7 +15094,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B4" t="str">
         <v>小于等于10%触发</v>
@@ -15087,7 +15129,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B5" t="str">
         <v>小于等于10%触发</v>
@@ -15122,7 +15164,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B6" t="str">
         <v>小于等于10%触发</v>
@@ -15157,7 +15199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B7" t="str">
         <v>小于等于10%触发</v>
@@ -15192,7 +15234,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B8" t="str">
         <v>小于等于10%触发</v>
@@ -15227,7 +15269,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B9" t="str">
         <v>小于等于10%触发</v>
@@ -15239,10 +15281,10 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E9" t="str">
-        <v>D</v>
+        <v>A</v>
       </c>
       <c r="F9">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -15251,18 +15293,18 @@
         <v>冷冻食材</v>
       </c>
       <c r="I9" t="str">
-        <v>冷冻水产</v>
+        <v>冷冻水果</v>
       </c>
       <c r="J9" t="str">
-        <v>带鱼段400g</v>
+        <v>冻榴莲500g</v>
       </c>
       <c r="K9" t="str">
-        <v>6971806121982</v>
+        <v>6977480891210</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B10" t="str">
         <v>小于等于10%触发</v>
@@ -15274,30 +15316,30 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E10" t="str">
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>冷冻食材</v>
+        <v>预制主食</v>
       </c>
       <c r="I10" t="str">
-        <v>冷冻水果</v>
+        <v>馒头发糕</v>
       </c>
       <c r="J10" t="str">
-        <v>冻榴莲500g</v>
+        <v>生活馆_料多多薯香乳酪包/400g</v>
       </c>
       <c r="K10" t="str">
-        <v>6977480891210</v>
+        <v>6971997913342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B11" t="str">
         <v>小于等于10%触发</v>
@@ -15309,10 +15351,10 @@
         <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E11" t="str">
-        <v>C</v>
+        <v>未评级</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>9999</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -15324,15 +15366,15 @@
         <v>馒头发糕</v>
       </c>
       <c r="J11" t="str">
-        <v>生活馆_料多多薯香乳酪包/400g</v>
+        <v>鲜奶馒头300g</v>
       </c>
       <c r="K11" t="str">
-        <v>6971997913342</v>
+        <v>6973560306940</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B12" t="str">
         <v>小于等于10%触发</v>
@@ -15341,33 +15383,33 @@
         <v>暂不纳入</v>
       </c>
       <c r="D12" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
+        <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E12" t="str">
-        <v>未评级</v>
+        <v>B</v>
       </c>
       <c r="F12">
-        <v>9999</v>
+        <v>23</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>预制主食</v>
+        <v>雪糕冰品</v>
       </c>
       <c r="I12" t="str">
-        <v>馒头发糕</v>
+        <v>雪糕冰淇淋</v>
       </c>
       <c r="J12" t="str">
-        <v>鲜奶馒头300g</v>
+        <v>雀巢8次方巧克力香草味84g</v>
       </c>
       <c r="K12" t="str">
-        <v>6973560306940</v>
+        <v>6918551807884</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B13" t="str">
         <v>小于等于10%触发</v>
@@ -15379,10 +15421,10 @@
         <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E13" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="F13">
-        <v>22</v>
+        <v>9999</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -15394,15 +15436,15 @@
         <v>雪糕冰淇淋</v>
       </c>
       <c r="J13" t="str">
-        <v>和路雪绿舌头54g</v>
+        <v>小金条无核榴莲肉100g</v>
       </c>
       <c r="K13" t="str">
-        <v>6909493800453</v>
+        <v>6977480896154</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B14" t="str">
         <v>小于等于10%触发</v>
@@ -15414,10 +15456,10 @@
         <v>无符合冰柜类型及尺寸的可用陈列位</v>
       </c>
       <c r="E14" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="F14">
-        <v>23</v>
+        <v>9999</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -15429,15 +15471,15 @@
         <v>雪糕冰淇淋</v>
       </c>
       <c r="J14" t="str">
-        <v>雀巢8次方巧克力香草味84g</v>
+        <v>伊利6重巧巧70g</v>
       </c>
       <c r="K14" t="str">
-        <v>6918551807884</v>
+        <v>6907992827353</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>示例生活馆</v>
+        <v>和县生活馆</v>
       </c>
       <c r="B15" t="str">
         <v>小于等于10%触发</v>
@@ -15446,139 +15488,34 @@
         <v>暂不纳入</v>
       </c>
       <c r="D15" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
+        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
       </c>
       <c r="E15" t="str">
-        <v>B</v>
+        <v>未评级</v>
       </c>
       <c r="F15">
-        <v>33</v>
+        <v>9999</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>雪糕冰品</v>
+        <v>预制菜类</v>
       </c>
       <c r="I15" t="str">
-        <v>雪糕冰淇淋</v>
+        <v>炸物小吃</v>
       </c>
       <c r="J15" t="str">
-        <v>和路雪可爱多香草67g</v>
+        <v>美好小酥肉800g</v>
       </c>
       <c r="K15" t="str">
-        <v>6909493401032</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B16" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C16" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D16" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E16" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F16">
-        <v>9999</v>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I16" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J16" t="str">
-        <v>小金条无核榴莲肉100g</v>
-      </c>
-      <c r="K16" t="str">
-        <v>6977480896154</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B17" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C17" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D17" t="str">
-        <v>无符合冰柜类型及尺寸的可用陈列位</v>
-      </c>
-      <c r="E17" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F17">
-        <v>9999</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v>雪糕冰品</v>
-      </c>
-      <c r="I17" t="str">
-        <v>雪糕冰淇淋</v>
-      </c>
-      <c r="J17" t="str">
-        <v>伊利6重巧巧70g</v>
-      </c>
-      <c r="K17" t="str">
-        <v>6907992827353</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>示例生活馆</v>
-      </c>
-      <c r="B18" t="str">
-        <v>小于等于10%触发</v>
-      </c>
-      <c r="C18" t="str">
-        <v>暂不纳入</v>
-      </c>
-      <c r="D18" t="str">
-        <v>为满足外储上限，按低等级、外储压力、周转排序暂不首批纳入</v>
-      </c>
-      <c r="E18" t="str">
-        <v>未评级</v>
-      </c>
-      <c r="F18">
-        <v>9999</v>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
-      <c r="H18" t="str">
-        <v>预制菜类</v>
-      </c>
-      <c r="I18" t="str">
-        <v>炸物小吃</v>
-      </c>
-      <c r="J18" t="str">
-        <v>美好小酥肉800g</v>
-      </c>
-      <c r="K18" t="str">
         <v>6971938880948</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K18"/>
+  <autoFilter ref="A1:K15"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K15"/>
   </ignoredErrors>
 </worksheet>
 </file>
